--- a/docs/downloads/2026-09-24/bursa-report-2026-09-24.xlsx
+++ b/docs/downloads/2026-09-24/bursa-report-2026-09-24.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-24" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-24'!$A$1:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-24'!$A$1:$M$143</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,10 +38,10 @@
       <color rgb="000CA30C"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="00D03B3B"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="00898781"/>
     </font>
   </fonts>
   <fills count="4">
@@ -74,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -92,12 +92,13 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -463,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -556,28 +557,28 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.59</v>
+        <v>1.1</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0261</v>
+        <v>0.0476</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>22992500</v>
+        <v>1861400</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.05</v>
+        <v>0.43</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>75.95</v>
+        <v>83.77</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -585,10 +586,10 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.533</v>
+        <v>0.946</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.487</v>
+        <v>0.78</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -597,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>RSI达75.95，处超买区；现价0.59高于50日均线0.487约21%，EMA20与SAR多头信号一致，但短线过热。</t>
+          <t>现价RM1.1高于50日均线RM0.78约41%，EMA20与SAR均呈多头，但RSI达83.77，处超买区，信号可靠性受高位回调风险制约。</t>
         </is>
       </c>
     </row>
@@ -609,28 +610,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.23</v>
+        <v>0.175</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0</v>
+        <v>-0.0541</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>5497100</v>
+        <v>167952300</v>
       </c>
       <c r="G3" s="12" t="n">
         <v>0.28</v>
       </c>
       <c r="H3" t="n">
-        <v>37.55</v>
+        <v>20.58</v>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
@@ -638,10 +639,10 @@
         </is>
       </c>
       <c r="J3" s="9" t="n">
-        <v>0.243</v>
+        <v>0.293</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>0.25</v>
+        <v>0.512</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="14" t="inlineStr"/>
@@ -654,39 +655,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>-0.027</v>
+        <v>0.24</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>4205000</v>
+        <v>30228200</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.01</v>
+        <v>1.57</v>
       </c>
       <c r="H4" t="n">
-        <v>20.93</v>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.77</v>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.293</v>
+        <v>0.231</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.512</v>
+        <v>0.233</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -699,39 +700,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>CFM</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>-0.0189</v>
+        <v>0.095</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>0.0556</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>525900</v>
+        <v>23678800</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>44.03</v>
       </c>
       <c r="H5" t="n">
-        <v>67.05</v>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
+        <v>81.81</v>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.075</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.681</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -744,45 +745,6210 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>0</v>
+        <v>0.485</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0.0211</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>507000</v>
+        <v>18700900</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.08</v>
+        <v>0.76</v>
       </c>
       <c r="H6" t="n">
-        <v>55.55</v>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
+        <v>56.56</v>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.518</v>
+        <v>0.468</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.529</v>
+        <v>0.47</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>5243</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VELESTO</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>16928200</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H7" t="n">
+        <v>37.55</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" s="14" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>16721500</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H8" t="n">
+        <v>76.81</v>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" s="14" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SUNMED</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>-0.0188</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>15987700</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H9" t="n">
+        <v>46.56</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>2.137</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>2.056</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" s="14" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SUPERMX</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0.0633</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>14961600</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H10" t="n">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>7113</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TOPGLOV</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>14631000</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H11" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>4723</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>JAKS</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>14419000</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H12" t="n">
+        <v>71.51000000000001</v>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5238</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AAGB</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>13813100</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H13" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5078</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>M&amp;G</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>13309200</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H14" t="n">
+        <v>62.58</v>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>3174</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>L&amp;G</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>12144100</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>85.45</v>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5216</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NEXG</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>0.0566</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>10760400</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H16" t="n">
+        <v>53.44</v>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0353</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>WESTRVR</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>0.0946</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>10553500</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="H17" t="n">
+        <v>72.56</v>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0163</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CAREPLS</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>10523700</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>67.23</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0182</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LKL</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>10105100</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>95.98999999999999</v>
+      </c>
+      <c r="H19" t="n">
+        <v>63.02</v>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="K19" s="9" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="14" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>7215</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NIHSIN</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>8927200</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H20" t="n">
+        <v>85.84999999999999</v>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="14" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0034</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MMAG</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>8738100</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H21" t="n">
+        <v>49.97</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="14" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0007</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PUC</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>8603400</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H22" t="n">
+        <v>56.29</v>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="14" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>8510600</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H23" t="n">
+        <v>61.39</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>4.482</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>7973800</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H24" t="n">
+        <v>47.43</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>0.603</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NATGATE</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>-0.0219</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>7718600</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H25" t="n">
+        <v>61.15</v>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>1.713</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>1.493</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>-0.006500000000000001</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>7684000</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H26" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CEB</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>-0.0169</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>7408100</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="H27" t="n">
+        <v>64.13</v>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="14" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>-0.0252</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>7389000</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H28" t="n">
+        <v>65.91</v>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="14" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2429</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TANCO</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>7084700</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H29" t="n">
+        <v>37.08</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="14" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0175</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>HHRG</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>-0.0303</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>6270100</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H30" t="n">
+        <v>51.62</v>
+      </c>
+      <c r="I30" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="14" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>9377</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>FSBM</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>5849200</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H31" t="n">
+        <v>39.23</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="14" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>5583700</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>62.25</v>
+      </c>
+      <c r="I32" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>1.083</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="14" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>7200</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>TEKSENG</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>5468500</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="H33" t="n">
+        <v>79.06999999999999</v>
+      </c>
+      <c r="I33" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="14" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>-0.0206</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>5384900</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H34" t="n">
+        <v>54.07</v>
+      </c>
+      <c r="I34" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="14" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>5365900</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H35" t="n">
+        <v>52.62</v>
+      </c>
+      <c r="I35" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="14" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0181</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AEMULUS</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>-0.0345</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>5190600</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H36" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="I36" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="14" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0055</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SERSOL</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>5155000</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H37" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="I37" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="14" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>8052</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CGB</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>5018400</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H38" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0024</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>JAG</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>0.0274</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>4470200</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H39" t="n">
+        <v>56.64</v>
+      </c>
+      <c r="I39" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="E40" s="16" t="n">
+        <v>0.0157</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>4458200</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H40" t="n">
+        <v>86.17</v>
+      </c>
+      <c r="I40" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>9326</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>LBALUM</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>3911400</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="H41" t="n">
+        <v>66.51000000000001</v>
+      </c>
+      <c r="I41" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>3907500</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H42" t="n">
+        <v>64.84999999999999</v>
+      </c>
+      <c r="I42" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>2.826</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>2.687</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>7155</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SKPRES</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>-0.0405</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>3820100</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H43" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="I43" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="14" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>9679</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>WCT</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>-0.0267</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>3802400</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H44" t="n">
+        <v>38.42</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="14" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>-0.0098</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>3477500</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H45" t="n">
+        <v>79.65000000000001</v>
+      </c>
+      <c r="I45" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="14" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>-0.0038</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>3476000</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H46" t="n">
+        <v>58.63</v>
+      </c>
+      <c r="I46" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>7.768</v>
+      </c>
+      <c r="K46" s="9" t="n">
+        <v>7.715</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="14" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>-0.0417</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>3465500</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H47" t="n">
+        <v>52.56</v>
+      </c>
+      <c r="I47" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>1.386</v>
+      </c>
+      <c r="K47" s="9" t="n">
+        <v>1.284</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="14" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>3458600</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H48" t="n">
+        <v>42.28</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>1.922</v>
+      </c>
+      <c r="K48" s="9" t="n">
+        <v>1.972</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="14" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E49" s="16" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>3370800</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H49" t="n">
+        <v>83.98999999999999</v>
+      </c>
+      <c r="I49" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="14" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1961</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>IOICORP</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E50" s="16" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>3351100</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H50" t="n">
+        <v>58.16</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>4.745</v>
+      </c>
+      <c r="K50" s="9" t="n">
+        <v>4.579</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="14" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0251</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SFPTECH</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>3256800</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H51" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="I51" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="K51" s="9" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="14" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>5099</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CAPITALA</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>-0.0196</v>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>3111600</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H52" t="n">
+        <v>33.17</v>
+      </c>
+      <c r="I52" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="K52" s="9" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="14" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0259</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>-0.009399999999999999</v>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>3021400</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H53" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="I53" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="K53" s="9" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="14" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E54" s="16" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>2964100</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H54" t="n">
+        <v>63.73</v>
+      </c>
+      <c r="I54" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K54" s="9" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="14" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>-0.0242</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>2944600</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H55" t="n">
+        <v>36.17</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="K55" s="9" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="14" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>5148</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>UEMS</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>-0.0092</v>
+      </c>
+      <c r="F56" s="11" t="n">
+        <v>2927300</v>
+      </c>
+      <c r="G56" s="12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H56" t="n">
+        <v>35.04</v>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="K56" s="9" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="14" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>-0.0074</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>2752400</v>
+      </c>
+      <c r="G57" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H57" t="n">
+        <v>45</v>
+      </c>
+      <c r="I57" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K57" s="9" t="n">
+        <v>2.893</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="14" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0172</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>OCK</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E58" s="16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F58" s="11" t="n">
+        <v>2646500</v>
+      </c>
+      <c r="G58" s="12" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H58" t="n">
+        <v>81.36</v>
+      </c>
+      <c r="I58" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="K58" s="9" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="14" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>YTLPOWR</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>-0.0118</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>2620500</v>
+      </c>
+      <c r="G59" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H59" t="n">
+        <v>62.62</v>
+      </c>
+      <c r="I59" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>5.655</v>
+      </c>
+      <c r="K59" s="9" t="n">
+        <v>5.068</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="14" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0267</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ECA</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>-0.0625</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>2616700</v>
+      </c>
+      <c r="G60" s="12" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H60" t="n">
+        <v>44.92</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="K60" s="9" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="14" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>-0.0182</v>
+      </c>
+      <c r="F61" s="11" t="n">
+        <v>2589100</v>
+      </c>
+      <c r="G61" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H61" t="n">
+        <v>57.69</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="K61" s="9" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="14" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>D&amp;O</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>2575800</v>
+      </c>
+      <c r="G62" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H62" t="n">
+        <v>70.97</v>
+      </c>
+      <c r="I62" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K62" s="9" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="14" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>-0.0196</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <v>2528700</v>
+      </c>
+      <c r="G63" s="12" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H63" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="I63" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="K63" s="9" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="14" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1651</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MRCB</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E64" s="16" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="F64" s="11" t="n">
+        <v>2501900</v>
+      </c>
+      <c r="G64" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H64" t="n">
+        <v>39.08</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K64" s="9" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="14" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>-0.0284</v>
+      </c>
+      <c r="F65" s="11" t="n">
+        <v>2417100</v>
+      </c>
+      <c r="G65" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H65" t="n">
+        <v>51.73</v>
+      </c>
+      <c r="I65" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="K65" s="9" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="14" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="F66" s="11" t="n">
+        <v>2415600</v>
+      </c>
+      <c r="G66" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H66" t="n">
+        <v>42.64</v>
+      </c>
+      <c r="I66" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="n">
+        <v>10.173</v>
+      </c>
+      <c r="K66" s="9" t="n">
+        <v>10.345</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="14" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SPSETIA</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="11" t="n">
+        <v>2330700</v>
+      </c>
+      <c r="G67" s="12" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H67" t="n">
+        <v>30.81</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="K67" s="9" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="14" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E68" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="11" t="n">
+        <v>2245400</v>
+      </c>
+      <c r="G68" s="12" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H68" t="n">
+        <v>33.24</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="n">
+        <v>1.059</v>
+      </c>
+      <c r="K68" s="9" t="n">
+        <v>1.072</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="14" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>5212</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>PAVREIT</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="F69" s="11" t="n">
+        <v>2222600</v>
+      </c>
+      <c r="G69" s="12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H69" t="n">
+        <v>40.66</v>
+      </c>
+      <c r="I69" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="n">
+        <v>1.591</v>
+      </c>
+      <c r="K69" s="9" t="n">
+        <v>1.654</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="14" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="11" t="n">
+        <v>2142300</v>
+      </c>
+      <c r="G70" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H70" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="K70" s="9" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="14" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E71" s="16" t="n">
+        <v>0.005600000000000001</v>
+      </c>
+      <c r="F71" s="11" t="n">
+        <v>2135600</v>
+      </c>
+      <c r="G71" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H71" t="n">
+        <v>68.48</v>
+      </c>
+      <c r="I71" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="K71" s="9" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="14" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>-0.0224</v>
+      </c>
+      <c r="F72" s="11" t="n">
+        <v>2037000</v>
+      </c>
+      <c r="G72" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H72" t="n">
+        <v>59.56</v>
+      </c>
+      <c r="I72" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="K72" s="9" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="14" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>5056</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ENGTEX</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="E73" s="16" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="F73" s="11" t="n">
+        <v>1992500</v>
+      </c>
+      <c r="G73" s="12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H73" t="n">
+        <v>60.62</v>
+      </c>
+      <c r="I73" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="K73" s="9" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="14" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>-0.0168</v>
+      </c>
+      <c r="F74" s="11" t="n">
+        <v>1972400</v>
+      </c>
+      <c r="G74" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H74" t="n">
+        <v>48.92</v>
+      </c>
+      <c r="I74" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="n">
+        <v>1.185</v>
+      </c>
+      <c r="K74" s="9" t="n">
+        <v>1.131</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="14" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="F75" s="11" t="n">
+        <v>1924500</v>
+      </c>
+      <c r="G75" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H75" t="n">
+        <v>59.41</v>
+      </c>
+      <c r="I75" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J75" s="9" t="n">
+        <v>2.589</v>
+      </c>
+      <c r="K75" s="9" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="14" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0193</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>KINERGY</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>-0.0238</v>
+      </c>
+      <c r="F76" s="11" t="n">
+        <v>1911000</v>
+      </c>
+      <c r="G76" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H76" t="n">
+        <v>52.95</v>
+      </c>
+      <c r="I76" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="K76" s="9" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="14" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SUNREIT</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>-0.0144</v>
+      </c>
+      <c r="F77" s="11" t="n">
+        <v>1838100</v>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H77" t="n">
+        <v>45.19</v>
+      </c>
+      <c r="I77" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J77" s="9" t="n">
+        <v>2.069</v>
+      </c>
+      <c r="K77" s="9" t="n">
+        <v>2.113</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="14" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E78" s="16" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="F78" s="11" t="n">
+        <v>1815100</v>
+      </c>
+      <c r="G78" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H78" t="n">
+        <v>62.02</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="n">
+        <v>2.592</v>
+      </c>
+      <c r="K78" s="9" t="n">
+        <v>2.476</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="14" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0345</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SUNLOGY</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>-0.0111</v>
+      </c>
+      <c r="F79" s="11" t="n">
+        <v>1802100</v>
+      </c>
+      <c r="G79" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H79" t="n">
+        <v>52.86</v>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="K79" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="14" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0450</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>MFGROUP</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E80" s="16" t="n">
+        <v>0.0196</v>
+      </c>
+      <c r="F80" s="11" t="n">
+        <v>1702900</v>
+      </c>
+      <c r="G80" s="12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H80" t="n">
+        <v>45.51</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="K80" s="9" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="14" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>0.0223</v>
+      </c>
+      <c r="F81" s="11" t="n">
+        <v>1692900</v>
+      </c>
+      <c r="G81" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H81" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="n">
+        <v>4.611</v>
+      </c>
+      <c r="K81" s="9" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="14" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>5145</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SEALINK</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="E82" s="16" t="n">
+        <v>0.0308</v>
+      </c>
+      <c r="F82" s="11" t="n">
+        <v>1678000</v>
+      </c>
+      <c r="G82" s="12" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H82" t="n">
+        <v>70.29000000000001</v>
+      </c>
+      <c r="I82" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="K82" s="9" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="14" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>5205</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SENDAI</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>-0.0175</v>
+      </c>
+      <c r="F83" s="11" t="n">
+        <v>1658800</v>
+      </c>
+      <c r="G83" s="12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H83" t="n">
+        <v>62.61</v>
+      </c>
+      <c r="I83" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="K83" s="9" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="14" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E84" s="16" t="n">
+        <v>0.0336</v>
+      </c>
+      <c r="F84" s="11" t="n">
+        <v>1645900</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H84" t="n">
+        <v>78.39</v>
+      </c>
+      <c r="I84" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="n">
+        <v>0.544</v>
+      </c>
+      <c r="K84" s="9" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="14" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0104</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>GENETEC</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>-0.0154</v>
+      </c>
+      <c r="F85" s="11" t="n">
+        <v>1575300</v>
+      </c>
+      <c r="G85" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H85" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="I85" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="K85" s="9" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="14" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="F86" s="11" t="n">
+        <v>1479200</v>
+      </c>
+      <c r="G86" s="12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H86" t="n">
+        <v>78.41</v>
+      </c>
+      <c r="I86" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J86" s="9" t="n">
+        <v>2.096</v>
+      </c>
+      <c r="K86" s="9" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="14" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>9075</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>THETA</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E87" s="16" t="n">
+        <v>0.0469</v>
+      </c>
+      <c r="F87" s="11" t="n">
+        <v>1440200</v>
+      </c>
+      <c r="G87" s="12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H87" t="n">
+        <v>52.84</v>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="K87" s="9" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" s="14" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>-0.0138</v>
+      </c>
+      <c r="F88" s="11" t="n">
+        <v>1384300</v>
+      </c>
+      <c r="G88" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H88" t="n">
+        <v>67.64</v>
+      </c>
+      <c r="I88" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J88" s="9" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K88" s="9" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" s="14" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="E89" s="16" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="F89" s="11" t="n">
+        <v>1345300</v>
+      </c>
+      <c r="G89" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H89" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="I89" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J89" s="9" t="n">
+        <v>13.546</v>
+      </c>
+      <c r="K89" s="9" t="n">
+        <v>14.106</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" s="14" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>5336</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>CKI</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>-0.0395</v>
+      </c>
+      <c r="F90" s="11" t="n">
+        <v>1338800</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H90" t="n">
+        <v>33.95</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J90" s="9" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="K90" s="9" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" s="14" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0032</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>REDTONE</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>-0.0132</v>
+      </c>
+      <c r="F91" s="11" t="n">
+        <v>1323400</v>
+      </c>
+      <c r="G91" s="12" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H91" t="n">
+        <v>73.53</v>
+      </c>
+      <c r="I91" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J91" s="9" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="K91" s="9" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" s="14" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0262</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SUNVIEW</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E92" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="11" t="n">
+        <v>1320800</v>
+      </c>
+      <c r="G92" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H92" t="n">
+        <v>50.08</v>
+      </c>
+      <c r="I92" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J92" s="9" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K92" s="9" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" s="14" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="E93" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="11" t="n">
+        <v>1310700</v>
+      </c>
+      <c r="G93" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H93" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="I93" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="K93" s="9" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" s="14" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E94" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="11" t="n">
+        <v>1225800</v>
+      </c>
+      <c r="G94" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H94" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="n">
+        <v>1.233</v>
+      </c>
+      <c r="K94" s="9" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" s="14" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="F95" s="11" t="n">
+        <v>1224600</v>
+      </c>
+      <c r="G95" s="12" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H95" t="n">
+        <v>41.29</v>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="n">
+        <v>1.473</v>
+      </c>
+      <c r="K95" s="9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" s="14" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0285</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>MERSEC</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="E96" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="11" t="n">
+        <v>1171400</v>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H96" t="n">
+        <v>43.77</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="K96" s="9" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" s="14" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0272</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>TTVHB</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="E97" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="11" t="n">
+        <v>1163700</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H97" t="n">
+        <v>51.46</v>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K97" s="9" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="14" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>-0.0077</v>
+      </c>
+      <c r="F98" s="11" t="n">
+        <v>1154400</v>
+      </c>
+      <c r="G98" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H98" t="n">
+        <v>66.18000000000001</v>
+      </c>
+      <c r="I98" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J98" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K98" s="9" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="14" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>-0.0254</v>
+      </c>
+      <c r="F99" s="11" t="n">
+        <v>1145800</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H99" t="n">
+        <v>40.37</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="K99" s="9" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="14" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0128</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>FRONTKN</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="F100" s="11" t="n">
+        <v>1105100</v>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H100" t="n">
+        <v>49.07</v>
+      </c>
+      <c r="I100" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>4.976</v>
+      </c>
+      <c r="K100" s="9" t="n">
+        <v>5.032</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="14" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0457</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>PENTECH</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="E101" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="11" t="n">
+        <v>1051400</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H101" t="n">
+        <v>54.93</v>
+      </c>
+      <c r="I101" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="K101" s="9" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="14" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>7225</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="E102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="11" t="n">
+        <v>1041500</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H102" t="n">
+        <v>51.39</v>
+      </c>
+      <c r="I102" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="K102" s="9" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="14" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>PBBANK</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="F103" s="11" t="n">
+        <v>1019900</v>
+      </c>
+      <c r="G103" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H103" t="n">
+        <v>42.95</v>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>4.857</v>
+      </c>
+      <c r="K103" s="9" t="n">
+        <v>4.973</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="14" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E104" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>1017800</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H104" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="I104" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J104" s="9" t="n">
+        <v>1.335</v>
+      </c>
+      <c r="K104" s="9" t="n">
+        <v>1.459</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="14" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="E105" s="16" t="n">
+        <v>0.005699999999999999</v>
+      </c>
+      <c r="F105" s="11" t="n">
+        <v>1009900</v>
+      </c>
+      <c r="G105" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H105" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="K105" s="9" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="14" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="E106" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>1007900</v>
+      </c>
+      <c r="G106" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H106" t="n">
+        <v>56.38</v>
+      </c>
+      <c r="I106" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K106" s="9" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="14" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>-0.0114</v>
+      </c>
+      <c r="F107" s="11" t="n">
+        <v>996300</v>
+      </c>
+      <c r="G107" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H107" t="n">
+        <v>33.64</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J107" s="9" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K107" s="9" t="n">
+        <v>2.802</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="14" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>-0.0153</v>
+      </c>
+      <c r="F108" s="11" t="n">
+        <v>994200</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H108" t="n">
+        <v>52</v>
+      </c>
+      <c r="I108" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="n">
+        <v>2.567</v>
+      </c>
+      <c r="K108" s="9" t="n">
+        <v>2.529</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="14" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>6888</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>AXIATA</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>-0.0059</v>
+      </c>
+      <c r="F109" s="11" t="n">
+        <v>969300</v>
+      </c>
+      <c r="G109" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H109" t="n">
+        <v>34.87</v>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="n">
+        <v>1.753</v>
+      </c>
+      <c r="K109" s="9" t="n">
+        <v>1.864</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="14" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>-0.0051</v>
+      </c>
+      <c r="F110" s="11" t="n">
+        <v>967700</v>
+      </c>
+      <c r="G110" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H110" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="I110" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J110" s="9" t="n">
+        <v>1.987</v>
+      </c>
+      <c r="K110" s="9" t="n">
+        <v>1.977</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="14" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E111" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="11" t="n">
+        <v>946600</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H111" t="n">
+        <v>34.81</v>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="n">
+        <v>1.127</v>
+      </c>
+      <c r="K111" s="9" t="n">
+        <v>1.155</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="14" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>-0.0261</v>
+      </c>
+      <c r="F112" s="11" t="n">
+        <v>892000</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H112" t="n">
+        <v>72.06999999999999</v>
+      </c>
+      <c r="I112" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="K112" s="9" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="14" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>BMGREEN</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="E113" s="16" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="F113" s="11" t="n">
+        <v>845600</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H113" t="n">
+        <v>58.75</v>
+      </c>
+      <c r="I113" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J113" s="9" t="n">
+        <v>1.646</v>
+      </c>
+      <c r="K113" s="9" t="n">
+        <v>1.729</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="14" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="E114" s="16" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>840400</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H114" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="I114" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="K114" s="9" t="n">
+        <v>2.094</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="14" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="F115" s="11" t="n">
+        <v>836600</v>
+      </c>
+      <c r="G115" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H115" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="I115" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J115" s="9" t="n">
+        <v>3.407</v>
+      </c>
+      <c r="K115" s="9" t="n">
+        <v>3.178</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="14" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="E116" s="16" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="F116" s="11" t="n">
+        <v>807000</v>
+      </c>
+      <c r="G116" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H116" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="I116" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="n">
+        <v>3.697</v>
+      </c>
+      <c r="K116" s="9" t="n">
+        <v>3.352</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="14" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>-0.0165</v>
+      </c>
+      <c r="F117" s="11" t="n">
+        <v>740900</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H117" t="n">
+        <v>57.39</v>
+      </c>
+      <c r="I117" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="K117" s="9" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="14" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>-0.0105</v>
+      </c>
+      <c r="F118" s="11" t="n">
+        <v>731900</v>
+      </c>
+      <c r="G118" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H118" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="n">
+        <v>1.972</v>
+      </c>
+      <c r="K118" s="9" t="n">
+        <v>2.091</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="14" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E119" s="16" t="n">
+        <v>0.009300000000000001</v>
+      </c>
+      <c r="F119" s="11" t="n">
+        <v>729100</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H119" t="n">
+        <v>63.07</v>
+      </c>
+      <c r="I119" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J119" s="9" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="K119" s="9" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="14" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>-0.0168</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>708700</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H120" t="n">
+        <v>67.22</v>
+      </c>
+      <c r="I120" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="K120" s="9" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="14" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E121" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>689500</v>
+      </c>
+      <c r="G121" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H121" t="n">
+        <v>78.48</v>
+      </c>
+      <c r="I121" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="K121" s="9" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="14" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>0293</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>KJTS</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E122" s="16" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>684900</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H122" t="n">
+        <v>56.47</v>
+      </c>
+      <c r="I122" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J122" s="9" t="n">
+        <v>1.029</v>
+      </c>
+      <c r="K122" s="9" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="14" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="E123" s="16" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="F123" s="11" t="n">
+        <v>659100</v>
+      </c>
+      <c r="G123" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H123" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="I123" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="n">
+        <v>2.398</v>
+      </c>
+      <c r="K123" s="9" t="n">
+        <v>2.073</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="14" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="E124" s="16" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="F124" s="11" t="n">
+        <v>653700</v>
+      </c>
+      <c r="G124" s="12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H124" t="n">
+        <v>53.68</v>
+      </c>
+      <c r="I124" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="K124" s="9" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="14" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="F125" s="11" t="n">
+        <v>639600</v>
+      </c>
+      <c r="G125" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H125" t="n">
+        <v>39.73</v>
+      </c>
+      <c r="I125" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J125" s="9" t="n">
+        <v>4.753</v>
+      </c>
+      <c r="K125" s="9" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="14" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E126" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="11" t="n">
+        <v>637700</v>
+      </c>
+      <c r="G126" s="12" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H126" t="n">
+        <v>46.81</v>
+      </c>
+      <c r="I126" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J126" s="9" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="K126" s="9" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="14" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>PMETAL</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>-0.0053</v>
+      </c>
+      <c r="F127" s="11" t="n">
+        <v>632900</v>
+      </c>
+      <c r="G127" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H127" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="I127" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J127" s="9" t="n">
+        <v>7.743</v>
+      </c>
+      <c r="K127" s="9" t="n">
+        <v>7.867</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="14" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>-0.0166</v>
+      </c>
+      <c r="F128" s="11" t="n">
+        <v>630700</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H128" t="n">
+        <v>50.06</v>
+      </c>
+      <c r="I128" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J128" s="9" t="n">
+        <v>1.774</v>
+      </c>
+      <c r="K128" s="9" t="n">
+        <v>1.811</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="14" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>6459</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>MNRB</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E129" s="16" t="n">
+        <v>0.0389</v>
+      </c>
+      <c r="F129" s="11" t="n">
+        <v>630500</v>
+      </c>
+      <c r="G129" s="12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="H129" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="I129" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="n">
+        <v>2.868</v>
+      </c>
+      <c r="K129" s="9" t="n">
+        <v>2.857</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="14" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>5308</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>SENFONG</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E130" s="10" t="n">
+        <v>-0.0073</v>
+      </c>
+      <c r="F130" s="11" t="n">
+        <v>595100</v>
+      </c>
+      <c r="G130" s="12" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="H130" t="n">
+        <v>42.76</v>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="K130" s="9" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="14" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>5121</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>HEKTAR</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="E131" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>592200</v>
+      </c>
+      <c r="G131" s="12" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H131" t="n">
+        <v>66.69</v>
+      </c>
+      <c r="I131" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K131" s="9" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="14" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>-0.0129</v>
+      </c>
+      <c r="F132" s="11" t="n">
+        <v>578300</v>
+      </c>
+      <c r="G132" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H132" t="n">
+        <v>71.63</v>
+      </c>
+      <c r="I132" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="K132" s="9" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="14" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>-0.006500000000000001</v>
+      </c>
+      <c r="F133" s="11" t="n">
+        <v>568600</v>
+      </c>
+      <c r="G133" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H133" t="n">
+        <v>56.23</v>
+      </c>
+      <c r="I133" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J133" s="9" t="n">
+        <v>3.021</v>
+      </c>
+      <c r="K133" s="9" t="n">
+        <v>3.042</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="14" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>-0.0066</v>
+      </c>
+      <c r="F134" s="11" t="n">
+        <v>568200</v>
+      </c>
+      <c r="G134" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H134" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="I134" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="n">
+        <v>1.573</v>
+      </c>
+      <c r="K134" s="9" t="n">
+        <v>1.688</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="14" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>-0.0206</v>
+      </c>
+      <c r="F135" s="11" t="n">
+        <v>562100</v>
+      </c>
+      <c r="G135" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H135" t="n">
+        <v>62.48</v>
+      </c>
+      <c r="I135" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J135" s="9" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="K135" s="9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="14" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>-0.0217</v>
+      </c>
+      <c r="F136" s="11" t="n">
+        <v>555400</v>
+      </c>
+      <c r="G136" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H136" t="n">
+        <v>56.02</v>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="n">
+        <v>1.334</v>
+      </c>
+      <c r="K136" s="9" t="n">
+        <v>1.128</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="14" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E137" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="11" t="n">
+        <v>546600</v>
+      </c>
+      <c r="G137" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H137" t="n">
+        <v>50.51</v>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="K137" s="9" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="14" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E138" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="11" t="n">
+        <v>537900</v>
+      </c>
+      <c r="G138" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H138" t="n">
+        <v>85.41</v>
+      </c>
+      <c r="I138" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="n">
+        <v>2.021</v>
+      </c>
+      <c r="K138" s="9" t="n">
+        <v>1.706</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="14" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>-0.0059</v>
+      </c>
+      <c r="F139" s="11" t="n">
+        <v>537500</v>
+      </c>
+      <c r="G139" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H139" t="n">
+        <v>64.31999999999999</v>
+      </c>
+      <c r="I139" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J139" s="9" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="K139" s="9" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="14" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>UNISEM</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>-0.0295</v>
+      </c>
+      <c r="F140" s="11" t="n">
+        <v>523300</v>
+      </c>
+      <c r="G140" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H140" t="n">
+        <v>58.31</v>
+      </c>
+      <c r="I140" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="n">
+        <v>4.392</v>
+      </c>
+      <c r="K140" s="9" t="n">
+        <v>4.429</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="14" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="F141" s="11" t="n">
+        <v>511600</v>
+      </c>
+      <c r="G141" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H141" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="I141" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J141" s="9" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="K141" s="9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="14" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>IHH</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="E142" s="16" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="F142" s="11" t="n">
+        <v>508100</v>
+      </c>
+      <c r="G142" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H142" t="n">
+        <v>54.04</v>
+      </c>
+      <c r="I142" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="n">
+        <v>7.935</v>
+      </c>
+      <c r="K142" s="9" t="n">
+        <v>8.173999999999999</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="14" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>KERJAYA</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="E143" s="16" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>507700</v>
+      </c>
+      <c r="G143" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H143" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J143" s="9" t="n">
+        <v>3.246</v>
+      </c>
+      <c r="K143" s="9" t="n">
+        <v>2.836</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M6"/>
+  <autoFilter ref="A1:M143"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-24/bursa-report-2026-09-24.xlsx
+++ b/docs/downloads/2026-09-24/bursa-report-2026-09-24.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-24" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-24'!$A$1:$M$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-24'!$A$1:$M$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M143"/>
+  <dimension ref="A1:M175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0476</v>
+        <v>0.0571</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1861400</v>
+        <v>3265400</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.43</v>
+        <v>0.76</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>83.77</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.946</v>
+        <v>0.947</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.78</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价RM1.1高于50日均线RM0.78约41%，EMA20与SAR均呈多头，但RSI达83.77，处超买区，信号可靠性受高位回调风险制约。</t>
+          <t>RSI达84.29，处超买区间；现价1.11远高于50日均线0.78，EMA20与SAR多头信号虽成立，但短线过热。</t>
         </is>
       </c>
     </row>
@@ -625,10 +625,10 @@
         <v>-0.0541</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>167952300</v>
+        <v>204714100</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.28</v>
+        <v>0.35</v>
       </c>
       <c r="H3" t="n">
         <v>20.58</v>
@@ -664,19 +664,19 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.24</v>
+        <v>0.245</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>30228200</v>
+        <v>32551100</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="H4" t="n">
-        <v>56.77</v>
+        <v>60.73</v>
       </c>
       <c r="I4" s="15" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.231</v>
+        <v>0.232</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>0.233</v>
@@ -700,28 +700,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CFM</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.095</v>
+        <v>0.3</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>0.0556</v>
+        <v>0.1321</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>23678800</v>
+        <v>29927500</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>44.03</v>
+        <v>2.18</v>
       </c>
       <c r="H5" t="n">
-        <v>81.81</v>
+        <v>60.15</v>
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.075</v>
+        <v>0.275</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.274</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -745,28 +745,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>CFM</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.485</v>
+        <v>0.095</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>0.0211</v>
+        <v>0.0556</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>18700900</v>
+        <v>24990500</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.76</v>
+        <v>46.47</v>
       </c>
       <c r="H6" t="n">
-        <v>56.56</v>
+        <v>81.81</v>
       </c>
       <c r="I6" s="15" t="inlineStr">
         <is>
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.468</v>
+        <v>0.075</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.47</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -790,39 +790,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.23</v>
+        <v>0.59</v>
       </c>
       <c r="E7" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>16928200</v>
+        <v>23904800</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.86</v>
+        <v>1.04</v>
       </c>
       <c r="H7" t="n">
-        <v>37.55</v>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.95</v>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.243</v>
+        <v>0.538</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.25</v>
+        <v>0.489</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -835,28 +835,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.595</v>
+        <v>0.485</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0211</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>16721500</v>
+        <v>23775400</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.72</v>
+        <v>0.97</v>
       </c>
       <c r="H8" t="n">
-        <v>76.81</v>
+        <v>56.56</v>
       </c>
       <c r="I8" s="15" t="inlineStr">
         <is>
@@ -864,10 +864,10 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.539</v>
+        <v>0.468</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.489</v>
+        <v>0.47</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>-0.0188</v>
+        <v>-0.0141</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>15987700</v>
+        <v>21473200</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="H9" t="n">
-        <v>46.56</v>
+        <v>47.59</v>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2.137</v>
+        <v>2.138</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>2.056</v>
@@ -925,39 +925,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.42</v>
+        <v>0.17</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>0.0633</v>
+        <v>0.0303</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>14961600</v>
+        <v>18482900</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.66</v>
+        <v>0.4</v>
       </c>
       <c r="H10" t="n">
-        <v>64.29000000000001</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.19</v>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.377</v>
+        <v>0.14</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.315</v>
+        <v>0.113</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -970,39 +970,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.785</v>
+        <v>0.425</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>0.0195</v>
+        <v>0.0759</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>14631000</v>
+        <v>18004000</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.35</v>
+        <v>0.8</v>
       </c>
       <c r="H11" t="n">
-        <v>64.20999999999999</v>
-      </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.12</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.735</v>
+        <v>0.377</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.68</v>
+        <v>0.315</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1015,39 +1015,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>0</v>
+        <v>0.535</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>-0.0183</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>14419000</v>
+        <v>17292300</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.31</v>
+        <v>0.44</v>
       </c>
       <c r="H12" t="n">
-        <v>71.51000000000001</v>
-      </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.62</v>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.139</v>
+        <v>0.658</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.113</v>
+        <v>0.875</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1060,28 +1060,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>-0.0275</v>
+        <v>0.23</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>13813100</v>
+        <v>17260200</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.35</v>
+        <v>0.88</v>
       </c>
       <c r="H13" t="n">
-        <v>26.29</v>
+        <v>37.55</v>
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.658</v>
+        <v>0.243</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.875</v>
+        <v>0.25</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1120,10 +1120,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>13309200</v>
+        <v>16739200</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.71</v>
+        <v>0.89</v>
       </c>
       <c r="H14" t="n">
         <v>62.58</v>
@@ -1150,28 +1150,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.23</v>
+        <v>0.795</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0.0222</v>
+        <v>0.0325</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>12144100</v>
+        <v>16595300</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.6</v>
+        <v>0.39</v>
       </c>
       <c r="H15" t="n">
-        <v>85.45</v>
+        <v>65.66</v>
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.198</v>
+        <v>0.736</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.182</v>
+        <v>0.68</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1195,28 +1195,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.28</v>
+        <v>0.23</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>0.0566</v>
+        <v>0.0222</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>10760400</v>
+        <v>13470600</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="H16" t="n">
-        <v>53.44</v>
+        <v>85.45</v>
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.273</v>
+        <v>0.198</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.273</v>
+        <v>0.182</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1249,19 +1249,19 @@
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.405</v>
+        <v>0.41</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>0.0946</v>
+        <v>0.1081</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>10553500</v>
+        <v>11601500</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>14.07</v>
+        <v>15.47</v>
       </c>
       <c r="H17" t="n">
-        <v>72.56</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="I17" s="15" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>0.364</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.332</v>
+        <v>0.333</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1285,39 +1285,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0163</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CAREPLS</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>0.0588</v>
+        <v>0.77</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>10523700</v>
+        <v>11159700</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>1.3</v>
+        <v>0.93</v>
       </c>
       <c r="H18" t="n">
-        <v>67.23</v>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.7</v>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.082</v>
+        <v>0.774</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.076</v>
+        <v>0.774</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1330,28 +1330,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0182</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LKL</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>0.1429</v>
+        <v>0.805</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>-0.0123</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>10105100</v>
+        <v>10978500</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>95.98999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="H19" t="n">
-        <v>63.02</v>
+        <v>46.93</v>
       </c>
       <c r="I19" s="15" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.034</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.034</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1375,39 +1375,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0163</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>CAREPLS</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.4</v>
+        <v>0.09</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>0.0127</v>
+        <v>0.0588</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>8927200</v>
+        <v>10674500</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.18</v>
+        <v>1.32</v>
       </c>
       <c r="H20" t="n">
-        <v>85.84999999999999</v>
-      </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>67.23</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.305</v>
+        <v>0.082</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.171</v>
+        <v>0.076</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1420,39 +1420,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0034</t>
+          <t>0182</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MMAG</t>
+          <t>LKL</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.025</v>
+        <v>0.035</v>
       </c>
       <c r="E21" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>8738100</v>
+        <v>10324900</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>3.9</v>
+        <v>98.08</v>
       </c>
       <c r="H21" t="n">
-        <v>49.97</v>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.98</v>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.025</v>
+        <v>0.034</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.027</v>
+        <v>0.034</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1465,28 +1465,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0007</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PUC</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>0</v>
+        <v>1.8</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>-0.0164</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>8603400</v>
+        <v>9912800</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1.11</v>
+        <v>0.29</v>
       </c>
       <c r="H22" t="n">
-        <v>56.29</v>
+        <v>62.18</v>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.032</v>
+        <v>1.714</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.033</v>
+        <v>1.493</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1510,39 +1510,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0007</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>PUC</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.035</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>8510600</v>
+        <v>9703400</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.47</v>
+        <v>1.25</v>
       </c>
       <c r="H23" t="n">
-        <v>61.39</v>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.29</v>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>4.71</v>
+        <v>0.032</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>4.482</v>
+        <v>0.033</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1555,39 +1555,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.605</v>
+        <v>0.4</v>
       </c>
       <c r="E24" s="16" t="n">
-        <v>0.0083</v>
+        <v>0.0127</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>7973800</v>
+        <v>9328100</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.84</v>
+        <v>0.19</v>
       </c>
       <c r="H24" t="n">
-        <v>47.43</v>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>85.84999999999999</v>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.609</v>
+        <v>0.305</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.603</v>
+        <v>0.171</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1600,39 +1600,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>-0.0219</v>
+        <v>4.82</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>0.008399999999999999</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>7718600</v>
+        <v>9312200</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.23</v>
+        <v>0.52</v>
       </c>
       <c r="H25" t="n">
-        <v>61.15</v>
-      </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.39</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1.713</v>
+        <v>4.71</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>1.493</v>
+        <v>4.482</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1645,28 +1645,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>-0.006500000000000001</v>
+        <v>0.165</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7684000</v>
+        <v>9146800</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.64</v>
+        <v>0.22</v>
       </c>
       <c r="H26" t="n">
-        <v>47.7</v>
+        <v>53.7</v>
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.774</v>
+        <v>0.16</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.774</v>
+        <v>0.149</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1690,39 +1690,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0034</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>MMAG</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>-0.0169</v>
+        <v>0.025</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>7408100</v>
+        <v>8888200</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>1.26</v>
+        <v>3.97</v>
       </c>
       <c r="H27" t="n">
-        <v>64.13</v>
-      </c>
-      <c r="I27" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.97</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.27</v>
+        <v>0.025</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.268</v>
+        <v>0.027</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1735,28 +1735,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.775</v>
+        <v>0.29</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>-0.0252</v>
+        <v>-0.0169</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>7389000</v>
+        <v>8191900</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.98</v>
+        <v>1.39</v>
       </c>
       <c r="H28" t="n">
-        <v>65.91</v>
+        <v>64.13</v>
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.681</v>
+        <v>0.268</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1780,28 +1780,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>0.0303</v>
+        <v>0.6</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>7084700</v>
+        <v>8103900</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.24</v>
+        <v>0.85</v>
       </c>
       <c r="H29" t="n">
-        <v>37.08</v>
+        <v>44.4</v>
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.186</v>
+        <v>0.609</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.228</v>
+        <v>0.603</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1825,28 +1825,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.16</v>
+        <v>0.775</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>-0.0303</v>
+        <v>-0.0252</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>6270100</v>
+        <v>8060800</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.15</v>
+        <v>1.07</v>
       </c>
       <c r="H30" t="n">
-        <v>51.62</v>
+        <v>65.91</v>
       </c>
       <c r="I30" s="15" t="inlineStr">
         <is>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.16</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.148</v>
+        <v>0.681</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1870,28 +1870,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FSBM</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E31" s="17" t="n">
-        <v>0</v>
+        <v>1.9</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>0.0106</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>5849200</v>
+        <v>7998000</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.22</v>
+        <v>1.45</v>
       </c>
       <c r="H31" t="n">
-        <v>39.23</v>
+        <v>45.5</v>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.141</v>
+        <v>1.924</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.165</v>
+        <v>1.973</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1915,28 +1915,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>1.14</v>
+        <v>0.375</v>
       </c>
       <c r="E32" s="16" t="n">
-        <v>0.0179</v>
+        <v>0.0274</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>5583700</v>
+        <v>7822200</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.5</v>
+        <v>1.38</v>
       </c>
       <c r="H32" t="n">
-        <v>62.25</v>
+        <v>56.64</v>
       </c>
       <c r="I32" s="15" t="inlineStr">
         <is>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>1.083</v>
+        <v>0.367</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>1.02</v>
+        <v>0.366</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1960,39 +1960,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TEKSENG</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>0.0526</v>
+        <v>0.865</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>5468500</v>
+        <v>7803200</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>26.6</v>
+        <v>0.44</v>
       </c>
       <c r="H33" t="n">
-        <v>79.06999999999999</v>
-      </c>
-      <c r="I33" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.39</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.251</v>
+        <v>0.868</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.238</v>
+        <v>0.871</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2005,39 +2005,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>FSBM</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>-0.0206</v>
+        <v>0.125</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>0.0417</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>5384900</v>
+        <v>7422100</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="H34" t="n">
-        <v>54.07</v>
-      </c>
-      <c r="I34" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.29</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>2.347</v>
+        <v>0.142</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>2.225</v>
+        <v>0.165</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2050,28 +2050,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.8149999999999999</v>
+        <v>1.57</v>
       </c>
       <c r="E35" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>5365900</v>
+        <v>7346000</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.43</v>
+        <v>3.44</v>
       </c>
       <c r="H35" t="n">
-        <v>52.62</v>
+        <v>42.33</v>
       </c>
       <c r="I35" s="15" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.8120000000000001</v>
+        <v>1.592</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.8090000000000001</v>
+        <v>1.654</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2095,39 +2095,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>-0.0345</v>
+        <v>0.165</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>5190600</v>
+        <v>7176100</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.85</v>
+        <v>0.25</v>
       </c>
       <c r="H36" t="n">
-        <v>56.96</v>
-      </c>
-      <c r="I36" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.18</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.398</v>
+        <v>0.185</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.397</v>
+        <v>0.228</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2140,28 +2140,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0055</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SERSOL</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.04</v>
+        <v>2.37</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>-0.2</v>
+        <v>-0.0247</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>5155000</v>
+        <v>6931000</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>1.62</v>
+        <v>0.35</v>
       </c>
       <c r="H37" t="n">
-        <v>52.2</v>
+        <v>53.27</v>
       </c>
       <c r="I37" s="15" t="inlineStr">
         <is>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.04</v>
+        <v>2.346</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.034</v>
+        <v>2.224</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2185,39 +2185,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E38" s="17" t="n">
-        <v>0</v>
+        <v>1.14</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>0.0179</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>5018400</v>
+        <v>6795900</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.28</v>
+        <v>0.6</v>
       </c>
       <c r="H38" t="n">
-        <v>45.39</v>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.25</v>
+      </c>
+      <c r="I38" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.868</v>
+        <v>1.083</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.871</v>
+        <v>1.02</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2230,39 +2230,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.375</v>
+        <v>4.8</v>
       </c>
       <c r="E39" s="16" t="n">
-        <v>0.0274</v>
+        <v>0.0042</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>4470200</v>
+        <v>6643300</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="H39" t="n">
-        <v>56.64</v>
-      </c>
-      <c r="I39" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.16</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.367</v>
+        <v>4.745</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.366</v>
+        <v>4.579</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2275,28 +2275,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>TEKSENG</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>4.54</v>
+        <v>0.305</v>
       </c>
       <c r="E40" s="16" t="n">
-        <v>0.0157</v>
+        <v>0.0702</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>4458200</v>
+        <v>6598800</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.38</v>
+        <v>32.09</v>
       </c>
       <c r="H40" t="n">
-        <v>86.17</v>
+        <v>80.11</v>
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>3.333</v>
+        <v>0.252</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>2.232</v>
+        <v>0.238</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2320,28 +2320,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LBALUM</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.49</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>0.0208</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>3911400</v>
+        <v>5983800</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>12.79</v>
+        <v>0.4</v>
       </c>
       <c r="H41" t="n">
-        <v>66.51000000000001</v>
+        <v>73.17</v>
       </c>
       <c r="I41" s="15" t="inlineStr">
         <is>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.478</v>
+        <v>0.462</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.471</v>
+        <v>0.394</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2365,28 +2365,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0055</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>SERSOL</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>0.0069</v>
+        <v>0.04</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>-0.2</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>3907500</v>
+        <v>5821700</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.31</v>
+        <v>1.83</v>
       </c>
       <c r="H42" t="n">
-        <v>64.84999999999999</v>
+        <v>52.2</v>
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>2.826</v>
+        <v>0.04</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>2.687</v>
+        <v>0.034</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2410,28 +2410,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>-0.0405</v>
+        <v>0.78</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>0.013</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>3820100</v>
+        <v>5563700</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>65.3</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.332</v>
+        <v>0.764</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.317</v>
+        <v>0.749</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2455,39 +2455,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>-0.0267</v>
+        <v>4.47</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>3802400</v>
+        <v>5542900</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="H44" t="n">
-        <v>38.42</v>
-      </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.379</v>
+        <v>3.326</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.392</v>
+        <v>2.23</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2500,28 +2500,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1.01</v>
+        <v>0.415</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>-0.0098</v>
+        <v>-0.046</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>3477500</v>
+        <v>5469900</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="H45" t="n">
-        <v>79.65000000000001</v>
+        <v>55.46</v>
       </c>
       <c r="I45" s="15" t="inlineStr">
         <is>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.852</v>
+        <v>0.397</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.744</v>
+        <v>0.397</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2545,28 +2545,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>7.9</v>
+        <v>0.805</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>-0.0038</v>
+        <v>-0.0062</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>3476000</v>
+        <v>5295600</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.26</v>
+        <v>1.69</v>
       </c>
       <c r="H46" t="n">
-        <v>58.63</v>
+        <v>49.77</v>
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>7.768</v>
+        <v>0.804</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>7.715</v>
+        <v>0.806</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2590,28 +2590,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1.38</v>
+        <v>7.92</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>-0.0417</v>
+        <v>-0.0013</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>3465500</v>
+        <v>5250100</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="H47" t="n">
-        <v>52.56</v>
+        <v>59.93</v>
       </c>
       <c r="I47" s="15" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>1.386</v>
+        <v>7.77</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>1.284</v>
+        <v>7.715</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2635,39 +2635,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="E48" s="17" t="n">
-        <v>0</v>
+        <v>2.93</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3458600</v>
+        <v>5042300</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.63</v>
+        <v>0.4</v>
       </c>
       <c r="H48" t="n">
-        <v>42.28</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.84999999999999</v>
+      </c>
+      <c r="I48" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>1.922</v>
+        <v>2.826</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>1.972</v>
+        <v>2.687</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2680,28 +2680,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="E49" s="16" t="n">
-        <v>0.013</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>3370800</v>
+        <v>5007900</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.61</v>
+        <v>1.41</v>
       </c>
       <c r="H49" t="n">
-        <v>83.98999999999999</v>
+        <v>68.48</v>
       </c>
       <c r="I49" s="15" t="inlineStr">
         <is>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.764</v>
+        <v>0.868</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.749</v>
+        <v>0.848</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2725,39 +2725,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>0.0042</v>
+        <v>1.39</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>-0.0347</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>3351100</v>
+        <v>4689500</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="H50" t="n">
-        <v>58.16</v>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.06</v>
+      </c>
+      <c r="I50" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>4.745</v>
+        <v>1.387</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>4.579</v>
+        <v>1.284</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2770,28 +2770,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.27</v>
+        <v>0.155</v>
       </c>
       <c r="E51" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>3256800</v>
+        <v>4330000</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="H51" t="n">
-        <v>43.1</v>
+        <v>44.71</v>
       </c>
       <c r="I51" s="15" t="inlineStr">
         <is>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.276</v>
+        <v>0.156</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.317</v>
+        <v>0.16</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2815,39 +2815,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>-0.0196</v>
+        <v>0.77</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>3111600</v>
+        <v>4210400</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.11</v>
+        <v>0.67</v>
       </c>
       <c r="H52" t="n">
-        <v>33.17</v>
-      </c>
-      <c r="I52" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.49</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.283</v>
+        <v>0.775</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.333</v>
+        <v>0.773</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2860,28 +2860,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.525</v>
+        <v>0.355</v>
       </c>
       <c r="E53" s="10" t="n">
-        <v>-0.009399999999999999</v>
+        <v>-0.0405</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>3021400</v>
+        <v>4166300</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.49</v>
+        <v>0.58</v>
       </c>
       <c r="H53" t="n">
-        <v>52.9</v>
+        <v>65.3</v>
       </c>
       <c r="I53" s="15" t="inlineStr">
         <is>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.518</v>
+        <v>0.332</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.529</v>
+        <v>0.317</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2905,28 +2905,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E54" s="16" t="n">
-        <v>0.025</v>
+        <v>5.84</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>-0.0118</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>2964100</v>
+        <v>4029400</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
       <c r="H54" t="n">
-        <v>63.73</v>
+        <v>62.62</v>
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>1.16</v>
+        <v>5.655</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>1.095</v>
+        <v>5.068</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2950,39 +2950,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>9326</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>LBALUM</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>-0.0242</v>
+        <v>0.495</v>
+      </c>
+      <c r="E55" s="16" t="n">
+        <v>0.0313</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>2944600</v>
+        <v>3952300</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.62</v>
+        <v>12.93</v>
       </c>
       <c r="H55" t="n">
-        <v>36.17</v>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70</v>
+      </c>
+      <c r="I55" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.644</v>
+        <v>0.479</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.659</v>
+        <v>0.471</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2995,39 +2995,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>-0.0092</v>
+        <v>1.03</v>
+      </c>
+      <c r="E56" s="16" t="n">
+        <v>0.0098</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>2927300</v>
+        <v>3923300</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="H56" t="n">
-        <v>35.04</v>
-      </c>
-      <c r="I56" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>82.59</v>
+      </c>
+      <c r="I56" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.854</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.594</v>
+        <v>0.744</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3040,39 +3040,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>2.67</v>
+        <v>0.54</v>
       </c>
       <c r="E57" s="10" t="n">
-        <v>-0.0074</v>
+        <v>-0.0092</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>2752400</v>
+        <v>3908500</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.24</v>
+        <v>0.58</v>
       </c>
       <c r="H57" t="n">
-        <v>45</v>
-      </c>
-      <c r="I57" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.04</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>2.68</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>2.893</v>
+        <v>0.594</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3085,39 +3085,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E58" s="16" t="n">
-        <v>0.01</v>
+        <v>0.605</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>-0.0242</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2646500</v>
+        <v>3897000</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="H58" t="n">
-        <v>81.36</v>
-      </c>
-      <c r="I58" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.17</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.439</v>
+        <v>0.644</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.399</v>
+        <v>0.659</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3130,28 +3130,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>-0.0118</v>
+        <v>1.23</v>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>0.025</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2620500</v>
+        <v>3885900</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.16</v>
+        <v>0.42</v>
       </c>
       <c r="H59" t="n">
-        <v>62.62</v>
+        <v>63.73</v>
       </c>
       <c r="I59" s="15" t="inlineStr">
         <is>
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>5.655</v>
+        <v>1.16</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>5.068</v>
+        <v>1.095</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3175,28 +3175,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0267</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.375</v>
+        <v>0.37</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>-0.0625</v>
+        <v>-0.0133</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2616700</v>
+        <v>3855600</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="H60" t="n">
-        <v>44.92</v>
+        <v>40.98</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.399</v>
+        <v>0.379</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.37</v>
+        <v>0.392</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3220,39 +3220,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.54</v>
+        <v>1.01</v>
       </c>
       <c r="E61" s="10" t="n">
-        <v>-0.0182</v>
+        <v>-0.0098</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>2589100</v>
+        <v>3797300</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.18</v>
+        <v>1.18</v>
       </c>
       <c r="H61" t="n">
-        <v>57.69</v>
-      </c>
-      <c r="I61" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>89.05</v>
+      </c>
+      <c r="I61" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.519</v>
+        <v>0.773</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.469</v>
+        <v>0.706</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3265,28 +3265,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.54</v>
+        <v>0.255</v>
       </c>
       <c r="E62" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2575800</v>
+        <v>3774500</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="H62" t="n">
-        <v>70.97</v>
+        <v>34.37</v>
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.46</v>
+        <v>0.284</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.393</v>
+        <v>0.333</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3310,28 +3310,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>1</v>
+        <v>0.265</v>
       </c>
       <c r="E63" s="10" t="n">
-        <v>-0.0196</v>
+        <v>-0.0185</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2528700</v>
+        <v>3753800</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.79</v>
+        <v>0.31</v>
       </c>
       <c r="H63" t="n">
-        <v>86.59999999999999</v>
+        <v>41.24</v>
       </c>
       <c r="I63" s="15" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.772</v>
+        <v>0.276</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.706</v>
+        <v>0.317</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3355,39 +3355,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E64" s="16" t="n">
-        <v>0.0175</v>
+        <v>0.405</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>-0.0357</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2501900</v>
+        <v>3615800</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="H64" t="n">
-        <v>39.08</v>
-      </c>
-      <c r="I64" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.41</v>
+      </c>
+      <c r="I64" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.3</v>
+        <v>0.406</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.313</v>
+        <v>0.409</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3400,28 +3400,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>MKLAND</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>-0.0284</v>
+        <v>0.165</v>
+      </c>
+      <c r="E65" s="16" t="n">
+        <v>0.1</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2417100</v>
+        <v>3569500</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.16</v>
+        <v>6.96</v>
       </c>
       <c r="H65" t="n">
-        <v>51.73</v>
+        <v>74.59</v>
       </c>
       <c r="I65" s="15" t="inlineStr">
         <is>
@@ -3429,10 +3429,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.677</v>
+        <v>0.146</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.658</v>
+        <v>0.144</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3445,39 +3445,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>10.12</v>
+        <v>0.535</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>-0.002</v>
+        <v>-0.0273</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2415600</v>
+        <v>3545300</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="H66" t="n">
-        <v>42.64</v>
-      </c>
-      <c r="I66" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.36</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>10.173</v>
+        <v>0.518</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>10.345</v>
+        <v>0.469</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3490,39 +3490,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E67" s="17" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2330700</v>
+        <v>3282200</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.61</v>
+        <v>0.22</v>
       </c>
       <c r="H67" t="n">
-        <v>30.81</v>
-      </c>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.68</v>
+      </c>
+      <c r="I67" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.802</v>
+        <v>0.678</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.855</v>
+        <v>0.659</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3535,39 +3535,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E68" s="17" t="n">
-        <v>0</v>
+        <v>0.525</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>2245400</v>
+        <v>3275000</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="H68" t="n">
-        <v>33.24</v>
-      </c>
-      <c r="I68" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.9</v>
+      </c>
+      <c r="I68" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>1.059</v>
+        <v>0.518</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>1.072</v>
+        <v>0.529</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3580,28 +3580,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>1.56</v>
+        <v>1.17</v>
       </c>
       <c r="E69" s="10" t="n">
-        <v>-0.0064</v>
+        <v>-0.0168</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2222600</v>
+        <v>3240500</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>1.04</v>
+        <v>0.43</v>
       </c>
       <c r="H69" t="n">
-        <v>40.66</v>
+        <v>48.92</v>
       </c>
       <c r="I69" s="15" t="inlineStr">
         <is>
@@ -3609,10 +3609,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>1.591</v>
+        <v>1.185</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>1.654</v>
+        <v>1.131</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3625,39 +3625,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E70" s="17" t="n">
-        <v>0</v>
+        <v>10.18</v>
+      </c>
+      <c r="E70" s="16" t="n">
+        <v>0.0039</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2142300</v>
+        <v>3192200</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.34</v>
+        <v>0.17</v>
       </c>
       <c r="H70" t="n">
-        <v>48.49</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.46</v>
+      </c>
+      <c r="I70" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.775</v>
+        <v>10.178</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.773</v>
+        <v>10.346</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3670,39 +3670,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0267</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E71" s="16" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.385</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>-0.0375</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2135600</v>
+        <v>3094200</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.6</v>
+        <v>0.97</v>
       </c>
       <c r="H71" t="n">
-        <v>68.48</v>
-      </c>
-      <c r="I71" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.36</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.868</v>
+        <v>0.4</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.848</v>
+        <v>0.37</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3715,28 +3715,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.655</v>
+        <v>2.67</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>-0.0224</v>
+        <v>-0.0074</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2037000</v>
+        <v>3020500</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="H72" t="n">
-        <v>59.56</v>
+        <v>45</v>
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.628</v>
+        <v>2.68</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.5679999999999999</v>
+        <v>2.893</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3760,28 +3760,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ENGTEX</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.455</v>
+        <v>0.505</v>
       </c>
       <c r="E73" s="16" t="n">
-        <v>0.0225</v>
+        <v>0.01</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1992500</v>
+        <v>2968100</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>2.1</v>
+        <v>0.98</v>
       </c>
       <c r="H73" t="n">
-        <v>60.62</v>
+        <v>81.36</v>
       </c>
       <c r="I73" s="15" t="inlineStr">
         <is>
@@ -3789,10 +3789,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.434</v>
+        <v>0.439</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.44</v>
+        <v>0.399</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3805,39 +3805,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>-0.0168</v>
+        <v>0.285</v>
+      </c>
+      <c r="E74" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1972400</v>
+        <v>2883900</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
       <c r="H74" t="n">
-        <v>48.92</v>
-      </c>
-      <c r="I74" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.99</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>1.185</v>
+        <v>0.299</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>1.131</v>
+        <v>0.313</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3850,28 +3850,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>2.66</v>
+        <v>2.05</v>
       </c>
       <c r="E75" s="10" t="n">
-        <v>-0.0075</v>
+        <v>-0.0144</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1924500</v>
+        <v>2609000</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.09</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H75" t="n">
-        <v>59.41</v>
+        <v>45.19</v>
       </c>
       <c r="I75" s="15" t="inlineStr">
         <is>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>2.589</v>
+        <v>2.069</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>2.425</v>
+        <v>2.113</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3895,28 +3895,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>ENGTEX</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E76" s="10" t="n">
-        <v>-0.0238</v>
+        <v>0.445</v>
+      </c>
+      <c r="E76" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1911000</v>
+        <v>2522600</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.17</v>
+        <v>2.65</v>
       </c>
       <c r="H76" t="n">
-        <v>52.95</v>
+        <v>56.42</v>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.407</v>
+        <v>0.433</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.409</v>
+        <v>0.44</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3940,28 +3940,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>2.05</v>
+        <v>0.66</v>
       </c>
       <c r="E77" s="10" t="n">
-        <v>-0.0144</v>
+        <v>-0.0149</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1838100</v>
+        <v>2429900</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.66</v>
+        <v>0.25</v>
       </c>
       <c r="H77" t="n">
-        <v>45.19</v>
+        <v>60.88</v>
       </c>
       <c r="I77" s="15" t="inlineStr">
         <is>
@@ -3969,10 +3969,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>2.069</v>
+        <v>0.629</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>2.113</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3985,28 +3985,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>PTT</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="E78" s="16" t="n">
-        <v>0.015</v>
+        <v>1.37</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>-0.09269999999999999</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1815100</v>
+        <v>2407900</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.3</v>
+        <v>13.19</v>
       </c>
       <c r="H78" t="n">
-        <v>62.02</v>
+        <v>40.54</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -4014,10 +4014,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>2.592</v>
+        <v>1.435</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>2.476</v>
+        <v>1.431</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4030,28 +4030,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>-0.0111</v>
+        <v>2.71</v>
+      </c>
+      <c r="E79" s="16" t="n">
+        <v>0.015</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1802100</v>
+        <v>2369000</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.23</v>
+        <v>0.39</v>
       </c>
       <c r="H79" t="n">
-        <v>52.86</v>
+        <v>62.02</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.444</v>
+        <v>2.592</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.4</v>
+        <v>2.476</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4075,28 +4075,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E80" s="16" t="n">
-        <v>0.0196</v>
+        <v>0.75</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>-0.0066</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1702900</v>
+        <v>2355700</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>2.39</v>
+        <v>0.62</v>
       </c>
       <c r="H80" t="n">
-        <v>45.51</v>
+        <v>29.9</v>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.262</v>
+        <v>0.801</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.267</v>
+        <v>0.855</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4120,28 +4120,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="E81" s="16" t="n">
-        <v>0.0223</v>
+        <v>1.01</v>
+      </c>
+      <c r="E81" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1692900</v>
+        <v>2322900</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.22</v>
+        <v>0.44</v>
       </c>
       <c r="H81" t="n">
-        <v>50.1</v>
+        <v>33.24</v>
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>4.611</v>
+        <v>1.059</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>4.54</v>
+        <v>1.072</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4165,28 +4165,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SEALINK</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.335</v>
+        <v>2.46</v>
       </c>
       <c r="E82" s="16" t="n">
-        <v>0.0308</v>
+        <v>0.025</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1678000</v>
+        <v>2174700</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>2.42</v>
+        <v>1.32</v>
       </c>
       <c r="H82" t="n">
-        <v>70.29000000000001</v>
+        <v>82.66</v>
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.315</v>
+        <v>2.103</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.308</v>
+        <v>1.905</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4210,28 +4210,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SENDAI</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.28</v>
+        <v>2.65</v>
       </c>
       <c r="E83" s="10" t="n">
-        <v>-0.0175</v>
+        <v>-0.0112</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1658800</v>
+        <v>2137100</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>1.07</v>
+        <v>0.1</v>
       </c>
       <c r="H83" t="n">
-        <v>62.61</v>
+        <v>58.44</v>
       </c>
       <c r="I83" s="15" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.254</v>
+        <v>2.588</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.271</v>
+        <v>2.425</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4255,28 +4255,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.615</v>
+        <v>0.55</v>
       </c>
       <c r="E84" s="16" t="n">
-        <v>0.0336</v>
+        <v>0.0092</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1645900</v>
+        <v>2134000</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>1.16</v>
+        <v>0.46</v>
       </c>
       <c r="H84" t="n">
-        <v>78.39</v>
+        <v>65.22</v>
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.544</v>
+        <v>0.511</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.485</v>
+        <v>0.459</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4300,28 +4300,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.32</v>
+        <v>13.12</v>
       </c>
       <c r="E85" s="10" t="n">
-        <v>-0.0154</v>
+        <v>-0.0015</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1575300</v>
+        <v>2129500</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="H85" t="n">
-        <v>46.33</v>
+        <v>26.72</v>
       </c>
       <c r="I85" s="15" t="inlineStr">
         <is>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.323</v>
+        <v>13.542</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.339</v>
+        <v>14.106</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4345,39 +4345,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E86" s="10" t="n">
-        <v>-0.0083</v>
+        <v>4.84</v>
+      </c>
+      <c r="E86" s="16" t="n">
+        <v>0.0021</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1479200</v>
+        <v>2098000</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="H86" t="n">
-        <v>78.41</v>
-      </c>
-      <c r="I86" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.37</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>2.096</v>
+        <v>4.858</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>1.904</v>
+        <v>4.973</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4390,28 +4390,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>THETA</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.67</v>
+        <v>4.59</v>
       </c>
       <c r="E87" s="16" t="n">
-        <v>0.0469</v>
+        <v>0.0223</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1440200</v>
+        <v>2070600</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>1.36</v>
+        <v>0.27</v>
       </c>
       <c r="H87" t="n">
-        <v>52.84</v>
+        <v>50.1</v>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.654</v>
+        <v>4.611</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.65</v>
+        <v>4.54</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4435,28 +4435,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>-0.0138</v>
+        <v>0.37</v>
+      </c>
+      <c r="E88" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1384300</v>
+        <v>2064400</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="H88" t="n">
-        <v>67.64</v>
+        <v>50.08</v>
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.66</v>
+        <v>0.37</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.606</v>
+        <v>0.37</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4480,28 +4480,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>13.16</v>
-      </c>
-      <c r="E89" s="16" t="n">
-        <v>0.0015</v>
+        <v>1.29</v>
+      </c>
+      <c r="E89" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1345300</v>
+        <v>1992700</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="H89" t="n">
-        <v>28.29</v>
+        <v>32.39</v>
       </c>
       <c r="I89" s="15" t="inlineStr">
         <is>
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>13.546</v>
+        <v>1.335</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>14.106</v>
+        <v>1.459</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4525,28 +4525,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CKI</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.365</v>
+        <v>0.445</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>-0.0395</v>
+        <v>-0.0111</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1338800</v>
+        <v>1990100</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="H90" t="n">
-        <v>33.95</v>
+        <v>52.86</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -4554,10 +4554,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.393</v>
+        <v>0.444</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.391</v>
+        <v>0.4</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4570,28 +4570,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0032</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>REDTONE</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.375</v>
+        <v>3.78</v>
       </c>
       <c r="E91" s="10" t="n">
-        <v>-0.0132</v>
+        <v>-0.0026</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1323400</v>
+        <v>1977000</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.84</v>
+        <v>0.47</v>
       </c>
       <c r="H91" t="n">
-        <v>73.53</v>
+        <v>71.75</v>
       </c>
       <c r="I91" s="15" t="inlineStr">
         <is>
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.352</v>
+        <v>3.407</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.317</v>
+        <v>3.178</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4615,28 +4615,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E92" s="17" t="n">
-        <v>0</v>
+        <v>1.76</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>-0.0276</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1320800</v>
+        <v>1961100</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="H92" t="n">
-        <v>50.08</v>
+        <v>47.72</v>
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.37</v>
+        <v>1.772</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.37</v>
+        <v>1.81</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4660,28 +4660,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E93" s="17" t="n">
-        <v>0</v>
+        <v>4.96</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>-0.004</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1310700</v>
+        <v>1931300</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.29</v>
+        <v>0.36</v>
       </c>
       <c r="H93" t="n">
-        <v>64.2</v>
+        <v>48.53</v>
       </c>
       <c r="I93" s="15" t="inlineStr">
         <is>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.511</v>
+        <v>4.975</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.459</v>
+        <v>5.032</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4705,39 +4705,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E94" s="17" t="n">
-        <v>0</v>
+        <v>0.615</v>
+      </c>
+      <c r="E94" s="16" t="n">
+        <v>0.0336</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1225800</v>
+        <v>1867300</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.29</v>
+        <v>1.31</v>
       </c>
       <c r="H94" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="I94" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.39</v>
+      </c>
+      <c r="I94" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>1.233</v>
+        <v>0.544</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>1.129</v>
+        <v>0.485</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4750,28 +4750,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E95" s="10" t="n">
-        <v>-0.0068</v>
+        <v>0.22</v>
+      </c>
+      <c r="E95" s="16" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1224600</v>
+        <v>1853800</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.46</v>
+        <v>0.25</v>
       </c>
       <c r="H95" t="n">
-        <v>41.29</v>
+        <v>54.19</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>1.473</v>
+        <v>0.214</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>1.54</v>
+        <v>0.211</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4795,39 +4795,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0285</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MERSEC</t>
+          <t>REDTONE</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E96" s="17" t="n">
-        <v>0</v>
+        <v>0.37</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>-0.0263</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1171400</v>
+        <v>1820100</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="H96" t="n">
-        <v>43.77</v>
-      </c>
-      <c r="I96" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.72</v>
+      </c>
+      <c r="I96" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.279</v>
+        <v>0.352</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.274</v>
+        <v>0.316</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4840,39 +4840,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.255</v>
+        <v>0.615</v>
       </c>
       <c r="E97" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1163700</v>
+        <v>1769700</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.3</v>
+        <v>0.58</v>
       </c>
       <c r="H97" t="n">
-        <v>51.46</v>
-      </c>
-      <c r="I97" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.45999999999999</v>
+      </c>
+      <c r="I97" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.25</v>
+        <v>0.608</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.254</v>
+        <v>0.586</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4885,39 +4885,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.645</v>
+        <v>1.27</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>-0.0077</v>
+        <v>-0.0155</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1154400</v>
+        <v>1750300</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.34</v>
+        <v>0.42</v>
       </c>
       <c r="H98" t="n">
-        <v>66.18000000000001</v>
-      </c>
-      <c r="I98" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.04</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.63</v>
+        <v>1.231</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.586</v>
+        <v>1.128</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4930,28 +4930,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>-0.0254</v>
+        <v>0.26</v>
+      </c>
+      <c r="E99" s="16" t="n">
+        <v>0.0196</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1145800</v>
+        <v>1702900</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.41</v>
+        <v>2.39</v>
       </c>
       <c r="H99" t="n">
-        <v>40.37</v>
+        <v>45.51</v>
       </c>
       <c r="I99" s="13" t="inlineStr">
         <is>
@@ -4959,10 +4959,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.593</v>
+        <v>0.262</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.613</v>
+        <v>0.267</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4975,28 +4975,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>SENDAI</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>4.97</v>
+        <v>0.28</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>-0.002</v>
+        <v>-0.0175</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1105100</v>
+        <v>1700900</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.21</v>
+        <v>1.09</v>
       </c>
       <c r="H100" t="n">
-        <v>49.07</v>
+        <v>62.61</v>
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>4.976</v>
+        <v>0.254</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>5.032</v>
+        <v>0.271</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5020,39 +5020,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E101" s="17" t="n">
-        <v>0</v>
+        <v>1.87</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>-0.0158</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1051400</v>
+        <v>1699300</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="H101" t="n">
-        <v>54.93</v>
-      </c>
-      <c r="I101" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.67</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.332</v>
+        <v>1.971</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.309</v>
+        <v>2.091</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5065,39 +5065,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>SEALINK</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E102" s="17" t="n">
-        <v>0</v>
+        <v>0.33</v>
+      </c>
+      <c r="E102" s="16" t="n">
+        <v>0.0154</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1041500</v>
+        <v>1688000</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.14</v>
+        <v>2.43</v>
       </c>
       <c r="H102" t="n">
-        <v>51.39</v>
-      </c>
-      <c r="I102" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.45</v>
+      </c>
+      <c r="I102" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.213</v>
+        <v>0.314</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.211</v>
+        <v>0.308</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5110,39 +5110,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>4.82</v>
+        <v>0.315</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>-0.0021</v>
+        <v>-0.0308</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1019900</v>
+        <v>1682400</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.05</v>
+        <v>0.23</v>
       </c>
       <c r="H103" t="n">
-        <v>42.95</v>
-      </c>
-      <c r="I103" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.78</v>
+      </c>
+      <c r="I103" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>4.857</v>
+        <v>0.322</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>4.973</v>
+        <v>0.339</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5155,28 +5155,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E104" s="17" t="n">
-        <v>0</v>
+        <v>0.23</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>-0.0612</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1017800</v>
+        <v>1639900</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.08</v>
+        <v>1.59</v>
       </c>
       <c r="H104" t="n">
-        <v>32.39</v>
+        <v>63.48</v>
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>1.335</v>
+        <v>0.213</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>1.459</v>
+        <v>0.206</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5200,28 +5200,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>CKI</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E105" s="16" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.365</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>-0.0395</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1009900</v>
+        <v>1615800</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.33</v>
+        <v>0.98</v>
       </c>
       <c r="H105" t="n">
-        <v>28.31</v>
+        <v>33.95</v>
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.931</v>
+        <v>0.393</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.969</v>
+        <v>0.391</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5245,39 +5245,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>THETA</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E106" s="17" t="n">
-        <v>0</v>
+        <v>0.68</v>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>0.0625</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1007900</v>
+        <v>1591100</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="H106" t="n">
-        <v>56.38</v>
-      </c>
-      <c r="I106" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.46</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.44</v>
+        <v>0.655</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.43</v>
+        <v>0.65</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5290,28 +5290,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="E107" s="10" t="n">
-        <v>-0.0114</v>
+        <v>-0.0118</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>996300</v>
+        <v>1582800</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="H107" t="n">
-        <v>33.64</v>
+        <v>33.89</v>
       </c>
       <c r="I107" s="13" t="inlineStr">
         <is>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>2.69</v>
+        <v>1.752</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>2.802</v>
+        <v>1.864</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5335,28 +5335,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>2.58</v>
+        <v>1.95</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>-0.0153</v>
+        <v>-0.0051</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>994200</v>
+        <v>1577700</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="H108" t="n">
-        <v>52</v>
+        <v>45.25</v>
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>2.567</v>
+        <v>1.987</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>2.529</v>
+        <v>1.977</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5380,28 +5380,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1.68</v>
+        <v>0.575</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>-0.0059</v>
+        <v>-0.0254</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>969300</v>
+        <v>1567900</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.15</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H109" t="n">
-        <v>34.87</v>
+        <v>40.37</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>1.753</v>
+        <v>0.593</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>1.864</v>
+        <v>0.613</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5425,28 +5425,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>1.95</v>
+        <v>0.325</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>-0.0051</v>
+        <v>-0.0152</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>967700</v>
+        <v>1505100</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="H110" t="n">
-        <v>45.25</v>
+        <v>90.75</v>
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
@@ -5454,10 +5454,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>1.987</v>
+        <v>0.253</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>1.977</v>
+        <v>0.216</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5470,28 +5470,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E111" s="17" t="n">
-        <v>0</v>
+        <v>2.23</v>
+      </c>
+      <c r="E111" s="16" t="n">
+        <v>0.0229</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>946600</v>
+        <v>1499900</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.41</v>
+        <v>0.21</v>
       </c>
       <c r="H111" t="n">
-        <v>34.81</v>
+        <v>53.37</v>
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>1.127</v>
+        <v>2.216</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>1.155</v>
+        <v>2.094</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5515,28 +5515,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>1.12</v>
+        <v>7.84</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>-0.0261</v>
+        <v>-0.0025</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>892000</v>
+        <v>1494900</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.34</v>
+        <v>0.13</v>
       </c>
       <c r="H112" t="n">
-        <v>72.06999999999999</v>
+        <v>35.4</v>
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.997</v>
+        <v>8.013</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.863</v>
+        <v>8.282</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5560,28 +5560,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="E113" s="16" t="n">
-        <v>0.0237</v>
+        <v>2.56</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>-0.0229</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>845600</v>
+        <v>1494800</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>1.12</v>
+        <v>0.24</v>
       </c>
       <c r="H113" t="n">
-        <v>58.75</v>
+        <v>49.74</v>
       </c>
       <c r="I113" s="15" t="inlineStr">
         <is>
@@ -5589,10 +5589,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>1.646</v>
+        <v>2.565</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>1.729</v>
+        <v>2.528</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5605,39 +5605,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="E114" s="16" t="n">
-        <v>0.0183</v>
+        <v>0.725</v>
+      </c>
+      <c r="E114" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>840400</v>
+        <v>1483600</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.12</v>
+        <v>0.23</v>
       </c>
       <c r="H114" t="n">
-        <v>52.64</v>
-      </c>
-      <c r="I114" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.11</v>
+      </c>
+      <c r="I114" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>2.215</v>
+        <v>0.661</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>2.094</v>
+        <v>0.606</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5650,39 +5650,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3.78</v>
+        <v>1.07</v>
       </c>
       <c r="E115" s="10" t="n">
-        <v>-0.0026</v>
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>836600</v>
+        <v>1473700</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.2</v>
+        <v>0.63</v>
       </c>
       <c r="H115" t="n">
-        <v>71.75</v>
-      </c>
-      <c r="I115" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.09</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>3.407</v>
+        <v>1.126</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>3.178</v>
+        <v>1.155</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5695,28 +5695,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>3.92</v>
+        <v>0.46</v>
       </c>
       <c r="E116" s="16" t="n">
-        <v>0.0182</v>
+        <v>0.011</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>807000</v>
+        <v>1431400</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.22</v>
+        <v>0.42</v>
       </c>
       <c r="H116" t="n">
-        <v>65.2</v>
+        <v>57.95</v>
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>3.697</v>
+        <v>0.441</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>3.352</v>
+        <v>0.43</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5740,28 +5740,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>-0.0165</v>
+        <v>1.09</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>740900</v>
+        <v>1379700</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
       <c r="H117" t="n">
-        <v>57.39</v>
+        <v>78.48</v>
       </c>
       <c r="I117" s="15" t="inlineStr">
         <is>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.985</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.574</v>
+        <v>0.829</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5785,28 +5785,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>1.88</v>
+        <v>1.45</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>-0.0105</v>
+        <v>-0.0068</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>731900</v>
+        <v>1328100</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.16</v>
+        <v>0.5</v>
       </c>
       <c r="H118" t="n">
-        <v>34.47</v>
+        <v>41.29</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>1.972</v>
+        <v>1.473</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>2.091</v>
+        <v>1.54</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5830,39 +5830,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.54</v>
+        <v>0.335</v>
       </c>
       <c r="E119" s="16" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.0152</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>729100</v>
+        <v>1327600</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="H119" t="n">
-        <v>63.07</v>
-      </c>
-      <c r="I119" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.63</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.489</v>
+        <v>0.337</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.389</v>
+        <v>0.329</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5875,28 +5875,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>1.17</v>
+        <v>0.59</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>-0.0168</v>
+        <v>-0.0248</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>708700</v>
+        <v>1264800</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.21</v>
+        <v>0.38</v>
       </c>
       <c r="H120" t="n">
-        <v>67.22</v>
+        <v>56.04</v>
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
@@ -5904,10 +5904,10 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>1.089</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.991</v>
+        <v>0.574</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5920,39 +5920,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E121" s="17" t="n">
-        <v>0</v>
+        <v>0.2</v>
+      </c>
+      <c r="E121" s="16" t="n">
+        <v>0.0256</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>689500</v>
+        <v>1264500</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="H121" t="n">
-        <v>78.48</v>
-      </c>
-      <c r="I121" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.7</v>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>0.985</v>
+        <v>0.199</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>0.829</v>
+        <v>0.196</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5965,39 +5965,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E122" s="16" t="n">
-        <v>0.0095</v>
+        <v>0.64</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>-0.0154</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>684900</v>
+        <v>1222400</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="H122" t="n">
-        <v>56.47</v>
-      </c>
-      <c r="I122" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.33</v>
+      </c>
+      <c r="I122" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>1.029</v>
+        <v>0.63</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.99</v>
+        <v>0.586</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -6010,39 +6010,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="E123" s="16" t="n">
-        <v>0.0038</v>
+        <v>2.6</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>-0.0114</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>659100</v>
+        <v>1219300</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="H123" t="n">
-        <v>81.98</v>
-      </c>
-      <c r="I123" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.64</v>
+      </c>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>2.398</v>
+        <v>2.69</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>2.073</v>
+        <v>2.802</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6055,28 +6055,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="E124" s="16" t="n">
-        <v>0.0051</v>
+        <v>0.335</v>
+      </c>
+      <c r="E124" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>653700</v>
+        <v>1213200</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1.25</v>
+        <v>0.12</v>
       </c>
       <c r="H124" t="n">
-        <v>53.68</v>
+        <v>54.93</v>
       </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.979</v>
+        <v>0.332</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.974</v>
+        <v>0.309</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6100,39 +6100,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>4.66</v>
+        <v>0.25</v>
       </c>
       <c r="E125" s="10" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0196</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>639600</v>
+        <v>1209800</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.13</v>
+        <v>0.31</v>
       </c>
       <c r="H125" t="n">
-        <v>39.73</v>
-      </c>
-      <c r="I125" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.55</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>4.753</v>
+        <v>0.249</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>5.02</v>
+        <v>0.254</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6145,39 +6145,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E126" s="17" t="n">
-        <v>0</v>
+        <v>1.17</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>-0.0168</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>637700</v>
+        <v>1176500</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.48</v>
+        <v>0.34</v>
       </c>
       <c r="H126" t="n">
-        <v>46.81</v>
-      </c>
-      <c r="I126" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.22</v>
+      </c>
+      <c r="I126" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.633</v>
+        <v>1.089</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.628</v>
+        <v>0.991</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6190,28 +6190,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0285</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>MERSEC</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="E127" s="10" t="n">
-        <v>-0.0053</v>
+        <v>0.275</v>
+      </c>
+      <c r="E127" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>632900</v>
+        <v>1171400</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.08</v>
+        <v>1.32</v>
       </c>
       <c r="H127" t="n">
-        <v>39.75</v>
+        <v>43.77</v>
       </c>
       <c r="I127" s="13" t="inlineStr">
         <is>
@@ -6219,10 +6219,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>7.743</v>
+        <v>0.279</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>7.867</v>
+        <v>0.274</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6235,39 +6235,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="E128" s="10" t="n">
-        <v>-0.0166</v>
+        <v>0.885</v>
+      </c>
+      <c r="E128" s="16" t="n">
+        <v>0.005699999999999999</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>630700</v>
+        <v>1164400</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="H128" t="n">
-        <v>50.06</v>
-      </c>
-      <c r="I128" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.31</v>
+      </c>
+      <c r="I128" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>1.774</v>
+        <v>0.931</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>1.811</v>
+        <v>0.969</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6280,28 +6280,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>6459</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>MNRB</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="E129" s="16" t="n">
-        <v>0.0389</v>
+        <v>1.14</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>630500</v>
+        <v>1128600</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>1.28</v>
+        <v>0.43</v>
       </c>
       <c r="H129" t="n">
-        <v>58.99</v>
+        <v>76.14</v>
       </c>
       <c r="I129" s="15" t="inlineStr">
         <is>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>2.868</v>
+        <v>0.999</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>2.857</v>
+        <v>0.863</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6325,39 +6325,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SENFONG</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E130" s="10" t="n">
-        <v>-0.0073</v>
+        <v>6.29</v>
+      </c>
+      <c r="E130" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>595100</v>
+        <v>1115500</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>3.57</v>
+        <v>0.06</v>
       </c>
       <c r="H130" t="n">
-        <v>42.76</v>
-      </c>
-      <c r="I130" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.97</v>
+      </c>
+      <c r="I130" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.6919999999999999</v>
+        <v>6.33</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.681</v>
+        <v>6.514</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6370,28 +6370,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>HEKTAR</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E131" s="17" t="n">
-        <v>0</v>
+        <v>0.24</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>-0.0204</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>592200</v>
+        <v>1044000</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.88</v>
+        <v>0.5</v>
       </c>
       <c r="H131" t="n">
-        <v>66.69</v>
+        <v>49.67</v>
       </c>
       <c r="I131" s="15" t="inlineStr">
         <is>
@@ -6399,10 +6399,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.5</v>
+        <v>0.241</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.473</v>
+        <v>0.243</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6415,39 +6415,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E132" s="10" t="n">
-        <v>-0.0129</v>
+        <v>0.44</v>
+      </c>
+      <c r="E132" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>578300</v>
+        <v>1034700</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.11</v>
+        <v>4.86</v>
       </c>
       <c r="H132" t="n">
-        <v>71.63</v>
-      </c>
-      <c r="I132" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.23</v>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.671</v>
+        <v>0.439</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.602</v>
+        <v>0.431</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6460,28 +6460,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="E133" s="10" t="n">
-        <v>-0.006500000000000001</v>
+        <v>8.109999999999999</v>
+      </c>
+      <c r="E133" s="16" t="n">
+        <v>0.0137</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>568600</v>
+        <v>1017700</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="H133" t="n">
-        <v>56.23</v>
+        <v>55.59</v>
       </c>
       <c r="I133" s="15" t="inlineStr">
         <is>
@@ -6489,10 +6489,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>3.021</v>
+        <v>7.939</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>3.042</v>
+        <v>8.175000000000001</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6505,39 +6505,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="E134" s="10" t="n">
-        <v>-0.0066</v>
+        <v>1.06</v>
+      </c>
+      <c r="E134" s="16" t="n">
+        <v>0.0095</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>568200</v>
+        <v>1012400</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.23</v>
+        <v>0.64</v>
       </c>
       <c r="H134" t="n">
-        <v>31.59</v>
-      </c>
-      <c r="I134" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.47</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>1.573</v>
+        <v>1.029</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>1.688</v>
+        <v>0.99</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6550,39 +6550,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>0.95</v>
+        <v>7.52</v>
       </c>
       <c r="E135" s="10" t="n">
-        <v>-0.0206</v>
+        <v>-0.0092</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>562100</v>
+        <v>981300</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.32</v>
+        <v>0.13</v>
       </c>
       <c r="H135" t="n">
-        <v>62.48</v>
-      </c>
-      <c r="I135" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.77</v>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>0.905</v>
+        <v>7.74</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>0.77</v>
+        <v>7.866</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6595,28 +6595,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E136" s="10" t="n">
-        <v>-0.0217</v>
+        <v>1.4</v>
+      </c>
+      <c r="E136" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>555400</v>
+        <v>980500</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.17</v>
+        <v>0.42</v>
       </c>
       <c r="H136" t="n">
-        <v>56.02</v>
+        <v>50.51</v>
       </c>
       <c r="I136" s="13" t="inlineStr">
         <is>
@@ -6624,10 +6624,10 @@
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>1.334</v>
+        <v>1.417</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>1.128</v>
+        <v>1.312</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6640,39 +6640,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E137" s="17" t="n">
-        <v>0</v>
+        <v>4.58</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>-0.0338</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>546600</v>
+        <v>971200</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.23</v>
+        <v>0.37</v>
       </c>
       <c r="H137" t="n">
-        <v>50.51</v>
-      </c>
-      <c r="I137" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.48</v>
+      </c>
+      <c r="I137" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>1.417</v>
+        <v>4.39</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>1.312</v>
+        <v>4.429</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6685,39 +6685,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="E138" s="17" t="n">
-        <v>0</v>
+        <v>6.73</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>-0.003</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>537900</v>
+        <v>956500</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="H138" t="n">
-        <v>85.41</v>
-      </c>
-      <c r="I138" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.77</v>
+      </c>
+      <c r="I138" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>2.021</v>
+        <v>6.795</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>1.706</v>
+        <v>6.778</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6730,28 +6730,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E139" s="10" t="n">
-        <v>-0.0059</v>
+        <v>3.91</v>
+      </c>
+      <c r="E139" s="16" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>537500</v>
+        <v>954000</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="H139" t="n">
-        <v>64.31999999999999</v>
+        <v>64.87</v>
       </c>
       <c r="I139" s="15" t="inlineStr">
         <is>
@@ -6759,10 +6759,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>0.792</v>
+        <v>3.697</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>0.709</v>
+        <v>3.351</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6775,28 +6775,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>0168</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>BMGREEN</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E140" s="10" t="n">
-        <v>-0.0295</v>
+        <v>1.73</v>
+      </c>
+      <c r="E140" s="16" t="n">
+        <v>0.0237</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>523300</v>
+        <v>929900</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.2</v>
+        <v>1.23</v>
       </c>
       <c r="H140" t="n">
-        <v>58.31</v>
+        <v>58.75</v>
       </c>
       <c r="I140" s="15" t="inlineStr">
         <is>
@@ -6804,10 +6804,10 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>4.392</v>
+        <v>1.646</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>4.429</v>
+        <v>1.729</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6820,28 +6820,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E141" s="10" t="n">
-        <v>-0.0063</v>
+        <v>2.63</v>
+      </c>
+      <c r="E141" s="16" t="n">
+        <v>0.0115</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>511600</v>
+        <v>893000</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="H141" t="n">
-        <v>58.67</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="I141" s="15" t="inlineStr">
         <is>
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>0.753</v>
+        <v>2.4</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>0.74</v>
+        <v>2.074</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6865,39 +6865,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>8.07</v>
-      </c>
-      <c r="E142" s="16" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.63</v>
+      </c>
+      <c r="E142" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>508100</v>
+        <v>887700</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.12</v>
+        <v>0.67</v>
       </c>
       <c r="H142" t="n">
-        <v>54.04</v>
-      </c>
-      <c r="I142" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.81</v>
+      </c>
+      <c r="I142" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>7.935</v>
+        <v>0.633</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>8.173999999999999</v>
+        <v>0.628</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6910,45 +6910,1485 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>KERJAYA</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="E143" s="16" t="n">
-        <v>0.0118</v>
+        <v>0.985</v>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>-0.0051</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>507700</v>
+        <v>865700</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.16</v>
+        <v>0.37</v>
       </c>
       <c r="H143" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="I143" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.92</v>
+      </c>
+      <c r="I143" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>3.246</v>
+        <v>0.999</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>2.836</v>
+        <v>1.015</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
     </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>-0.0161</v>
+      </c>
+      <c r="F144" s="11" t="n">
+        <v>855200</v>
+      </c>
+      <c r="G144" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H144" t="n">
+        <v>53.07</v>
+      </c>
+      <c r="I144" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="n">
+        <v>3.018</v>
+      </c>
+      <c r="K144" s="9" t="n">
+        <v>3.041</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="14" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>-0.0277</v>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>854500</v>
+      </c>
+      <c r="G145" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H145" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="I145" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="n">
+        <v>5.292</v>
+      </c>
+      <c r="K145" s="9" t="n">
+        <v>5.265</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="14" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E146" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" s="11" t="n">
+        <v>836000</v>
+      </c>
+      <c r="G146" s="12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H146" t="n">
+        <v>62.41</v>
+      </c>
+      <c r="I146" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="K146" s="9" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="14" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E147" s="10" t="n">
+        <v>-0.0132</v>
+      </c>
+      <c r="F147" s="11" t="n">
+        <v>816500</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H147" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="I147" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J147" s="9" t="n">
+        <v>1.572</v>
+      </c>
+      <c r="K147" s="9" t="n">
+        <v>1.688</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="14" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="E148" s="16" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="F148" s="11" t="n">
+        <v>788800</v>
+      </c>
+      <c r="G148" s="12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="H148" t="n">
+        <v>53.68</v>
+      </c>
+      <c r="I148" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="K148" s="9" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="14" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>5309</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ITMAX</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="E149" s="16" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="F149" s="11" t="n">
+        <v>770500</v>
+      </c>
+      <c r="G149" s="12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H149" t="n">
+        <v>53.01</v>
+      </c>
+      <c r="I149" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="n">
+        <v>4.418</v>
+      </c>
+      <c r="K149" s="9" t="n">
+        <v>4.496</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="14" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E150" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" s="11" t="n">
+        <v>768800</v>
+      </c>
+      <c r="G150" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H150" t="n">
+        <v>59.59</v>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="n">
+        <v>1.336</v>
+      </c>
+      <c r="K150" s="9" t="n">
+        <v>1.128</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="14" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>ECOSHOP</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="E151" s="16" t="n">
+        <v>0.0136</v>
+      </c>
+      <c r="F151" s="11" t="n">
+        <v>758500</v>
+      </c>
+      <c r="G151" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H151" t="n">
+        <v>55.77</v>
+      </c>
+      <c r="I151" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="n">
+        <v>1.472</v>
+      </c>
+      <c r="K151" s="9" t="n">
+        <v>1.473</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="14" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E152" s="10" t="n">
+        <v>-0.0127</v>
+      </c>
+      <c r="F152" s="11" t="n">
+        <v>753100</v>
+      </c>
+      <c r="G152" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H152" t="n">
+        <v>57.34</v>
+      </c>
+      <c r="I152" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J152" s="9" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="K152" s="9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="14" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E153" s="10" t="n">
+        <v>-0.0309</v>
+      </c>
+      <c r="F153" s="11" t="n">
+        <v>736300</v>
+      </c>
+      <c r="G153" s="12" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H153" t="n">
+        <v>38.42</v>
+      </c>
+      <c r="I153" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J153" s="9" t="n">
+        <v>1.633</v>
+      </c>
+      <c r="K153" s="9" t="n">
+        <v>1.697</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="14" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="E154" s="10" t="n">
+        <v>-0.0086</v>
+      </c>
+      <c r="F154" s="11" t="n">
+        <v>728000</v>
+      </c>
+      <c r="G154" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H154" t="n">
+        <v>33.88</v>
+      </c>
+      <c r="I154" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J154" s="9" t="n">
+        <v>3.637</v>
+      </c>
+      <c r="K154" s="9" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="14" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>6459</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>MNRB</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E155" s="16" t="n">
+        <v>0.0389</v>
+      </c>
+      <c r="F155" s="11" t="n">
+        <v>714000</v>
+      </c>
+      <c r="G155" s="12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H155" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="I155" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J155" s="9" t="n">
+        <v>2.868</v>
+      </c>
+      <c r="K155" s="9" t="n">
+        <v>2.857</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="14" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>5180</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>CLMT</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E156" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="11" t="n">
+        <v>701500</v>
+      </c>
+      <c r="G156" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H156" t="n">
+        <v>46.86</v>
+      </c>
+      <c r="I156" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J156" s="9" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="K156" s="9" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="14" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="E157" s="10" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="F157" s="11" t="n">
+        <v>693300</v>
+      </c>
+      <c r="G157" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H157" t="n">
+        <v>84.48999999999999</v>
+      </c>
+      <c r="I157" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J157" s="9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="K157" s="9" t="n">
+        <v>1.706</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="14" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="E158" s="10" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="F158" s="11" t="n">
+        <v>689700</v>
+      </c>
+      <c r="G158" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H158" t="n">
+        <v>39.73</v>
+      </c>
+      <c r="I158" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J158" s="9" t="n">
+        <v>4.753</v>
+      </c>
+      <c r="K158" s="9" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="14" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E159" s="10" t="n">
+        <v>-0.0206</v>
+      </c>
+      <c r="F159" s="11" t="n">
+        <v>681600</v>
+      </c>
+      <c r="G159" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H159" t="n">
+        <v>62.48</v>
+      </c>
+      <c r="I159" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J159" s="9" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="K159" s="9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="14" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>5121</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>HEKTAR</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E160" s="16" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="F160" s="11" t="n">
+        <v>642200</v>
+      </c>
+      <c r="G160" s="12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H160" t="n">
+        <v>68.97</v>
+      </c>
+      <c r="I160" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J160" s="9" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="K160" s="9" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="14" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>KERJAYA</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="E161" s="16" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="F161" s="11" t="n">
+        <v>635000</v>
+      </c>
+      <c r="G161" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H161" t="n">
+        <v>69.29000000000001</v>
+      </c>
+      <c r="I161" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J161" s="9" t="n">
+        <v>3.245</v>
+      </c>
+      <c r="K161" s="9" t="n">
+        <v>2.836</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="14" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>5272</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>RANHILL</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="E162" s="16" t="n">
+        <v>0.0186</v>
+      </c>
+      <c r="F162" s="11" t="n">
+        <v>613800</v>
+      </c>
+      <c r="G162" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H162" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="I162" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J162" s="9" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K162" s="9" t="n">
+        <v>2.469</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="14" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E163" s="10" t="n">
+        <v>-0.0194</v>
+      </c>
+      <c r="F163" s="11" t="n">
+        <v>609900</v>
+      </c>
+      <c r="G163" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H163" t="n">
+        <v>70.37</v>
+      </c>
+      <c r="I163" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J163" s="9" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K163" s="9" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="14" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>5308</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>SENFONG</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E164" s="16" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="F164" s="11" t="n">
+        <v>607100</v>
+      </c>
+      <c r="G164" s="12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H164" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="I164" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J164" s="9" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="K164" s="9" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="14" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E165" s="10" t="n">
+        <v>-0.0059</v>
+      </c>
+      <c r="F165" s="11" t="n">
+        <v>597400</v>
+      </c>
+      <c r="G165" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H165" t="n">
+        <v>64.31999999999999</v>
+      </c>
+      <c r="I165" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J165" s="9" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="K165" s="9" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="14" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E166" s="10" t="n">
+        <v>-0.0236</v>
+      </c>
+      <c r="F166" s="11" t="n">
+        <v>575200</v>
+      </c>
+      <c r="G166" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H166" t="n">
+        <v>59.46</v>
+      </c>
+      <c r="I166" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J166" s="9" t="n">
+        <v>2.769</v>
+      </c>
+      <c r="K166" s="9" t="n">
+        <v>2.662</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="14" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>6012</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>MAXIS</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="E167" s="10" t="n">
+        <v>-0.0111</v>
+      </c>
+      <c r="F167" s="11" t="n">
+        <v>563000</v>
+      </c>
+      <c r="G167" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H167" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="I167" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J167" s="9" t="n">
+        <v>3.579</v>
+      </c>
+      <c r="K167" s="9" t="n">
+        <v>3.602</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="14" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>MATRIX</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E168" s="16" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="F168" s="11" t="n">
+        <v>550000</v>
+      </c>
+      <c r="G168" s="12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H168" t="n">
+        <v>37.83</v>
+      </c>
+      <c r="I168" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J168" s="9" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="K168" s="9" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="14" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>0336</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>WINSTAR</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E169" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="11" t="n">
+        <v>548500</v>
+      </c>
+      <c r="G169" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H169" t="n">
+        <v>50.83</v>
+      </c>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J169" s="9" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="K169" s="9" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="14" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>AMBANK</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="E170" s="16" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="F170" s="11" t="n">
+        <v>536600</v>
+      </c>
+      <c r="G170" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H170" t="n">
+        <v>35.78</v>
+      </c>
+      <c r="I170" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J170" s="9" t="n">
+        <v>6.766</v>
+      </c>
+      <c r="K170" s="9" t="n">
+        <v>6.874</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="14" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>8206</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>ECOWLD</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E171" s="10" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="F171" s="11" t="n">
+        <v>531700</v>
+      </c>
+      <c r="G171" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H171" t="n">
+        <v>40.41</v>
+      </c>
+      <c r="I171" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J171" s="9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="K171" s="9" t="n">
+        <v>2.029</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="14" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>5340</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>UMSINT</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="E172" s="16" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="F172" s="11" t="n">
+        <v>530100</v>
+      </c>
+      <c r="G172" s="12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H172" t="n">
+        <v>60.81</v>
+      </c>
+      <c r="I172" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J172" s="9" t="n">
+        <v>8.318</v>
+      </c>
+      <c r="K172" s="9" t="n">
+        <v>8.122999999999999</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="14" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="E173" s="10" t="n">
+        <v>-0.0294</v>
+      </c>
+      <c r="F173" s="11" t="n">
+        <v>526600</v>
+      </c>
+      <c r="G173" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H173" t="n">
+        <v>54.51</v>
+      </c>
+      <c r="I173" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J173" s="9" t="n">
+        <v>5.827</v>
+      </c>
+      <c r="K173" s="9" t="n">
+        <v>5.715</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="14" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E174" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" s="11" t="n">
+        <v>524100</v>
+      </c>
+      <c r="G174" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H174" t="n">
+        <v>38.02</v>
+      </c>
+      <c r="I174" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J174" s="9" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="K174" s="9" t="n">
+        <v>1.051</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="14" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>FFB</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="E175" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" s="11" t="n">
+        <v>518300</v>
+      </c>
+      <c r="G175" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H175" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="I175" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J175" s="9" t="n">
+        <v>2.004</v>
+      </c>
+      <c r="K175" s="9" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M143"/>
+  <autoFilter ref="A1:M175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-24/bursa-report-2026-09-24.xlsx
+++ b/docs/downloads/2026-09-24/bursa-report-2026-09-24.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-24" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-24'!$A$1:$M$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-24'!$A$1:$M$193</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M175"/>
+  <dimension ref="A1:M193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0571</v>
+        <v>0.0476</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>3265400</v>
+        <v>4292800</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>84.29000000000001</v>
+        <v>83.77</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.947</v>
+        <v>0.946</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.78</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>RSI达84.29，处超买区间；现价1.11远高于50日均线0.78，EMA20与SAR多头信号虽成立，但短线过热。</t>
+          <t>RSI达83.77，处超买区；现价1.10远高于50日均线0.78，EMA20与SAR多头信号虽确认趋势，但短线过热，可靠性存疑。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.175</v>
+        <v>0.18</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>-0.0541</v>
+        <v>-0.027</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>204714100</v>
+        <v>214980100</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="H3" t="n">
-        <v>20.58</v>
+        <v>20.93</v>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
@@ -664,19 +664,19 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.245</v>
+        <v>0.24</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>32551100</v>
+        <v>32995500</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="H4" t="n">
-        <v>60.73</v>
+        <v>56.77</v>
       </c>
       <c r="I4" s="15" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.232</v>
+        <v>0.231</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>0.233</v>
@@ -709,19 +709,19 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.3</v>
+        <v>0.295</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>0.1321</v>
+        <v>0.1132</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>29927500</v>
+        <v>32273300</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="H5" t="n">
-        <v>60.15</v>
+        <v>58.66</v>
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.275</v>
+        <v>0.274</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>0.274</v>
@@ -760,10 +760,10 @@
         <v>0.0556</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>24990500</v>
+        <v>25781300</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>46.47</v>
+        <v>47.94</v>
       </c>
       <c r="H6" t="n">
         <v>81.81</v>
@@ -790,39 +790,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E7" s="17" t="n">
-        <v>0</v>
+        <v>2.08</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>-0.0235</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>23904800</v>
+        <v>24988900</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>1.04</v>
+        <v>1.75</v>
       </c>
       <c r="H7" t="n">
-        <v>75.95</v>
-      </c>
-      <c r="I7" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.58</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.538</v>
+        <v>2.136</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.489</v>
+        <v>2.055</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -835,28 +835,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>0.0211</v>
+        <v>0.59</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>23775400</v>
+        <v>24777500</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.97</v>
+        <v>1.07</v>
       </c>
       <c r="H8" t="n">
-        <v>56.56</v>
+        <v>75.95</v>
       </c>
       <c r="I8" s="15" t="inlineStr">
         <is>
@@ -864,10 +864,10 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.468</v>
+        <v>0.538</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.47</v>
+        <v>0.489</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -880,39 +880,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>-0.0141</v>
+        <v>0.48</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>0.0105</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>21473200</v>
+        <v>23826500</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>1.5</v>
+        <v>0.97</v>
       </c>
       <c r="H9" t="n">
-        <v>47.59</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.94</v>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2.138</v>
+        <v>0.467</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>2.056</v>
+        <v>0.47</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>0.0303</v>
+        <v>0.165</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>18482900</v>
+        <v>19599500</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="H10" t="n">
-        <v>73.19</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="I10" s="15" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.14</v>
+        <v>0.139</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>0.113</v>
@@ -970,28 +970,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>0.0759</v>
+        <v>0.525</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>-0.0367</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>18004000</v>
+        <v>18724900</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.8</v>
+        <v>0.48</v>
       </c>
       <c r="H11" t="n">
-        <v>65.12</v>
+        <v>25.96</v>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.377</v>
+        <v>0.657</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.315</v>
+        <v>0.875</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1015,28 +1015,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>-0.0183</v>
+        <v>0.42</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0.0633</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>17292300</v>
+        <v>18197900</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="H12" t="n">
-        <v>26.62</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.658</v>
+        <v>0.377</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.875</v>
+        <v>0.315</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1060,39 +1060,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="E13" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>17260200</v>
+        <v>18163700</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.88</v>
+        <v>0.96</v>
       </c>
       <c r="H13" t="n">
-        <v>37.55</v>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.58</v>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.243</v>
+        <v>0.302</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.25</v>
+        <v>0.289</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1105,39 +1105,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.31</v>
+        <v>0.23</v>
       </c>
       <c r="E14" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>16739200</v>
+        <v>18100100</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="H14" t="n">
-        <v>62.58</v>
-      </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.55</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.302</v>
+        <v>0.243</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.289</v>
+        <v>0.25</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.795</v>
+        <v>0.79</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0.0325</v>
+        <v>0.026</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>16595300</v>
+        <v>17145800</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="H15" t="n">
-        <v>65.66</v>
+        <v>64.95</v>
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
@@ -1204,19 +1204,19 @@
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>0.0222</v>
+        <v>0.225</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>13470600</v>
+        <v>14739900</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="H16" t="n">
-        <v>85.45</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
@@ -1240,39 +1240,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>FSBM</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>0.1081</v>
+        <v>0.12</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>11601500</v>
+        <v>13693700</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>15.47</v>
+        <v>0.53</v>
       </c>
       <c r="H17" t="n">
-        <v>73.70999999999999</v>
-      </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.23</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.364</v>
+        <v>0.141</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.333</v>
+        <v>0.165</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1294,19 +1294,19 @@
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.77</v>
+        <v>0.765</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>-0.006500000000000001</v>
+        <v>-0.0129</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>11159700</v>
+        <v>12731100</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="H18" t="n">
-        <v>47.7</v>
+        <v>45.62</v>
       </c>
       <c r="I18" s="15" t="inlineStr">
         <is>
@@ -1330,28 +1330,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>-0.0123</v>
+        <v>0.41</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>0.1081</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>10978500</v>
+        <v>12053800</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.88</v>
+        <v>16.07</v>
       </c>
       <c r="H19" t="n">
-        <v>46.93</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="I19" s="15" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.364</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.333</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1375,39 +1375,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0163</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CAREPLS</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>0.0588</v>
+        <v>0.395</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>10674500</v>
+        <v>11797700</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>1.32</v>
+        <v>0.24</v>
       </c>
       <c r="H20" t="n">
-        <v>67.23</v>
-      </c>
-      <c r="I20" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>85.45999999999999</v>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.082</v>
+        <v>0.305</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.076</v>
+        <v>0.171</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1420,28 +1420,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0182</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LKL</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="E21" s="17" t="n">
-        <v>0</v>
+        <v>0.8</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>-0.0184</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>10324900</v>
+        <v>11784800</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>98.08</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>53.98</v>
+        <v>44.53</v>
       </c>
       <c r="I21" s="15" t="inlineStr">
         <is>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.034</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.034</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1465,28 +1465,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>-0.0164</v>
+        <v>0.155</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>9912800</v>
+        <v>11680000</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.29</v>
+        <v>0.61</v>
       </c>
       <c r="H22" t="n">
-        <v>62.18</v>
+        <v>44.71</v>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1.714</v>
+        <v>0.156</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>1.493</v>
+        <v>0.16</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1510,28 +1510,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0007</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PUC</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>0</v>
+        <v>1.8</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>-0.0164</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>9703400</v>
+        <v>11434900</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>1.25</v>
+        <v>0.34</v>
       </c>
       <c r="H23" t="n">
-        <v>56.29</v>
+        <v>62.18</v>
       </c>
       <c r="I23" s="15" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.032</v>
+        <v>1.714</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.033</v>
+        <v>1.493</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1555,28 +1555,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0182</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>LKL</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>0.0127</v>
+        <v>0.035</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>9328100</v>
+        <v>11203000</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.19</v>
+        <v>106.42</v>
       </c>
       <c r="H24" t="n">
-        <v>85.84999999999999</v>
+        <v>53.98</v>
       </c>
       <c r="I24" s="15" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.305</v>
+        <v>0.034</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.171</v>
+        <v>0.034</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1600,28 +1600,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0163</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>CAREPLS</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>4.82</v>
+        <v>0.09</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0588</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>9312200</v>
+        <v>10684500</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.52</v>
+        <v>1.32</v>
       </c>
       <c r="H25" t="n">
-        <v>61.39</v>
+        <v>67.23</v>
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>4.71</v>
+        <v>0.082</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>4.482</v>
+        <v>0.076</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1645,39 +1645,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E26" s="17" t="n">
-        <v>0</v>
+        <v>4.84</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>0.0126</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>9146800</v>
+        <v>10247100</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.22</v>
+        <v>0.57</v>
       </c>
       <c r="H26" t="n">
-        <v>53.7</v>
-      </c>
-      <c r="I26" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.38</v>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.16</v>
+        <v>4.711</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.149</v>
+        <v>4.482</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1690,28 +1690,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0034</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MMAG</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.025</v>
+        <v>0.865</v>
       </c>
       <c r="E27" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>8888200</v>
+        <v>10139600</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>3.97</v>
+        <v>0.57</v>
       </c>
       <c r="H27" t="n">
-        <v>49.97</v>
+        <v>45.39</v>
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.025</v>
+        <v>0.868</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.027</v>
+        <v>0.871</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1735,28 +1735,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0007</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>PUC</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>-0.0169</v>
+        <v>0.035</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>8191900</v>
+        <v>9753400</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="H28" t="n">
-        <v>64.13</v>
+        <v>56.29</v>
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.27</v>
+        <v>0.032</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.268</v>
+        <v>0.033</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1780,39 +1780,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E29" s="17" t="n">
-        <v>0</v>
+        <v>0.16</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>-0.0303</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>8103900</v>
+        <v>9685100</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.85</v>
+        <v>0.24</v>
       </c>
       <c r="H29" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.62</v>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.609</v>
+        <v>0.16</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.603</v>
+        <v>0.148</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1825,39 +1825,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0034</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>MMAG</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>-0.0252</v>
+        <v>0.025</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>8060800</v>
+        <v>8938300</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1.07</v>
+        <v>3.99</v>
       </c>
       <c r="H30" t="n">
-        <v>65.91</v>
-      </c>
-      <c r="I30" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.97</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.025</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.681</v>
+        <v>0.027</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1879,19 +1879,19 @@
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>0.0106</v>
+        <v>0.016</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>7998000</v>
+        <v>8698400</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="H31" t="n">
-        <v>45.5</v>
+        <v>46.98</v>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>1.924</v>
+        <v>1.925</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>1.973</v>
@@ -1915,39 +1915,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E32" s="16" t="n">
-        <v>0.0274</v>
+        <v>0.6</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>7822200</v>
+        <v>8501700</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>1.38</v>
+        <v>0.89</v>
       </c>
       <c r="H32" t="n">
-        <v>56.64</v>
-      </c>
-      <c r="I32" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.4</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.367</v>
+        <v>0.609</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.366</v>
+        <v>0.603</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1960,39 +1960,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E33" s="17" t="n">
-        <v>0</v>
+        <v>0.775</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>-0.0252</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>7803200</v>
+        <v>8473500</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.44</v>
+        <v>1.12</v>
       </c>
       <c r="H33" t="n">
-        <v>45.39</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.91</v>
+      </c>
+      <c r="I33" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.868</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.871</v>
+        <v>0.681</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2005,39 +2005,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FSBM</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E34" s="16" t="n">
-        <v>0.0417</v>
+        <v>2.37</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>-0.0247</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>7422100</v>
+        <v>8366500</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.28</v>
+        <v>0.43</v>
       </c>
       <c r="H34" t="n">
-        <v>41.29</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.27</v>
+      </c>
+      <c r="I34" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.142</v>
+        <v>2.346</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.165</v>
+        <v>2.224</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2050,28 +2050,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="E35" s="17" t="n">
-        <v>0</v>
+        <v>0.29</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>7346000</v>
+        <v>8265400</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>3.44</v>
+        <v>1.41</v>
       </c>
       <c r="H35" t="n">
-        <v>42.33</v>
+        <v>64.13</v>
       </c>
       <c r="I35" s="15" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>1.592</v>
+        <v>0.27</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>1.654</v>
+        <v>0.268</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2095,39 +2095,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E36" s="17" t="n">
-        <v>0</v>
+        <v>0.375</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>0.0274</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>7176100</v>
+        <v>7854900</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.25</v>
+        <v>1.38</v>
       </c>
       <c r="H36" t="n">
-        <v>34.18</v>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.64</v>
+      </c>
+      <c r="I36" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.185</v>
+        <v>0.367</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.228</v>
+        <v>0.366</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2140,39 +2140,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>-0.0247</v>
+        <v>0.165</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>6931000</v>
+        <v>7738300</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.35</v>
+        <v>0.26</v>
       </c>
       <c r="H37" t="n">
-        <v>53.27</v>
-      </c>
-      <c r="I37" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.18</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>2.346</v>
+        <v>0.185</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>2.224</v>
+        <v>0.228</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2185,28 +2185,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E38" s="16" t="n">
-        <v>0.0179</v>
+        <v>1.57</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>6795900</v>
+        <v>7480700</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="H38" t="n">
-        <v>62.25</v>
+        <v>42.33</v>
       </c>
       <c r="I38" s="15" t="inlineStr">
         <is>
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>1.083</v>
+        <v>1.592</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>1.02</v>
+        <v>1.654</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2230,39 +2230,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>4.8</v>
+        <v>1.15</v>
       </c>
       <c r="E39" s="16" t="n">
-        <v>0.0042</v>
+        <v>0.0268</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>6643300</v>
+        <v>7137300</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="H39" t="n">
-        <v>58.16</v>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.4</v>
+      </c>
+      <c r="I39" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>4.745</v>
+        <v>1.084</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>4.579</v>
+        <v>1.02</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2275,28 +2275,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TEKSENG</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.305</v>
+        <v>1.03</v>
       </c>
       <c r="E40" s="16" t="n">
-        <v>0.0702</v>
+        <v>0.0098</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>6598800</v>
+        <v>6943900</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>32.09</v>
+        <v>2.16</v>
       </c>
       <c r="H40" t="n">
-        <v>80.11</v>
+        <v>91.87</v>
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.252</v>
+        <v>0.775</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.238</v>
+        <v>0.706</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2329,19 +2329,19 @@
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.555</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.0278</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>5983800</v>
+        <v>6842800</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="H41" t="n">
-        <v>73.17</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="I41" s="15" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.462</v>
+        <v>0.461</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>0.394</v>
@@ -2365,39 +2365,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0055</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SERSOL</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>-0.2</v>
+        <v>4.79</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>0.0021</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>5821700</v>
+        <v>6749500</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>1.83</v>
+        <v>0.83</v>
       </c>
       <c r="H42" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="I42" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.46</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.04</v>
+        <v>4.744</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.034</v>
+        <v>4.578</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2410,28 +2410,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>TEKSENG</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.78</v>
+        <v>0.305</v>
       </c>
       <c r="E43" s="16" t="n">
-        <v>0.013</v>
+        <v>0.0702</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>5563700</v>
+        <v>6608800</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>1</v>
+        <v>32.14</v>
       </c>
       <c r="H43" t="n">
-        <v>83.98999999999999</v>
+        <v>80.11</v>
       </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.764</v>
+        <v>0.252</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.749</v>
+        <v>0.238</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2455,28 +2455,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0055</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>SERSOL</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>0</v>
+        <v>0.04</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>-0.2</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>5542900</v>
+        <v>6031400</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.47</v>
+        <v>1.9</v>
       </c>
       <c r="H44" t="n">
-        <v>85.70999999999999</v>
+        <v>52.2</v>
       </c>
       <c r="I44" s="15" t="inlineStr">
         <is>
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>3.326</v>
+        <v>0.04</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>2.23</v>
+        <v>0.034</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2500,28 +2500,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>-0.046</v>
+        <v>4.56</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>0.0201</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>5469900</v>
+        <v>5984800</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.89</v>
+        <v>0.51</v>
       </c>
       <c r="H45" t="n">
-        <v>55.46</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="I45" s="15" t="inlineStr">
         <is>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.397</v>
+        <v>3.335</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.397</v>
+        <v>2.232</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2545,28 +2545,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>-0.0062</v>
+        <v>0.785</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>0.0195</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>5295600</v>
+        <v>5884200</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>1.69</v>
+        <v>1.06</v>
       </c>
       <c r="H46" t="n">
-        <v>49.77</v>
+        <v>86.17</v>
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.804</v>
+        <v>0.764</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.806</v>
+        <v>0.749</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2590,28 +2590,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>-0.0013</v>
+        <v>2.94</v>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>0.0103</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>5250100</v>
+        <v>5787500</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="H47" t="n">
-        <v>59.93</v>
+        <v>65.58</v>
       </c>
       <c r="I47" s="15" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>7.77</v>
+        <v>2.827</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>7.715</v>
+        <v>2.687</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2635,28 +2635,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>2.93</v>
+        <v>7.94</v>
       </c>
       <c r="E48" s="16" t="n">
-        <v>0.0069</v>
+        <v>0.0013</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>5042300</v>
+        <v>5699700</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="H48" t="n">
-        <v>64.84999999999999</v>
+        <v>61.05</v>
       </c>
       <c r="I48" s="15" t="inlineStr">
         <is>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>2.826</v>
+        <v>7.772</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>2.687</v>
+        <v>7.715</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2680,28 +2680,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E49" s="16" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.42</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>-0.0345</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>5007900</v>
+        <v>5633900</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>1.41</v>
+        <v>0.92</v>
       </c>
       <c r="H49" t="n">
-        <v>68.48</v>
+        <v>56.96</v>
       </c>
       <c r="I49" s="15" t="inlineStr">
         <is>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.868</v>
+        <v>0.398</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.848</v>
+        <v>0.397</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2725,28 +2725,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>1.39</v>
+        <v>5.84</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>-0.0347</v>
+        <v>-0.0118</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>4689500</v>
+        <v>5468400</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="H50" t="n">
-        <v>54.06</v>
+        <v>62.62</v>
       </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>1.387</v>
+        <v>5.655</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>1.284</v>
+        <v>5.068</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2770,28 +2770,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>0</v>
+        <v>1.4</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>4330000</v>
+        <v>5347300</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.23</v>
+        <v>0.41</v>
       </c>
       <c r="H51" t="n">
-        <v>44.71</v>
+        <v>55.64</v>
       </c>
       <c r="I51" s="15" t="inlineStr">
         <is>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.156</v>
+        <v>1.388</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.16</v>
+        <v>1.284</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2815,39 +2815,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E52" s="17" t="n">
-        <v>0</v>
+        <v>0.8</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>-0.0123</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>4210400</v>
+        <v>5317200</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.67</v>
+        <v>1.7</v>
       </c>
       <c r="H52" t="n">
-        <v>48.49</v>
-      </c>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.48</v>
+      </c>
+      <c r="I52" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.775</v>
+        <v>0.804</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.773</v>
+        <v>0.806</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2860,39 +2860,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>PTT</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.355</v>
+        <v>1.38</v>
       </c>
       <c r="E53" s="10" t="n">
-        <v>-0.0405</v>
+        <v>-0.0861</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>4166300</v>
+        <v>5137600</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.58</v>
+        <v>28.15</v>
       </c>
       <c r="H53" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="I53" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.67</v>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.332</v>
+        <v>1.436</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.317</v>
+        <v>1.432</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2905,28 +2905,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>-0.0118</v>
+        <v>0.9</v>
+      </c>
+      <c r="E54" s="16" t="n">
+        <v>0.005600000000000001</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>4029400</v>
+        <v>5137100</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.25</v>
+        <v>1.45</v>
       </c>
       <c r="H54" t="n">
-        <v>62.62</v>
+        <v>68.48</v>
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>5.655</v>
+        <v>0.868</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>5.068</v>
+        <v>0.848</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2950,39 +2950,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LBALUM</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="E55" s="16" t="n">
-        <v>0.0313</v>
+        <v>0.54</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>-0.0092</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>3952300</v>
+        <v>4777700</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>12.93</v>
+        <v>0.71</v>
       </c>
       <c r="H55" t="n">
-        <v>70</v>
-      </c>
-      <c r="I55" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.04</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.479</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.471</v>
+        <v>0.594</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -3004,19 +3004,19 @@
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E56" s="16" t="n">
-        <v>0.0098</v>
+        <v>1.02</v>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>3923300</v>
+        <v>4682200</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.49</v>
+        <v>0.59</v>
       </c>
       <c r="H56" t="n">
-        <v>82.59</v>
+        <v>82.06</v>
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.854</v>
+        <v>0.853</v>
       </c>
       <c r="K56" s="9" t="n">
         <v>0.744</v>
@@ -3040,39 +3040,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0219</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.54</v>
+        <v>0.31</v>
       </c>
       <c r="E57" s="10" t="n">
-        <v>-0.0092</v>
+        <v>-0.0159</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>3908500</v>
+        <v>4497800</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="H57" t="n">
-        <v>35.04</v>
-      </c>
-      <c r="I57" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.27</v>
+      </c>
+      <c r="I57" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.306</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.594</v>
+        <v>0.293</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3085,39 +3085,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>-0.0242</v>
+        <v>1.23</v>
+      </c>
+      <c r="E58" s="16" t="n">
+        <v>0.025</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>3897000</v>
+        <v>4465000</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.82</v>
+        <v>0.48</v>
       </c>
       <c r="H58" t="n">
-        <v>36.17</v>
-      </c>
-      <c r="I58" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.73</v>
+      </c>
+      <c r="I58" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.644</v>
+        <v>1.16</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.659</v>
+        <v>1.095</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3130,28 +3130,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E59" s="16" t="n">
-        <v>0.025</v>
+        <v>0.26</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>3885900</v>
+        <v>4356300</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="H59" t="n">
-        <v>63.73</v>
+        <v>39.54</v>
       </c>
       <c r="I59" s="15" t="inlineStr">
         <is>
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>1.16</v>
+        <v>0.276</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>1.095</v>
+        <v>0.317</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3175,28 +3175,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.37</v>
+        <v>0.61</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>-0.0133</v>
+        <v>-0.0161</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>3855600</v>
+        <v>4322000</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="H60" t="n">
-        <v>40.98</v>
+        <v>37.29</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.379</v>
+        <v>0.644</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.392</v>
+        <v>0.659</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3220,39 +3220,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>-0.0098</v>
+        <v>0.77</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>3797300</v>
+        <v>4268800</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>1.18</v>
+        <v>0.68</v>
       </c>
       <c r="H61" t="n">
-        <v>89.05</v>
-      </c>
-      <c r="I61" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.49</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="K61" s="9" t="n">
         <v>0.773</v>
-      </c>
-      <c r="K61" s="9" t="n">
-        <v>0.706</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3265,39 +3265,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.255</v>
+        <v>0.195</v>
       </c>
       <c r="E62" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>3774500</v>
+        <v>4264700</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.14</v>
+        <v>0.51</v>
       </c>
       <c r="H62" t="n">
-        <v>34.37</v>
-      </c>
-      <c r="I62" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.28</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.284</v>
+        <v>0.198</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.333</v>
+        <v>0.196</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3310,28 +3310,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.265</v>
+        <v>0.355</v>
       </c>
       <c r="E63" s="10" t="n">
-        <v>-0.0185</v>
+        <v>-0.0405</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>3753800</v>
+        <v>4221400</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.31</v>
+        <v>0.58</v>
       </c>
       <c r="H63" t="n">
-        <v>41.24</v>
+        <v>65.3</v>
       </c>
       <c r="I63" s="15" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.276</v>
+        <v>0.332</v>
       </c>
       <c r="K63" s="9" t="n">
         <v>0.317</v>
@@ -3355,28 +3355,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.405</v>
+        <v>0.325</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>-0.0357</v>
+        <v>-0.0152</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>3615800</v>
+        <v>4202800</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.32</v>
+        <v>0.47</v>
       </c>
       <c r="H64" t="n">
-        <v>48.41</v>
+        <v>90.75</v>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
@@ -3384,10 +3384,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.406</v>
+        <v>0.253</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.409</v>
+        <v>0.216</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3400,39 +3400,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MKLAND</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E65" s="16" t="n">
-        <v>0.1</v>
+        <v>0.535</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>-0.0273</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>3569500</v>
+        <v>4069700</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>6.96</v>
+        <v>0.29</v>
       </c>
       <c r="H65" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="I65" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.36</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.146</v>
+        <v>0.518</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.144</v>
+        <v>0.469</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3445,39 +3445,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>9326</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>LBALUM</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>-0.0273</v>
+        <v>0.5</v>
+      </c>
+      <c r="E66" s="16" t="n">
+        <v>0.0417</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>3545300</v>
+        <v>4028100</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.25</v>
+        <v>13.18</v>
       </c>
       <c r="H66" t="n">
-        <v>56.36</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.83</v>
+      </c>
+      <c r="I66" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.518</v>
+        <v>0.479</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.469</v>
+        <v>0.471</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3490,28 +3490,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="E67" s="10" t="n">
-        <v>-0.0213</v>
+        <v>-0.0196</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>3282200</v>
+        <v>3930100</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.22</v>
+        <v>0.14</v>
       </c>
       <c r="H67" t="n">
-        <v>52.68</v>
+        <v>33.17</v>
       </c>
       <c r="I67" s="15" t="inlineStr">
         <is>
@@ -3519,10 +3519,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.678</v>
+        <v>0.283</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.659</v>
+        <v>0.333</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3535,39 +3535,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.525</v>
+        <v>0.37</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>-0.009399999999999999</v>
+        <v>-0.0133</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>3275000</v>
+        <v>3860600</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.53</v>
+        <v>0.83</v>
       </c>
       <c r="H68" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="I68" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.98</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.518</v>
+        <v>0.379</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.529</v>
+        <v>0.392</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3589,19 +3589,19 @@
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="E69" s="10" t="n">
-        <v>-0.0168</v>
+        <v>-0.0336</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>3240500</v>
+        <v>3845200</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.43</v>
+        <v>0.52</v>
       </c>
       <c r="H69" t="n">
-        <v>48.92</v>
+        <v>46.58</v>
       </c>
       <c r="I69" s="15" t="inlineStr">
         <is>
@@ -3609,10 +3609,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>1.185</v>
+        <v>1.183</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>1.131</v>
+        <v>1.13</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3625,39 +3625,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>10.18</v>
+        <v>0.29</v>
       </c>
       <c r="E70" s="16" t="n">
-        <v>0.0039</v>
+        <v>0.0175</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>3192200</v>
+        <v>3816800</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.17</v>
+        <v>0.48</v>
       </c>
       <c r="H70" t="n">
-        <v>47.46</v>
-      </c>
-      <c r="I70" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.08</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>10.178</v>
+        <v>0.3</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>10.346</v>
+        <v>0.313</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3670,39 +3670,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0267</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.385</v>
+        <v>0.405</v>
       </c>
       <c r="E71" s="10" t="n">
-        <v>-0.0375</v>
+        <v>-0.0357</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>3094200</v>
+        <v>3735200</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.97</v>
+        <v>0.33</v>
       </c>
       <c r="H71" t="n">
-        <v>47.36</v>
-      </c>
-      <c r="I71" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.41</v>
+      </c>
+      <c r="I71" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.4</v>
+        <v>0.406</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.37</v>
+        <v>0.409</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3715,28 +3715,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>2.67</v>
+        <v>0.525</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>-0.0074</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>3020500</v>
+        <v>3692600</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.26</v>
+        <v>0.6</v>
       </c>
       <c r="H72" t="n">
-        <v>45</v>
+        <v>52.9</v>
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>2.68</v>
+        <v>0.518</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>2.893</v>
+        <v>0.529</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3760,28 +3760,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>MKLAND</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.505</v>
+        <v>0.165</v>
       </c>
       <c r="E73" s="16" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2968100</v>
+        <v>3678500</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.98</v>
+        <v>7.17</v>
       </c>
       <c r="H73" t="n">
-        <v>81.36</v>
+        <v>74.59</v>
       </c>
       <c r="I73" s="15" t="inlineStr">
         <is>
@@ -3789,10 +3789,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.439</v>
+        <v>0.146</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.399</v>
+        <v>0.144</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3805,39 +3805,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E74" s="17" t="n">
-        <v>0</v>
+        <v>2.7</v>
+      </c>
+      <c r="E74" s="16" t="n">
+        <v>0.0037</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2883900</v>
+        <v>3628000</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="H74" t="n">
-        <v>33.99</v>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.66</v>
+      </c>
+      <c r="I74" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.299</v>
+        <v>2.682</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.313</v>
+        <v>2.894</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3850,28 +3850,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>2.05</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E75" s="10" t="n">
-        <v>-0.0144</v>
+        <v>-0.0284</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2609000</v>
+        <v>3484400</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.24</v>
       </c>
       <c r="H75" t="n">
-        <v>45.19</v>
+        <v>51.73</v>
       </c>
       <c r="I75" s="15" t="inlineStr">
         <is>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>2.069</v>
+        <v>0.677</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>2.113</v>
+        <v>0.658</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3895,28 +3895,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ENGTEX</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E76" s="17" t="n">
-        <v>0</v>
+        <v>10.16</v>
+      </c>
+      <c r="E76" s="16" t="n">
+        <v>0.002</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2522600</v>
+        <v>3395900</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>2.65</v>
+        <v>0.19</v>
       </c>
       <c r="H76" t="n">
-        <v>56.42</v>
+        <v>45.8</v>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.433</v>
+        <v>10.176</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.44</v>
+        <v>10.345</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3940,28 +3940,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.66</v>
+        <v>0.495</v>
       </c>
       <c r="E77" s="10" t="n">
-        <v>-0.0149</v>
+        <v>-0.01</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2429900</v>
+        <v>3141600</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.25</v>
+        <v>1.04</v>
       </c>
       <c r="H77" t="n">
-        <v>60.88</v>
+        <v>77.48</v>
       </c>
       <c r="I77" s="15" t="inlineStr">
         <is>
@@ -3969,10 +3969,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.629</v>
+        <v>0.438</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.399</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3985,28 +3985,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>0267</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PTT</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>1.37</v>
+        <v>0.38</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>-0.09269999999999999</v>
+        <v>-0.05</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2407900</v>
+        <v>3125000</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>13.19</v>
+        <v>0.98</v>
       </c>
       <c r="H78" t="n">
-        <v>40.54</v>
+        <v>46.11</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -4014,10 +4014,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>1.435</v>
+        <v>0.399</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1.431</v>
+        <v>0.37</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4030,28 +4030,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="E79" s="16" t="n">
-        <v>0.015</v>
+        <v>4.83</v>
+      </c>
+      <c r="E79" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2369000</v>
+        <v>3020000</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.39</v>
+        <v>0.14</v>
       </c>
       <c r="H79" t="n">
-        <v>62.02</v>
+        <v>44.01</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>2.592</v>
+        <v>4.857</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>2.476</v>
+        <v>4.973</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4075,39 +4075,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>-0.0066</v>
+        <v>0.37</v>
+      </c>
+      <c r="E80" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2355700</v>
+        <v>3007800</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.62</v>
+        <v>0.34</v>
       </c>
       <c r="H80" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="I80" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.08</v>
+      </c>
+      <c r="I80" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.801</v>
+        <v>0.37</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.855</v>
+        <v>0.37</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4120,39 +4120,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E81" s="17" t="n">
-        <v>0</v>
+        <v>2.7</v>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>0.0112</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2322900</v>
+        <v>2969600</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.44</v>
+        <v>0.49</v>
       </c>
       <c r="H81" t="n">
-        <v>33.24</v>
-      </c>
-      <c r="I81" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.42</v>
+      </c>
+      <c r="I81" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>1.059</v>
+        <v>2.591</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>1.072</v>
+        <v>2.476</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4165,28 +4165,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>2.46</v>
+        <v>1.3</v>
       </c>
       <c r="E82" s="16" t="n">
-        <v>0.025</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2174700</v>
+        <v>2954700</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1.32</v>
+        <v>0.23</v>
       </c>
       <c r="H82" t="n">
-        <v>82.66</v>
+        <v>35.39</v>
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>2.103</v>
+        <v>1.336</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>1.905</v>
+        <v>1.459</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4210,28 +4210,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>ENGTEX</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>-0.0112</v>
+        <v>0.445</v>
+      </c>
+      <c r="E83" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2137100</v>
+        <v>2843400</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.1</v>
+        <v>2.99</v>
       </c>
       <c r="H83" t="n">
-        <v>58.44</v>
+        <v>56.42</v>
       </c>
       <c r="I83" s="15" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>2.588</v>
+        <v>0.433</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>2.425</v>
+        <v>0.44</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4255,28 +4255,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E84" s="16" t="n">
-        <v>0.0092</v>
+        <v>2.05</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>-0.0144</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2134000</v>
+        <v>2767000</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.46</v>
+        <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>65.22</v>
+        <v>45.19</v>
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.511</v>
+        <v>2.069</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.459</v>
+        <v>2.113</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4309,19 +4309,19 @@
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>13.12</v>
+        <v>13.1</v>
       </c>
       <c r="E85" s="10" t="n">
-        <v>-0.0015</v>
+        <v>-0.003</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2129500</v>
+        <v>2684500</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="H85" t="n">
-        <v>26.72</v>
+        <v>26.3</v>
       </c>
       <c r="I85" s="15" t="inlineStr">
         <is>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>13.542</v>
+        <v>13.54</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>14.106</v>
+        <v>14.105</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4345,39 +4345,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="E86" s="16" t="n">
-        <v>0.0021</v>
+        <v>0.66</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>-0.0149</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2098000</v>
+        <v>2661900</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.1</v>
+        <v>0.27</v>
       </c>
       <c r="H86" t="n">
-        <v>45.37</v>
-      </c>
-      <c r="I86" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.88</v>
+      </c>
+      <c r="I86" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>4.858</v>
+        <v>0.629</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>4.973</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4390,39 +4390,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="E87" s="16" t="n">
-        <v>0.0223</v>
+        <v>7.82</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>-0.0051</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2070600</v>
+        <v>2605000</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="H87" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="I87" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>34.59</v>
+      </c>
+      <c r="I87" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>4.611</v>
+        <v>8.010999999999999</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>4.54</v>
+        <v>8.282</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4435,28 +4435,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E88" s="17" t="n">
-        <v>0</v>
+        <v>0.23</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>-0.0612</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2064400</v>
+        <v>2489900</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.23</v>
+        <v>2.41</v>
       </c>
       <c r="H88" t="n">
-        <v>50.08</v>
+        <v>63.48</v>
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.37</v>
+        <v>0.213</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.37</v>
+        <v>0.206</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4480,39 +4480,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E89" s="17" t="n">
-        <v>0</v>
+        <v>0.75</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>-0.0066</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1992700</v>
+        <v>2466500</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.15</v>
+        <v>0.65</v>
       </c>
       <c r="H89" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="I89" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.9</v>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>1.335</v>
+        <v>0.801</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>1.459</v>
+        <v>0.855</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4525,39 +4525,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E90" s="10" t="n">
-        <v>-0.0111</v>
+        <v>2.49</v>
+      </c>
+      <c r="E90" s="16" t="n">
+        <v>0.0375</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1990100</v>
+        <v>2455300</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.26</v>
+        <v>1.49</v>
       </c>
       <c r="H90" t="n">
-        <v>52.86</v>
-      </c>
-      <c r="I90" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>83.40000000000001</v>
+      </c>
+      <c r="I90" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.444</v>
+        <v>2.106</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.4</v>
+        <v>1.906</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4570,28 +4570,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>-0.0026</v>
+        <v>0.545</v>
+      </c>
+      <c r="E91" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1977000</v>
+        <v>2434800</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="H91" t="n">
-        <v>71.75</v>
+        <v>64.2</v>
       </c>
       <c r="I91" s="15" t="inlineStr">
         <is>
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>3.407</v>
+        <v>0.511</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>3.178</v>
+        <v>0.459</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4615,28 +4615,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>-0.0276</v>
+        <v>0.615</v>
+      </c>
+      <c r="E92" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1961100</v>
+        <v>2419700</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="H92" t="n">
-        <v>47.72</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>1.772</v>
+        <v>0.608</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>1.81</v>
+        <v>0.586</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4660,39 +4660,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>4.96</v>
+        <v>1</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>-0.004</v>
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1931300</v>
+        <v>2400000</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="H93" t="n">
-        <v>48.53</v>
-      </c>
-      <c r="I93" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.5</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>4.975</v>
+        <v>1.058</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>5.032</v>
+        <v>1.072</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4705,28 +4705,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.615</v>
+        <v>3.81</v>
       </c>
       <c r="E94" s="16" t="n">
-        <v>0.0336</v>
+        <v>0.0053</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1867300</v>
+        <v>2395600</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>1.31</v>
+        <v>0.57</v>
       </c>
       <c r="H94" t="n">
-        <v>78.39</v>
+        <v>72.94</v>
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.544</v>
+        <v>3.41</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.485</v>
+        <v>3.179</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4750,39 +4750,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E95" s="16" t="n">
-        <v>0.0233</v>
+        <v>4.96</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>-0.004</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1853800</v>
+        <v>2253800</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.25</v>
+        <v>0.42</v>
       </c>
       <c r="H95" t="n">
-        <v>54.19</v>
-      </c>
-      <c r="I95" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.53</v>
+      </c>
+      <c r="I95" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.214</v>
+        <v>4.975</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.211</v>
+        <v>5.032</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4795,39 +4795,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0032</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>REDTONE</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>-0.0263</v>
+        <v>4.62</v>
+      </c>
+      <c r="E96" s="16" t="n">
+        <v>0.029</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1820100</v>
+        <v>2198200</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>1.16</v>
+        <v>0.29</v>
       </c>
       <c r="H96" t="n">
-        <v>68.72</v>
-      </c>
-      <c r="I96" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.97</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.352</v>
+        <v>4.614</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.316</v>
+        <v>4.541</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4840,28 +4840,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E97" s="17" t="n">
-        <v>0</v>
+        <v>2.65</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1769700</v>
+        <v>2182900</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.58</v>
+        <v>0.1</v>
       </c>
       <c r="H97" t="n">
-        <v>69.45999999999999</v>
+        <v>58.44</v>
       </c>
       <c r="I97" s="15" t="inlineStr">
         <is>
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.608</v>
+        <v>2.588</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.586</v>
+        <v>2.425</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4885,28 +4885,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>1.27</v>
+        <v>7.54</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>-0.0155</v>
+        <v>-0.0066</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1750300</v>
+        <v>2148400</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.42</v>
+        <v>0.29</v>
       </c>
       <c r="H98" t="n">
-        <v>57.04</v>
+        <v>39.42</v>
       </c>
       <c r="I98" s="13" t="inlineStr">
         <is>
@@ -4914,10 +4914,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>1.231</v>
+        <v>7.742</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>1.128</v>
+        <v>7.866</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4930,39 +4930,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.26</v>
+        <v>0.615</v>
       </c>
       <c r="E99" s="16" t="n">
-        <v>0.0196</v>
+        <v>0.0336</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1702900</v>
+        <v>2136400</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>2.39</v>
+        <v>1.5</v>
       </c>
       <c r="H99" t="n">
-        <v>45.51</v>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.39</v>
+      </c>
+      <c r="I99" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.262</v>
+        <v>0.544</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.267</v>
+        <v>0.485</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4975,28 +4975,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SENDAI</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.28</v>
+        <v>1.76</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>-0.0175</v>
+        <v>-0.0276</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1700900</v>
+        <v>2119100</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1.09</v>
+        <v>0.32</v>
       </c>
       <c r="H100" t="n">
-        <v>62.61</v>
+        <v>47.72</v>
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.254</v>
+        <v>1.772</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.271</v>
+        <v>1.81</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5020,39 +5020,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>REDTONE</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>1.87</v>
+        <v>0.365</v>
       </c>
       <c r="E101" s="10" t="n">
-        <v>-0.0158</v>
+        <v>-0.0395</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1699300</v>
+        <v>2077400</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.38</v>
+        <v>1.32</v>
       </c>
       <c r="H101" t="n">
-        <v>33.67</v>
-      </c>
-      <c r="I101" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.51000000000001</v>
+      </c>
+      <c r="I101" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>1.971</v>
+        <v>0.351</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>2.091</v>
+        <v>0.316</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5065,28 +5065,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SEALINK</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E102" s="16" t="n">
-        <v>0.0154</v>
+        <v>2.56</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>-0.0229</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1688000</v>
+        <v>2063800</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>2.43</v>
+        <v>0.32</v>
       </c>
       <c r="H102" t="n">
-        <v>67.45</v>
+        <v>49.74</v>
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
@@ -5094,10 +5094,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.314</v>
+        <v>2.565</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.308</v>
+        <v>2.528</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5110,28 +5110,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.315</v>
+        <v>6.27</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>-0.0308</v>
+        <v>-0.0032</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1682400</v>
+        <v>2037600</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.23</v>
+        <v>0.12</v>
       </c>
       <c r="H103" t="n">
-        <v>43.78</v>
+        <v>43.74</v>
       </c>
       <c r="I103" s="15" t="inlineStr">
         <is>
@@ -5139,10 +5139,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.322</v>
+        <v>6.328</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.339</v>
+        <v>6.514</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5155,28 +5155,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.23</v>
+        <v>1.95</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>-0.0612</v>
+        <v>-0.0051</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1639900</v>
+        <v>2036100</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1.59</v>
+        <v>0.29</v>
       </c>
       <c r="H104" t="n">
-        <v>63.48</v>
+        <v>45.25</v>
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.213</v>
+        <v>1.987</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.206</v>
+        <v>1.977</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5200,28 +5200,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CKI</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.365</v>
+        <v>0.445</v>
       </c>
       <c r="E105" s="10" t="n">
-        <v>-0.0395</v>
+        <v>-0.0111</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1615800</v>
+        <v>2033700</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.98</v>
+        <v>0.26</v>
       </c>
       <c r="H105" t="n">
-        <v>33.95</v>
+        <v>52.86</v>
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.393</v>
+        <v>0.444</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.391</v>
+        <v>0.4</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5245,39 +5245,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>THETA</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.68</v>
+        <v>2.7</v>
       </c>
       <c r="E106" s="16" t="n">
-        <v>0.0625</v>
+        <v>0.0385</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1591100</v>
+        <v>2013900</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1.5</v>
+        <v>0.31</v>
       </c>
       <c r="H106" t="n">
-        <v>54.46</v>
-      </c>
-      <c r="I106" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.83</v>
+      </c>
+      <c r="I106" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.655</v>
+        <v>2.406</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.65</v>
+        <v>2.075</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5290,28 +5290,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>1.67</v>
+        <v>1.26</v>
       </c>
       <c r="E107" s="10" t="n">
-        <v>-0.0118</v>
+        <v>-0.0233</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1582800</v>
+        <v>1961300</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.25</v>
+        <v>0.47</v>
       </c>
       <c r="H107" t="n">
-        <v>33.89</v>
+        <v>55.88</v>
       </c>
       <c r="I107" s="13" t="inlineStr">
         <is>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>1.752</v>
+        <v>1.23</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>1.864</v>
+        <v>1.128</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5335,39 +5335,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>-0.0051</v>
+        <v>-0.0105</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1577700</v>
+        <v>1900700</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.23</v>
+        <v>0.42</v>
       </c>
       <c r="H108" t="n">
-        <v>45.25</v>
-      </c>
-      <c r="I108" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.47</v>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>1.987</v>
+        <v>1.972</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>1.977</v>
+        <v>2.091</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5380,28 +5380,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E109" s="10" t="n">
-        <v>-0.0254</v>
+        <v>0.215</v>
+      </c>
+      <c r="E109" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1567900</v>
+        <v>1892800</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="H109" t="n">
-        <v>40.37</v>
+        <v>51.39</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.593</v>
+        <v>0.213</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.613</v>
+        <v>0.211</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5425,28 +5425,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>SEALINK</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E110" s="10" t="n">
-        <v>-0.0152</v>
+        <v>0.33</v>
+      </c>
+      <c r="E110" s="16" t="n">
+        <v>0.0154</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1505100</v>
+        <v>1847000</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.17</v>
+        <v>2.66</v>
       </c>
       <c r="H110" t="n">
-        <v>90.75</v>
+        <v>67.45</v>
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
@@ -5454,10 +5454,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.253</v>
+        <v>0.314</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.216</v>
+        <v>0.308</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5479,19 +5479,19 @@
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="E111" s="16" t="n">
-        <v>0.0229</v>
+        <v>0.0321</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1499900</v>
+        <v>1834100</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="H111" t="n">
-        <v>53.37</v>
+        <v>54.77</v>
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>2.216</v>
+        <v>2.218</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>2.094</v>
+        <v>2.095</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5515,39 +5515,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>7.84</v>
+        <v>1.68</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>-0.0025</v>
+        <v>-0.0059</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1494900</v>
+        <v>1789300</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.13</v>
+        <v>0.28</v>
       </c>
       <c r="H112" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="I112" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.87</v>
+      </c>
+      <c r="I112" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>8.013</v>
+        <v>1.753</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>8.282</v>
+        <v>1.864</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5560,39 +5560,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="E113" s="10" t="n">
-        <v>-0.0229</v>
+        <v>0.26</v>
+      </c>
+      <c r="E113" s="16" t="n">
+        <v>0.0196</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1494800</v>
+        <v>1785500</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.24</v>
+        <v>2.51</v>
       </c>
       <c r="H113" t="n">
-        <v>49.74</v>
-      </c>
-      <c r="I113" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.51</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>2.565</v>
+        <v>0.262</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>2.528</v>
+        <v>0.267</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5605,28 +5605,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.725</v>
+        <v>1.09</v>
       </c>
       <c r="E114" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1483600</v>
+        <v>1779000</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.23</v>
+        <v>0.14</v>
       </c>
       <c r="H114" t="n">
-        <v>71.11</v>
+        <v>78.48</v>
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
@@ -5634,10 +5634,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.661</v>
+        <v>0.985</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.606</v>
+        <v>0.829</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5650,39 +5650,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>SENDAI</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E115" s="10" t="n">
-        <v>-0.009300000000000001</v>
+        <v>0.285</v>
+      </c>
+      <c r="E115" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1473700</v>
+        <v>1772200</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.63</v>
+        <v>1.14</v>
       </c>
       <c r="H115" t="n">
-        <v>33.09</v>
-      </c>
-      <c r="I115" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.79000000000001</v>
+      </c>
+      <c r="I115" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>1.126</v>
+        <v>0.254</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>1.155</v>
+        <v>0.271</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5695,39 +5695,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>THETA</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.46</v>
+        <v>0.68</v>
       </c>
       <c r="E116" s="16" t="n">
-        <v>0.011</v>
+        <v>0.0625</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1431400</v>
+        <v>1766200</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.42</v>
+        <v>1.67</v>
       </c>
       <c r="H116" t="n">
-        <v>57.95</v>
-      </c>
-      <c r="I116" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.46</v>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.441</v>
+        <v>0.655</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.43</v>
+        <v>0.65</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5740,28 +5740,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E117" s="17" t="n">
-        <v>0</v>
+        <v>0.32</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>-0.0154</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1379700</v>
+        <v>1761500</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.11</v>
+        <v>0.24</v>
       </c>
       <c r="H117" t="n">
-        <v>78.48</v>
+        <v>46.33</v>
       </c>
       <c r="I117" s="15" t="inlineStr">
         <is>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.985</v>
+        <v>0.323</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.829</v>
+        <v>0.339</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5785,28 +5785,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>CKI</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>1.45</v>
+        <v>0.36</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>-0.0068</v>
+        <v>-0.0526</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1328100</v>
+        <v>1701400</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.5</v>
+        <v>1.03</v>
       </c>
       <c r="H118" t="n">
-        <v>41.29</v>
+        <v>32.31</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>1.473</v>
+        <v>0.392</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>1.54</v>
+        <v>0.391</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5830,28 +5830,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>LCTITAN</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E119" s="16" t="n">
-        <v>0.0152</v>
+        <v>2.6</v>
+      </c>
+      <c r="E119" s="10" t="n">
+        <v>-0.0114</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1327600</v>
+        <v>1649400</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="H119" t="n">
-        <v>49.63</v>
+        <v>33.64</v>
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
@@ -5859,10 +5859,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.337</v>
+        <v>2.69</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.329</v>
+        <v>2.802</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5875,28 +5875,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>-0.0248</v>
+        <v>-0.0069</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1264800</v>
+        <v>1612500</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.38</v>
+        <v>0.25</v>
       </c>
       <c r="H120" t="n">
-        <v>56.04</v>
+        <v>69.33</v>
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
@@ -5904,10 +5904,10 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.574</v>
+        <v>0.606</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5920,28 +5920,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E121" s="16" t="n">
-        <v>0.0256</v>
+        <v>0.575</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>-0.0254</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1264500</v>
+        <v>1603400</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.15</v>
+        <v>0.57</v>
       </c>
       <c r="H121" t="n">
-        <v>50.7</v>
+        <v>40.37</v>
       </c>
       <c r="I121" s="13" t="inlineStr">
         <is>
@@ -5949,10 +5949,10 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>0.199</v>
+        <v>0.593</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>0.196</v>
+        <v>0.613</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5965,39 +5965,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E122" s="10" t="n">
-        <v>-0.0154</v>
+        <v>1.47</v>
+      </c>
+      <c r="E122" s="16" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1222400</v>
+        <v>1572100</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.36</v>
+        <v>0.6</v>
       </c>
       <c r="H122" t="n">
-        <v>62.33</v>
-      </c>
-      <c r="I122" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.88</v>
+      </c>
+      <c r="I122" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.63</v>
+        <v>1.475</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.586</v>
+        <v>1.541</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -6010,28 +6010,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>-0.0114</v>
+        <v>0.44</v>
+      </c>
+      <c r="E123" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1219300</v>
+        <v>1534700</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.38</v>
+        <v>7.21</v>
       </c>
       <c r="H123" t="n">
-        <v>33.64</v>
+        <v>57.23</v>
       </c>
       <c r="I123" s="13" t="inlineStr">
         <is>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>2.69</v>
+        <v>0.439</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>2.802</v>
+        <v>0.431</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6055,39 +6055,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E124" s="17" t="n">
-        <v>0</v>
+        <v>1.07</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1213200</v>
+        <v>1489900</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.12</v>
+        <v>0.64</v>
       </c>
       <c r="H124" t="n">
-        <v>54.93</v>
-      </c>
-      <c r="I124" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.09</v>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.332</v>
+        <v>1.126</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.309</v>
+        <v>1.155</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6100,39 +6100,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E125" s="10" t="n">
-        <v>-0.0196</v>
+        <v>0.46</v>
+      </c>
+      <c r="E125" s="16" t="n">
+        <v>0.011</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1209800</v>
+        <v>1464900</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.31</v>
+        <v>0.43</v>
       </c>
       <c r="H125" t="n">
-        <v>49.55</v>
-      </c>
-      <c r="I125" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.95</v>
+      </c>
+      <c r="I125" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.249</v>
+        <v>0.441</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.254</v>
+        <v>0.43</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6145,28 +6145,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>1.17</v>
+        <v>0.59</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>-0.0168</v>
+        <v>-0.0248</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1176500</v>
+        <v>1420900</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.34</v>
+        <v>0.43</v>
       </c>
       <c r="H126" t="n">
-        <v>67.22</v>
+        <v>56.04</v>
       </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>1.089</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.991</v>
+        <v>0.574</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6190,39 +6190,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0285</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MERSEC</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.275</v>
+        <v>0.245</v>
       </c>
       <c r="E127" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1171400</v>
+        <v>1400500</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>1.32</v>
+        <v>0.67</v>
       </c>
       <c r="H127" t="n">
-        <v>43.77</v>
-      </c>
-      <c r="I127" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.86</v>
+      </c>
+      <c r="I127" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.279</v>
+        <v>0.241</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0.274</v>
+        <v>0.243</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6235,28 +6235,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>HIAPTEK</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E128" s="16" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.26</v>
+      </c>
+      <c r="E128" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1164400</v>
+        <v>1396000</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.38</v>
+        <v>1.08</v>
       </c>
       <c r="H128" t="n">
-        <v>28.31</v>
+        <v>55.36</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>0.931</v>
+        <v>0.256</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>0.969</v>
+        <v>0.259</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6280,39 +6280,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E129" s="10" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.33</v>
+      </c>
+      <c r="E129" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1128600</v>
+        <v>1347900</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="H129" t="n">
-        <v>76.14</v>
-      </c>
-      <c r="I129" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.27</v>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.999</v>
+        <v>0.337</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.863</v>
+        <v>0.329</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6325,28 +6325,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>6.29</v>
+        <v>0.335</v>
       </c>
       <c r="E130" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1115500</v>
+        <v>1317000</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="H130" t="n">
-        <v>44.97</v>
+        <v>54.93</v>
       </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
@@ -6354,10 +6354,10 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>6.33</v>
+        <v>0.332</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>6.514</v>
+        <v>0.309</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6370,39 +6370,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E131" s="10" t="n">
-        <v>-0.0204</v>
+        <v>0.885</v>
+      </c>
+      <c r="E131" s="16" t="n">
+        <v>0.005699999999999999</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1044000</v>
+        <v>1287600</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="H131" t="n">
-        <v>49.67</v>
-      </c>
-      <c r="I131" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.31</v>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.241</v>
+        <v>0.931</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.243</v>
+        <v>0.969</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6415,39 +6415,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>EMETALL</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E132" s="17" t="n">
-        <v>0</v>
+        <v>8.1</v>
+      </c>
+      <c r="E132" s="16" t="n">
+        <v>0.0125</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1034700</v>
+        <v>1273100</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>4.86</v>
+        <v>0.31</v>
       </c>
       <c r="H132" t="n">
-        <v>57.23</v>
-      </c>
-      <c r="I132" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.21</v>
+      </c>
+      <c r="I132" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.439</v>
+        <v>7.938</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.431</v>
+        <v>8.175000000000001</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6460,28 +6460,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="E133" s="16" t="n">
-        <v>0.0137</v>
+        <v>1.18</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1017700</v>
+        <v>1270000</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.25</v>
+        <v>0.37</v>
       </c>
       <c r="H133" t="n">
-        <v>55.59</v>
+        <v>69.41</v>
       </c>
       <c r="I133" s="15" t="inlineStr">
         <is>
@@ -6489,10 +6489,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>7.939</v>
+        <v>1.09</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>8.175000000000001</v>
+        <v>0.992</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6505,39 +6505,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E134" s="16" t="n">
-        <v>0.0095</v>
+        <v>0.99</v>
+      </c>
+      <c r="E134" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1012400</v>
+        <v>1266300</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="H134" t="n">
-        <v>56.47</v>
-      </c>
-      <c r="I134" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.18</v>
+      </c>
+      <c r="I134" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>1.029</v>
+        <v>0.999</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.99</v>
+        <v>1.015</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6550,28 +6550,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>7.52</v>
+        <v>3.44</v>
       </c>
       <c r="E135" s="10" t="n">
-        <v>-0.0092</v>
+        <v>-0.0115</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>981300</v>
+        <v>1247300</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.13</v>
+        <v>0.33</v>
       </c>
       <c r="H135" t="n">
-        <v>38.77</v>
+        <v>33.41</v>
       </c>
       <c r="I135" s="13" t="inlineStr">
         <is>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>7.74</v>
+        <v>3.636</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>7.866</v>
+        <v>3.709</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6595,39 +6595,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E136" s="17" t="n">
-        <v>0</v>
+        <v>0.645</v>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>-0.0077</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>980500</v>
+        <v>1242300</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="H136" t="n">
-        <v>50.51</v>
-      </c>
-      <c r="I136" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.18000000000001</v>
+      </c>
+      <c r="I136" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>1.417</v>
+        <v>0.63</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>1.312</v>
+        <v>0.586</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6640,28 +6640,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>4.58</v>
+        <v>1.14</v>
       </c>
       <c r="E137" s="10" t="n">
-        <v>-0.0338</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>971200</v>
+        <v>1238100</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.37</v>
+        <v>0.47</v>
       </c>
       <c r="H137" t="n">
-        <v>57.48</v>
+        <v>76.14</v>
       </c>
       <c r="I137" s="15" t="inlineStr">
         <is>
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>4.39</v>
+        <v>0.999</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>4.429</v>
+        <v>0.863</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6685,28 +6685,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>6.73</v>
+        <v>0.25</v>
       </c>
       <c r="E138" s="10" t="n">
-        <v>-0.003</v>
+        <v>-0.0196</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>956500</v>
+        <v>1209800</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="H138" t="n">
-        <v>44.77</v>
+        <v>49.55</v>
       </c>
       <c r="I138" s="13" t="inlineStr">
         <is>
@@ -6714,10 +6714,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>6.795</v>
+        <v>0.249</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>6.778</v>
+        <v>0.254</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6730,39 +6730,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="E139" s="16" t="n">
-        <v>0.0156</v>
+        <v>6.71</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>-0.0059</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>954000</v>
+        <v>1198400</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="H139" t="n">
-        <v>64.87</v>
-      </c>
-      <c r="I139" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.37</v>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>3.697</v>
+        <v>6.794</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>3.351</v>
+        <v>6.778</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6775,39 +6775,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>0285</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>MERSEC</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="E140" s="16" t="n">
-        <v>0.0237</v>
+        <v>0.275</v>
+      </c>
+      <c r="E140" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>929900</v>
+        <v>1171400</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="H140" t="n">
-        <v>58.75</v>
-      </c>
-      <c r="I140" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.77</v>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>1.646</v>
+        <v>0.279</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>1.729</v>
+        <v>0.274</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6820,39 +6820,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="E141" s="16" t="n">
-        <v>0.0115</v>
+        <v>1.05</v>
+      </c>
+      <c r="E141" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>893000</v>
+        <v>1149000</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.14</v>
+        <v>0.72</v>
       </c>
       <c r="H141" t="n">
-        <v>82.70999999999999</v>
-      </c>
-      <c r="I141" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.97</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>2.4</v>
+        <v>1.028</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>2.074</v>
+        <v>0.99</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6865,39 +6865,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E142" s="17" t="n">
-        <v>0</v>
+        <v>4.57</v>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>-0.0359</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>887700</v>
+        <v>1111200</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.67</v>
+        <v>0.43</v>
       </c>
       <c r="H142" t="n">
-        <v>46.81</v>
-      </c>
-      <c r="I142" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.08</v>
+      </c>
+      <c r="I142" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>0.633</v>
+        <v>4.389</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>0.628</v>
+        <v>4.428</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6910,28 +6910,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="E143" s="10" t="n">
-        <v>-0.0051</v>
+        <v>3.92</v>
+      </c>
+      <c r="E143" s="16" t="n">
+        <v>0.0182</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>865700</v>
+        <v>1082300</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="H143" t="n">
-        <v>44.92</v>
+        <v>65.2</v>
       </c>
       <c r="I143" s="15" t="inlineStr">
         <is>
@@ -6939,10 +6939,10 @@
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>0.999</v>
+        <v>3.697</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>1.015</v>
+        <v>3.352</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6955,28 +6955,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>3.05</v>
+        <v>0.76</v>
       </c>
       <c r="E144" s="10" t="n">
-        <v>-0.0161</v>
+        <v>-0.0194</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>855200</v>
+        <v>1038900</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="H144" t="n">
-        <v>53.07</v>
+        <v>70.37</v>
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
@@ -6984,10 +6984,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>3.018</v>
+        <v>0.67</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>3.041</v>
+        <v>0.602</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -7000,39 +7000,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>5.26</v>
+        <v>1.39</v>
       </c>
       <c r="E145" s="10" t="n">
-        <v>-0.0277</v>
+        <v>-0.0071</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>854500</v>
+        <v>1020700</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.36</v>
+        <v>0.44</v>
       </c>
       <c r="H145" t="n">
-        <v>49.46</v>
-      </c>
-      <c r="I145" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.73</v>
+      </c>
+      <c r="I145" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>5.292</v>
+        <v>1.416</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>5.265</v>
+        <v>1.312</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7045,28 +7045,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E146" s="17" t="n">
-        <v>0</v>
+        <v>5.26</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>-0.0277</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>836000</v>
+        <v>1013300</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="H146" t="n">
-        <v>62.41</v>
+        <v>49.46</v>
       </c>
       <c r="I146" s="15" t="inlineStr">
         <is>
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>0.488</v>
+        <v>5.292</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>0.389</v>
+        <v>5.265</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7090,39 +7090,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E147" s="10" t="n">
-        <v>-0.0132</v>
+        <v>1.12</v>
+      </c>
+      <c r="E147" s="16" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>816500</v>
+        <v>1005500</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.34</v>
+        <v>0.76</v>
       </c>
       <c r="H147" t="n">
-        <v>30.43</v>
-      </c>
-      <c r="I147" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.32</v>
+      </c>
+      <c r="I147" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>1.572</v>
+        <v>1.155</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>1.688</v>
+        <v>1.188</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7135,28 +7135,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0168</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>BMGREEN</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>0.985</v>
+        <v>1.74</v>
       </c>
       <c r="E148" s="16" t="n">
-        <v>0.0051</v>
+        <v>0.0296</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>788800</v>
+        <v>986400</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="H148" t="n">
-        <v>53.68</v>
+        <v>59.68</v>
       </c>
       <c r="I148" s="15" t="inlineStr">
         <is>
@@ -7164,10 +7164,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>0.979</v>
+        <v>1.647</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>0.974</v>
+        <v>1.729</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7180,39 +7180,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ITMAX</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="E149" s="16" t="n">
-        <v>0.0205</v>
+        <v>3.06</v>
+      </c>
+      <c r="E149" s="10" t="n">
+        <v>-0.0129</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>770500</v>
+        <v>972300</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.41</v>
+        <v>0.28</v>
       </c>
       <c r="H149" t="n">
-        <v>53.01</v>
-      </c>
-      <c r="I149" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.08</v>
+      </c>
+      <c r="I149" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>4.418</v>
+        <v>3.019</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>4.496</v>
+        <v>3.041</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7225,28 +7225,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>ITMAX</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E150" s="17" t="n">
-        <v>0</v>
+        <v>4.46</v>
+      </c>
+      <c r="E150" s="16" t="n">
+        <v>0.0159</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>768800</v>
+        <v>963400</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.24</v>
+        <v>0.51</v>
       </c>
       <c r="H150" t="n">
-        <v>59.59</v>
+        <v>51.87</v>
       </c>
       <c r="I150" s="13" t="inlineStr">
         <is>
@@ -7254,10 +7254,10 @@
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>1.336</v>
+        <v>4.416</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>1.128</v>
+        <v>4.495</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7270,28 +7270,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="E151" s="16" t="n">
-        <v>0.0136</v>
+        <v>1.51</v>
+      </c>
+      <c r="E151" s="10" t="n">
+        <v>-0.0066</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>758500</v>
+        <v>952500</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="H151" t="n">
-        <v>55.77</v>
+        <v>31.59</v>
       </c>
       <c r="I151" s="15" t="inlineStr">
         <is>
@@ -7299,10 +7299,10 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>1.472</v>
+        <v>1.573</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>1.473</v>
+        <v>1.688</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7315,28 +7315,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E152" s="10" t="n">
-        <v>-0.0127</v>
+        <v>1.48</v>
+      </c>
+      <c r="E152" s="16" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>753100</v>
+        <v>937800</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.27</v>
+        <v>0.09</v>
       </c>
       <c r="H152" t="n">
-        <v>57.34</v>
+        <v>53.31</v>
       </c>
       <c r="I152" s="15" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>0.753</v>
+        <v>1.471</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>0.74</v>
+        <v>1.473</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7375,10 +7375,10 @@
         <v>-0.0309</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>736300</v>
+        <v>911600</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.53</v>
+        <v>0.65</v>
       </c>
       <c r="H153" t="n">
         <v>38.42</v>
@@ -7405,28 +7405,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="E154" s="10" t="n">
-        <v>-0.0086</v>
+        <v>1.39</v>
+      </c>
+      <c r="E154" s="16" t="n">
+        <v>0.0072</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>728000</v>
+        <v>908400</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="H154" t="n">
-        <v>33.88</v>
+        <v>60.43</v>
       </c>
       <c r="I154" s="13" t="inlineStr">
         <is>
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>3.637</v>
+        <v>1.337</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>3.71</v>
+        <v>1.129</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7450,39 +7450,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>6459</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>MNRB</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="E155" s="16" t="n">
-        <v>0.0389</v>
+        <v>0.63</v>
+      </c>
+      <c r="E155" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>714000</v>
+        <v>887700</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>1.45</v>
+        <v>0.67</v>
       </c>
       <c r="H155" t="n">
-        <v>58.99</v>
-      </c>
-      <c r="I155" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.81</v>
+      </c>
+      <c r="I155" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>2.868</v>
+        <v>0.633</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>2.857</v>
+        <v>0.628</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7495,28 +7495,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E156" s="17" t="n">
-        <v>0</v>
+        <v>1.96</v>
+      </c>
+      <c r="E156" s="10" t="n">
+        <v>-0.0051</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>701500</v>
+        <v>877000</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.18</v>
+        <v>0.28</v>
       </c>
       <c r="H156" t="n">
-        <v>46.86</v>
+        <v>37.43</v>
       </c>
       <c r="I156" s="15" t="inlineStr">
         <is>
@@ -7524,10 +7524,10 @@
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>0.589</v>
+        <v>2.003</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>0.587</v>
+        <v>2.125</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7540,28 +7540,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="E157" s="10" t="n">
-        <v>-0.0039</v>
+        <v>0.535</v>
+      </c>
+      <c r="E157" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>693300</v>
+        <v>836000</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.32</v>
+        <v>0.45</v>
       </c>
       <c r="H157" t="n">
-        <v>84.48999999999999</v>
+        <v>62.41</v>
       </c>
       <c r="I157" s="15" t="inlineStr">
         <is>
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>2.02</v>
+        <v>0.488</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>1.706</v>
+        <v>0.389</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7585,28 +7585,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>4.66</v>
+        <v>2.54</v>
       </c>
       <c r="E158" s="10" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0039</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>689700</v>
+        <v>835000</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.14</v>
+        <v>0.39</v>
       </c>
       <c r="H158" t="n">
-        <v>39.73</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="I158" s="15" t="inlineStr">
         <is>
@@ -7614,10 +7614,10 @@
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>4.753</v>
+        <v>2.02</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>5.02</v>
+        <v>1.706</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7630,28 +7630,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>0.95</v>
+        <v>4.64</v>
       </c>
       <c r="E159" s="10" t="n">
-        <v>-0.0206</v>
+        <v>-0.0128</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>681600</v>
+        <v>834900</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.39</v>
+        <v>0.17</v>
       </c>
       <c r="H159" t="n">
-        <v>62.48</v>
+        <v>38.77</v>
       </c>
       <c r="I159" s="15" t="inlineStr">
         <is>
@@ -7659,10 +7659,10 @@
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>0.905</v>
+        <v>4.751</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>0.77</v>
+        <v>5.02</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7675,28 +7675,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>HEKTAR</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E160" s="16" t="n">
-        <v>0.0097</v>
+        <v>0.785</v>
+      </c>
+      <c r="E160" s="10" t="n">
+        <v>-0.0063</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>642200</v>
+        <v>815000</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.95</v>
+        <v>0.3</v>
       </c>
       <c r="H160" t="n">
-        <v>68.97</v>
+        <v>58.67</v>
       </c>
       <c r="I160" s="15" t="inlineStr">
         <is>
@@ -7704,10 +7704,10 @@
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>0.501</v>
+        <v>0.753</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>0.473</v>
+        <v>0.74</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7720,28 +7720,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>KERJAYA</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="E161" s="16" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.585</v>
+      </c>
+      <c r="E161" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>635000</v>
+        <v>804100</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="H161" t="n">
-        <v>69.29000000000001</v>
+        <v>46.86</v>
       </c>
       <c r="I161" s="13" t="inlineStr">
         <is>
@@ -7749,10 +7749,10 @@
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>3.245</v>
+        <v>0.589</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>2.836</v>
+        <v>0.587</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
@@ -7765,28 +7765,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>3.28</v>
+        <v>0.985</v>
       </c>
       <c r="E162" s="16" t="n">
-        <v>0.0186</v>
+        <v>0.0051</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>613800</v>
+        <v>788800</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.2</v>
+        <v>1.51</v>
       </c>
       <c r="H162" t="n">
-        <v>77.3</v>
+        <v>53.68</v>
       </c>
       <c r="I162" s="15" t="inlineStr">
         <is>
@@ -7794,10 +7794,10 @@
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>2.86</v>
+        <v>0.979</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>2.469</v>
+        <v>0.974</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7810,28 +7810,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>MNRB</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E163" s="10" t="n">
-        <v>-0.0194</v>
+        <v>2.94</v>
+      </c>
+      <c r="E163" s="16" t="n">
+        <v>0.0389</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>609900</v>
+        <v>743700</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.12</v>
+        <v>1.51</v>
       </c>
       <c r="H163" t="n">
-        <v>70.37</v>
+        <v>58.99</v>
       </c>
       <c r="I163" s="15" t="inlineStr">
         <is>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>0.67</v>
+        <v>2.868</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>0.602</v>
+        <v>2.857</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7855,28 +7855,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>SENFONG</t>
+          <t>KERJAYA</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>0.695</v>
+        <v>3.42</v>
       </c>
       <c r="E164" s="16" t="n">
-        <v>0.0146</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>607100</v>
+        <v>741000</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>3.65</v>
+        <v>0.24</v>
       </c>
       <c r="H164" t="n">
-        <v>52.75</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="I164" s="13" t="inlineStr">
         <is>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>0.6929999999999999</v>
+        <v>3.245</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>2.836</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7900,28 +7900,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>0.84</v>
+        <v>0.945</v>
       </c>
       <c r="E165" s="10" t="n">
-        <v>-0.0059</v>
+        <v>-0.0258</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>597400</v>
+        <v>735400</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.19</v>
+        <v>0.42</v>
       </c>
       <c r="H165" t="n">
-        <v>64.31999999999999</v>
+        <v>61.49</v>
       </c>
       <c r="I165" s="15" t="inlineStr">
         <is>
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>0.792</v>
+        <v>0.904</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>0.709</v>
+        <v>0.77</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7945,28 +7945,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E166" s="10" t="n">
-        <v>-0.0236</v>
+        <v>3.27</v>
+      </c>
+      <c r="E166" s="16" t="n">
+        <v>0.0155</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>575200</v>
+        <v>730700</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="H166" t="n">
-        <v>59.46</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="I166" s="15" t="inlineStr">
         <is>
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>2.769</v>
+        <v>2.86</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>2.662</v>
+        <v>2.469</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7990,39 +7990,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>MAXIS</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>3.57</v>
+        <v>5.92</v>
       </c>
       <c r="E167" s="10" t="n">
-        <v>-0.0111</v>
+        <v>-0.0343</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>563000</v>
+        <v>694600</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="H167" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="I167" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.63</v>
+      </c>
+      <c r="I167" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>3.579</v>
+        <v>5.824</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>3.602</v>
+        <v>5.714</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -8035,39 +8035,39 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>MAXIS</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E168" s="16" t="n">
-        <v>0.018</v>
+        <v>3.59</v>
+      </c>
+      <c r="E168" s="10" t="n">
+        <v>-0.005500000000000001</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>550000</v>
+        <v>693800</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.41</v>
+        <v>0.3</v>
       </c>
       <c r="H168" t="n">
-        <v>37.83</v>
-      </c>
-      <c r="I168" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.5</v>
+      </c>
+      <c r="I168" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>1.156</v>
+        <v>3.581</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>1.188</v>
+        <v>3.603</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8080,39 +8080,39 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0336</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>WINSTAR</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E169" s="17" t="n">
-        <v>0</v>
+        <v>0.545</v>
+      </c>
+      <c r="E169" s="16" t="n">
+        <v>0.009300000000000001</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>548500</v>
+        <v>657500</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.36</v>
+        <v>0.16</v>
       </c>
       <c r="H169" t="n">
-        <v>50.83</v>
-      </c>
-      <c r="I169" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>30.26</v>
+      </c>
+      <c r="I169" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>0.651</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>0.608</v>
+        <v>0.598</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8134,19 +8134,19 @@
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>6.63</v>
-      </c>
-      <c r="E170" s="16" t="n">
-        <v>0.0015</v>
+        <v>6.62</v>
+      </c>
+      <c r="E170" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>536600</v>
+        <v>651500</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="H170" t="n">
-        <v>35.78</v>
+        <v>34.74</v>
       </c>
       <c r="I170" s="13" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>6.766</v>
+        <v>6.765</v>
       </c>
       <c r="K170" s="9" t="n">
         <v>6.874</v>
@@ -8170,28 +8170,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>ECOWLD</t>
+          <t>HEKTAR</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="E171" s="10" t="n">
-        <v>-0.0052</v>
+        <v>0.52</v>
+      </c>
+      <c r="E171" s="16" t="n">
+        <v>0.0097</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>531700</v>
+        <v>642200</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>0.29</v>
+        <v>0.95</v>
       </c>
       <c r="H171" t="n">
-        <v>40.41</v>
+        <v>68.97</v>
       </c>
       <c r="I171" s="15" t="inlineStr">
         <is>
@@ -8199,10 +8199,10 @@
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>1.96</v>
+        <v>0.501</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>2.029</v>
+        <v>0.473</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8215,28 +8215,28 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>UMSINT</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>8.66</v>
-      </c>
-      <c r="E172" s="16" t="n">
-        <v>0.031</v>
+        <v>1.13</v>
+      </c>
+      <c r="E172" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>530100</v>
+        <v>640800</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2.35</v>
+        <v>0.28</v>
       </c>
       <c r="H172" t="n">
-        <v>60.81</v>
+        <v>59.23</v>
       </c>
       <c r="I172" s="15" t="inlineStr">
         <is>
@@ -8244,10 +8244,10 @@
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>8.318</v>
+        <v>1.077</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>8.122999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8260,39 +8260,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>5.95</v>
+        <v>2.9</v>
       </c>
       <c r="E173" s="10" t="n">
-        <v>-0.0294</v>
+        <v>-0.0236</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>526600</v>
+        <v>640600</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="H173" t="n">
-        <v>54.51</v>
-      </c>
-      <c r="I173" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.46</v>
+      </c>
+      <c r="I173" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>5.827</v>
+        <v>2.769</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>5.715</v>
+        <v>2.662</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8305,28 +8305,28 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E174" s="17" t="n">
-        <v>0</v>
+        <v>0.63</v>
+      </c>
+      <c r="E174" s="10" t="n">
+        <v>-0.0156</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>524100</v>
+        <v>637000</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H174" t="n">
-        <v>38.02</v>
+        <v>58.68</v>
       </c>
       <c r="I174" s="13" t="inlineStr">
         <is>
@@ -8334,10 +8334,10 @@
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>1.007</v>
+        <v>0.614</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>1.051</v>
+        <v>0.577</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8350,28 +8350,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1.97</v>
+        <v>1.37</v>
       </c>
       <c r="E175" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>518300</v>
+        <v>628400</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
       </c>
       <c r="H175" t="n">
-        <v>38.8</v>
+        <v>62.95</v>
       </c>
       <c r="I175" s="15" t="inlineStr">
         <is>
@@ -8379,16 +8379,826 @@
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>2.004</v>
+        <v>1.346</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>2.125</v>
+        <v>1.322</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
     </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>5248</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>BAUTO</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E176" s="16" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="F176" s="11" t="n">
+        <v>626900</v>
+      </c>
+      <c r="G176" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H176" t="n">
+        <v>49.27</v>
+      </c>
+      <c r="I176" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J176" s="9" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="K176" s="9" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="14" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E177" s="10" t="n">
+        <v>-0.0059</v>
+      </c>
+      <c r="F177" s="11" t="n">
+        <v>625200</v>
+      </c>
+      <c r="G177" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H177" t="n">
+        <v>64.31999999999999</v>
+      </c>
+      <c r="I177" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J177" s="9" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="K177" s="9" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="14" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>5340</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>UMSINT</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="E178" s="16" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="F178" s="11" t="n">
+        <v>621500</v>
+      </c>
+      <c r="G178" s="12" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H178" t="n">
+        <v>61.23</v>
+      </c>
+      <c r="I178" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J178" s="9" t="n">
+        <v>8.319000000000001</v>
+      </c>
+      <c r="K178" s="9" t="n">
+        <v>8.122999999999999</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="14" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>5308</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>SENFONG</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E179" s="16" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="F179" s="11" t="n">
+        <v>607100</v>
+      </c>
+      <c r="G179" s="12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H179" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="I179" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J179" s="9" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="K179" s="9" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="14" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>0375</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>THMY</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="E180" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" s="11" t="n">
+        <v>599500</v>
+      </c>
+      <c r="G180" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H180" t="n">
+        <v>60.57</v>
+      </c>
+      <c r="I180" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J180" s="9" t="n">
+        <v>1.854</v>
+      </c>
+      <c r="K180" s="9" t="n">
+        <v>1.864</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="14" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>8206</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>ECOWLD</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="E181" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" s="11" t="n">
+        <v>592900</v>
+      </c>
+      <c r="G181" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H181" t="n">
+        <v>41.77</v>
+      </c>
+      <c r="I181" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J181" s="9" t="n">
+        <v>1.961</v>
+      </c>
+      <c r="K181" s="9" t="n">
+        <v>2.029</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="14" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>SIMEPROP</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E182" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" s="11" t="n">
+        <v>580900</v>
+      </c>
+      <c r="G182" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H182" t="n">
+        <v>40.36</v>
+      </c>
+      <c r="I182" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J182" s="9" t="n">
+        <v>1.295</v>
+      </c>
+      <c r="K182" s="9" t="n">
+        <v>1.326</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="14" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>7034</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>TGUAN</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="E183" s="16" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="F183" s="11" t="n">
+        <v>560700</v>
+      </c>
+      <c r="G183" s="12" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H183" t="n">
+        <v>38.72</v>
+      </c>
+      <c r="I183" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J183" s="9" t="n">
+        <v>1.596</v>
+      </c>
+      <c r="K183" s="9" t="n">
+        <v>1.554</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="14" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D184" s="9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E184" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" s="11" t="n">
+        <v>558300</v>
+      </c>
+      <c r="G184" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H184" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="I184" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J184" s="9" t="n">
+        <v>1.104</v>
+      </c>
+      <c r="K184" s="9" t="n">
+        <v>1.121</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" s="14" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>SUNCON</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="E185" s="16" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F185" s="11" t="n">
+        <v>550100</v>
+      </c>
+      <c r="G185" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H185" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="I185" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J185" s="9" t="n">
+        <v>7.646</v>
+      </c>
+      <c r="K185" s="9" t="n">
+        <v>7.796</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" s="14" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>0336</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>WINSTAR</t>
+        </is>
+      </c>
+      <c r="D186" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E186" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" s="11" t="n">
+        <v>548500</v>
+      </c>
+      <c r="G186" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H186" t="n">
+        <v>50.83</v>
+      </c>
+      <c r="I186" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J186" s="9" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="K186" s="9" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" s="14" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>7052</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>PADINI</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E187" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" s="11" t="n">
+        <v>544700</v>
+      </c>
+      <c r="G187" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H187" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="I187" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J187" s="9" t="n">
+        <v>1.104</v>
+      </c>
+      <c r="K187" s="9" t="n">
+        <v>1.289</v>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" s="14" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D188" s="9" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E188" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" s="11" t="n">
+        <v>534600</v>
+      </c>
+      <c r="G188" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H188" t="n">
+        <v>38.02</v>
+      </c>
+      <c r="I188" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J188" s="9" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="K188" s="9" t="n">
+        <v>1.051</v>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" s="14" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>5053</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>OSK</t>
+        </is>
+      </c>
+      <c r="D189" s="9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E189" s="16" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="F189" s="11" t="n">
+        <v>529900</v>
+      </c>
+      <c r="G189" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H189" t="n">
+        <v>40.43</v>
+      </c>
+      <c r="I189" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J189" s="9" t="n">
+        <v>1.918</v>
+      </c>
+      <c r="K189" s="9" t="n">
+        <v>1.964</v>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" s="14" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>7174</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="D190" s="9" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E190" s="10" t="n">
+        <v>-0.009399999999999999</v>
+      </c>
+      <c r="F190" s="11" t="n">
+        <v>516200</v>
+      </c>
+      <c r="G190" s="12" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H190" t="n">
+        <v>47.57</v>
+      </c>
+      <c r="I190" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J190" s="9" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="K190" s="9" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" s="14" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>5123</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>SENTRAL</t>
+        </is>
+      </c>
+      <c r="D191" s="9" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E191" s="10" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="F191" s="11" t="n">
+        <v>508700</v>
+      </c>
+      <c r="G191" s="12" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H191" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="I191" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J191" s="9" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="K191" s="9" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" s="14" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>4197</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>SIME</t>
+        </is>
+      </c>
+      <c r="D192" s="9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E192" s="10" t="n">
+        <v>-0.0239</v>
+      </c>
+      <c r="F192" s="11" t="n">
+        <v>502000</v>
+      </c>
+      <c r="G192" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H192" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="I192" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J192" s="9" t="n">
+        <v>2.428</v>
+      </c>
+      <c r="K192" s="9" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" s="14" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>7231</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>WELLCAL</t>
+        </is>
+      </c>
+      <c r="D193" s="9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E193" s="16" t="n">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="F193" s="11" t="n">
+        <v>500200</v>
+      </c>
+      <c r="G193" s="12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H193" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="I193" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J193" s="9" t="n">
+        <v>1.112</v>
+      </c>
+      <c r="K193" s="9" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M175"/>
+  <autoFilter ref="A1:M193"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-24/bursa-report-2026-09-24.xlsx
+++ b/docs/downloads/2026-09-24/bursa-report-2026-09-24.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.67高于50日均线0.645，EMA20与SAR均呈多头，T3形态突破；RSI 58.41处中性偏强区间，未超买，信号技术面一致性尚可。</t>
+          <t>现价0.67高于50日均线0.645，EMA20与SAR均呈多头，T3形态突破；RSI 58.41处中性偏强，未超买，信号技术面较可靠。</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
         <v>0.027</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>425152300</v>
+        <v>425202300</v>
       </c>
       <c r="G3" s="12" t="n">
         <v>0.72</v>
@@ -670,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>166667800</v>
+        <v>166867800</v>
       </c>
       <c r="G4" s="12" t="n"/>
       <c r="I4" s="13" t="inlineStr">
@@ -706,7 +706,7 @@
         <v>0.2075</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>64577400</v>
+        <v>64617400</v>
       </c>
       <c r="G5" s="12" t="n">
         <v>4.71</v>
@@ -796,7 +796,7 @@
         <v>-0.0282</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>43454100</v>
+        <v>43462600</v>
       </c>
       <c r="G7" s="12" t="n">
         <v>3.05</v>
@@ -841,7 +841,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>39988400</v>
+        <v>39920400</v>
       </c>
       <c r="G8" s="12" t="n">
         <v>2.09</v>
@@ -1066,10 +1066,10 @@
         <v>-0.0556</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>29264000</v>
+        <v>29365000</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>54.42</v>
+        <v>54.61</v>
       </c>
       <c r="H13" t="n">
         <v>67.5</v>
@@ -1111,7 +1111,7 @@
         <v>-0.0833</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>28929400</v>
+        <v>29009400</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>1.11</v>
@@ -1141,39 +1141,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.415</v>
+        <v>1.18</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>0.0506</v>
+        <v>0.1569</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>26299800</v>
+        <v>26309700</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>1.16</v>
+        <v>8.19</v>
       </c>
       <c r="H15" t="n">
-        <v>63.43</v>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>94.29000000000001</v>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.376</v>
+        <v>0.79</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.314</v>
+        <v>0.709</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1186,39 +1186,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1.18</v>
+        <v>0.415</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>0.1569</v>
+        <v>0.0506</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>26230700</v>
+        <v>26299800</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>8.17</v>
+        <v>1.16</v>
       </c>
       <c r="H16" t="n">
-        <v>94.29000000000001</v>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>63.43</v>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.79</v>
+        <v>0.376</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.709</v>
+        <v>0.314</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
         <v>0.013</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>22900100</v>
+        <v>22909100</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>0.54</v>
@@ -1606,10 +1606,10 @@
         <v>0.1489</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>18544700</v>
+        <v>18928200</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>0.0222</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>18199100</v>
+        <v>18247100</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>0.9</v>
@@ -1779,7 +1779,7 @@
         <v>-0.03700000000000001</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>17214500</v>
+        <v>17216500</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>0.88</v>
@@ -1914,10 +1914,10 @@
         <v>0.1081</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>16691200</v>
+        <v>16746200</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>22.25</v>
+        <v>22.33</v>
       </c>
       <c r="H32" t="n">
         <v>73.70999999999999</v>
@@ -1959,7 +1959,7 @@
         <v>-0.0219</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>16652600</v>
+        <v>16664400</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>0.49</v>
@@ -2049,7 +2049,7 @@
         <v>-0.0314</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>16310600</v>
+        <v>16335100</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>2.16</v>
@@ -2094,7 +2094,7 @@
         <v>0.0069</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>15580300</v>
+        <v>15582300</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>1.23</v>
@@ -2139,7 +2139,7 @@
         <v>-0.006500000000000001</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>15108100</v>
+        <v>15107100</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>1.26</v>
@@ -2184,7 +2184,7 @@
         <v>-0.0021</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>14891700</v>
+        <v>14910200</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>0.68</v>
@@ -2274,7 +2274,7 @@
         <v>-0.0229</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>14301000</v>
+        <v>14302300</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>2.25</v>
@@ -2319,10 +2319,10 @@
         <v>-0.0278</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>13463400</v>
+        <v>13572300</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="H41" t="n">
         <v>66.87</v>
@@ -2904,7 +2904,7 @@
         <v>-0.0347</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>10026000</v>
+        <v>10027200</v>
       </c>
       <c r="G54" s="12" t="n">
         <v>0.77</v>
@@ -2949,7 +2949,7 @@
         <v>-0.0038</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>9990800</v>
+        <v>9991000</v>
       </c>
       <c r="G55" s="12" t="n">
         <v>0.89</v>
@@ -2994,7 +2994,7 @@
         <v>0.049</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>9901200</v>
+        <v>9902200</v>
       </c>
       <c r="G56" s="12" t="n">
         <v>1.25</v>
@@ -3039,7 +3039,7 @@
         <v>-0.0064</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>9693000</v>
+        <v>9693500</v>
       </c>
       <c r="G57" s="12" t="n">
         <v>0.55</v>
@@ -3129,7 +3129,7 @@
         <v>0.0157</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>9313400</v>
+        <v>9319100</v>
       </c>
       <c r="G59" s="12" t="n">
         <v>0.79</v>
@@ -3159,28 +3159,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="E60" s="17" t="n">
-        <v>-0.03</v>
+        <v>1.08</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0.0286</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>9070900</v>
+        <v>9283100</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>1.49</v>
+        <v>2.16</v>
       </c>
       <c r="H60" t="n">
-        <v>52.44</v>
+        <v>82.63</v>
       </c>
       <c r="I60" s="16" t="inlineStr">
         <is>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>2.581</v>
+        <v>0.944</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>2.474</v>
+        <v>0.779</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3204,39 +3204,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>0.0286</v>
+        <v>2.59</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>-0.03</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>9011100</v>
+        <v>9084200</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="H61" t="n">
-        <v>82.63</v>
-      </c>
-      <c r="I61" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.44</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.944</v>
+        <v>2.581</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.779</v>
+        <v>2.474</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3309,7 +3309,7 @@
         <v>-0.046</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>8729000</v>
+        <v>8731000</v>
       </c>
       <c r="G63" s="12" t="n">
         <v>1.43</v>
@@ -3444,7 +3444,7 @@
         <v>0.0179</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>8141300</v>
+        <v>8154300</v>
       </c>
       <c r="G66" s="12" t="n">
         <v>0.72</v>
@@ -3624,10 +3624,10 @@
         <v>0.0702</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>7615200</v>
+        <v>7620200</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>37.04</v>
+        <v>37.06</v>
       </c>
       <c r="H70" t="n">
         <v>80.11</v>
@@ -3879,39 +3879,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E76" s="17" t="n">
-        <v>-0.0256</v>
+        <v>1.23</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>0.025</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>6548400</v>
+        <v>6454200</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.78</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H76" t="n">
-        <v>44.22</v>
-      </c>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.73</v>
+      </c>
+      <c r="I76" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.198</v>
+        <v>1.16</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.196</v>
+        <v>1.095</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3969,39 +3969,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>0.025</v>
+        <v>0.19</v>
+      </c>
+      <c r="E78" s="17" t="n">
+        <v>-0.0256</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>6445700</v>
+        <v>6415900</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="H78" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="I78" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.22</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>1.16</v>
+        <v>0.198</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1.095</v>
+        <v>0.196</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4119,7 +4119,7 @@
         <v>-0.0541</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>6267400</v>
+        <v>6269400</v>
       </c>
       <c r="G81" s="12" t="n">
         <v>0.87</v>
@@ -4149,39 +4149,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>0145</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>DATAPRP</t>
+          <t>TFP</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.075</v>
+        <v>0.06</v>
       </c>
       <c r="E82" s="17" t="n">
-        <v>-0.0625</v>
+        <v>-0.07690000000000001</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>6217900</v>
+        <v>6231800</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.49</v>
+        <v>2.18</v>
       </c>
       <c r="H82" t="n">
-        <v>50.91</v>
-      </c>
-      <c r="I82" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.36</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.075</v>
+        <v>0.065</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.074</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4194,28 +4194,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>DATAPRP</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.075</v>
+      </c>
+      <c r="E83" s="17" t="n">
+        <v>-0.0625</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>6206800</v>
+        <v>6217900</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="H83" t="n">
-        <v>35.39</v>
+        <v>50.91</v>
       </c>
       <c r="I83" s="16" t="inlineStr">
         <is>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>1.336</v>
+        <v>0.075</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>1.459</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4239,39 +4239,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>4.58</v>
+        <v>1.3</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>0.02</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>6169200</v>
+        <v>6206800</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.82</v>
+        <v>0.47</v>
       </c>
       <c r="H84" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="I84" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>35.39</v>
+      </c>
+      <c r="I84" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>4.61</v>
+        <v>1.336</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>4.54</v>
+        <v>1.459</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4284,28 +4284,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0145</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TFP</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E85" s="17" t="n">
-        <v>-0.07690000000000001</v>
+        <v>4.58</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>0.02</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>6133900</v>
+        <v>6169200</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>2.15</v>
+        <v>0.82</v>
       </c>
       <c r="H85" t="n">
-        <v>41.36</v>
+        <v>49.8</v>
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
@@ -4313,10 +4313,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.065</v>
+        <v>4.61</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.074</v>
+        <v>4.54</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4389,7 +4389,7 @@
         <v>0.029</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>6029500</v>
+        <v>6048700</v>
       </c>
       <c r="G87" s="12" t="n">
         <v>1.44</v>
@@ -4479,7 +4479,7 @@
         <v>-0.0364</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>5935100</v>
+        <v>5974500</v>
       </c>
       <c r="G89" s="12" t="n">
         <v>0.42</v>
@@ -4569,7 +4569,7 @@
         <v>-0.0261</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>5814800</v>
+        <v>5833900</v>
       </c>
       <c r="G91" s="12" t="n">
         <v>0.27</v>
@@ -4614,7 +4614,7 @@
         <v>-0.002</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>5724500</v>
+        <v>5724600</v>
       </c>
       <c r="G92" s="12" t="n">
         <v>0.31</v>
@@ -4704,7 +4704,7 @@
         <v>-0.03700000000000001</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>5579100</v>
+        <v>5609100</v>
       </c>
       <c r="G94" s="12" t="n">
         <v>0.46</v>
@@ -4884,7 +4884,7 @@
         <v>-0.0196</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>5427400</v>
+        <v>5429200</v>
       </c>
       <c r="G98" s="12" t="n">
         <v>0.2</v>
@@ -4974,10 +4974,10 @@
         <v>0.1</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>5321300</v>
+        <v>5356700</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="H100" t="n">
         <v>86.31999999999999</v>
@@ -5140,7 +5140,7 @@
         <v>-0.02</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>4924600</v>
+        <v>4924700</v>
       </c>
       <c r="G104" s="12" t="n">
         <v>1.63</v>
@@ -5185,7 +5185,7 @@
         <v>-0.0426</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>4902400</v>
+        <v>4908900</v>
       </c>
       <c r="G105" s="12" t="n">
         <v>0.33</v>
@@ -5275,7 +5275,7 @@
         <v>-0.0138</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>4754300</v>
+        <v>4759300</v>
       </c>
       <c r="G107" s="12" t="n">
         <v>0.75</v>
@@ -5320,7 +5320,7 @@
         <v>-0.0373</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>4717700</v>
+        <v>4738200</v>
       </c>
       <c r="G108" s="12" t="n">
         <v>0.49</v>
@@ -5365,7 +5365,7 @@
         <v>-0.0118</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>4648300</v>
+        <v>4650300</v>
       </c>
       <c r="G109" s="12" t="n">
         <v>0.73</v>
@@ -5485,28 +5485,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>2.46</v>
+        <v>0.52</v>
       </c>
       <c r="E112" s="17" t="n">
-        <v>-0.0199</v>
+        <v>-0.0189</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>4545900</v>
+        <v>4547300</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.27</v>
+        <v>0.74</v>
       </c>
       <c r="H112" t="n">
-        <v>57.88</v>
+        <v>50.5</v>
       </c>
       <c r="I112" s="16" t="inlineStr">
         <is>
@@ -5514,10 +5514,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>2.429</v>
+        <v>0.517</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>2.258</v>
+        <v>0.529</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5530,28 +5530,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.52</v>
+        <v>2.46</v>
       </c>
       <c r="E113" s="17" t="n">
-        <v>-0.0189</v>
+        <v>-0.0199</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>4541300</v>
+        <v>4546400</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.74</v>
+        <v>0.27</v>
       </c>
       <c r="H113" t="n">
-        <v>50.5</v>
+        <v>57.88</v>
       </c>
       <c r="I113" s="16" t="inlineStr">
         <is>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.517</v>
+        <v>2.429</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.529</v>
+        <v>2.258</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5575,28 +5575,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0380</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>AQUAWALK</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E114" s="17" t="n">
-        <v>-0.0267</v>
+        <v>0.14</v>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>4387400</v>
+        <v>4430300</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.32</v>
       </c>
       <c r="H114" t="n">
-        <v>38.42</v>
+        <v>38.65</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.379</v>
+        <v>0.148</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.392</v>
+        <v>0.153</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5620,39 +5620,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.31</v>
+        <v>0.365</v>
       </c>
       <c r="E115" s="17" t="n">
-        <v>-0.0462</v>
+        <v>-0.0267</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>4333400</v>
+        <v>4387400</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.58</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H115" t="n">
-        <v>41.49</v>
-      </c>
-      <c r="I115" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.42</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.322</v>
+        <v>0.379</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.339</v>
+        <v>0.392</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5665,28 +5665,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="E116" s="10" t="n">
-        <v>0.0075</v>
+        <v>0.31</v>
+      </c>
+      <c r="E116" s="17" t="n">
+        <v>-0.0462</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>4324100</v>
+        <v>4363400</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>1.05</v>
+        <v>0.58</v>
       </c>
       <c r="H116" t="n">
-        <v>53.63</v>
+        <v>41.49</v>
       </c>
       <c r="I116" s="16" t="inlineStr">
         <is>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>7.934</v>
+        <v>0.322</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>8.173999999999999</v>
+        <v>0.339</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5710,39 +5710,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ECOFIRS</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E117" s="17" t="n">
-        <v>-0.0154</v>
+        <v>8.06</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>0.0075</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>4260200</v>
+        <v>4324100</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>1.44</v>
+        <v>1.05</v>
       </c>
       <c r="H117" t="n">
-        <v>40.34</v>
-      </c>
-      <c r="I117" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.63</v>
+      </c>
+      <c r="I117" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.335</v>
+        <v>7.934</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.343</v>
+        <v>8.173999999999999</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5755,39 +5755,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>LBALUM</t>
+          <t>ECOFIRS</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E118" s="10" t="n">
-        <v>0.0208</v>
+        <v>0.32</v>
+      </c>
+      <c r="E118" s="17" t="n">
+        <v>-0.0154</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>4254700</v>
+        <v>4260200</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>13.92</v>
+        <v>1.44</v>
       </c>
       <c r="H118" t="n">
-        <v>66.51000000000001</v>
-      </c>
-      <c r="I118" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.34</v>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.478</v>
+        <v>0.335</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.471</v>
+        <v>0.343</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5800,39 +5800,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>9326</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>LBALUM</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E119" s="17" t="n">
-        <v>-0.0222</v>
+        <v>0.49</v>
+      </c>
+      <c r="E119" s="10" t="n">
+        <v>0.0208</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>4188700</v>
+        <v>4254700</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.54</v>
+        <v>13.92</v>
       </c>
       <c r="H119" t="n">
-        <v>51.45</v>
-      </c>
-      <c r="I119" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.51000000000001</v>
+      </c>
+      <c r="I119" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.443</v>
+        <v>0.478</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.4</v>
+        <v>0.471</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5845,39 +5845,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.755</v>
+        <v>0.44</v>
       </c>
       <c r="E120" s="17" t="n">
-        <v>-0.0258</v>
+        <v>-0.0222</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>4048000</v>
+        <v>4215200</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.79</v>
+        <v>0.55</v>
       </c>
       <c r="H120" t="n">
-        <v>69.16</v>
-      </c>
-      <c r="I120" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.45</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.67</v>
+        <v>0.443</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.602</v>
+        <v>0.4</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5890,28 +5890,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E121" s="10" t="n">
-        <v>0.0672</v>
+        <v>0.755</v>
+      </c>
+      <c r="E121" s="17" t="n">
+        <v>-0.0258</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>3925500</v>
+        <v>4048000</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>2.76</v>
+        <v>0.79</v>
       </c>
       <c r="H121" t="n">
-        <v>80.78</v>
+        <v>69.16</v>
       </c>
       <c r="I121" s="16" t="inlineStr">
         <is>
@@ -5919,10 +5919,10 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>0.546</v>
+        <v>0.67</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>0.486</v>
+        <v>0.602</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5935,39 +5935,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.89</v>
+        <v>0.635</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.0672</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>3892200</v>
+        <v>3925500</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>1.26</v>
+        <v>2.76</v>
       </c>
       <c r="H122" t="n">
-        <v>30.77</v>
-      </c>
-      <c r="I122" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>80.78</v>
+      </c>
+      <c r="I122" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.931</v>
+        <v>0.546</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.969</v>
+        <v>0.486</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5980,28 +5980,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E123" s="15" t="n">
-        <v>0</v>
+        <v>0.89</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>0.0114</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>3875600</v>
+        <v>3892200</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.53</v>
+        <v>1.26</v>
       </c>
       <c r="H123" t="n">
-        <v>51.39</v>
+        <v>30.77</v>
       </c>
       <c r="I123" s="13" t="inlineStr">
         <is>
@@ -6009,10 +6009,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.213</v>
+        <v>0.931</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.211</v>
+        <v>0.969</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6025,28 +6025,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>7066</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>YONGTAI</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.105</v>
+        <v>0.215</v>
       </c>
       <c r="E124" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>3868300</v>
+        <v>3875600</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1.2</v>
+        <v>0.53</v>
       </c>
       <c r="H124" t="n">
-        <v>43.4</v>
+        <v>51.39</v>
       </c>
       <c r="I124" s="13" t="inlineStr">
         <is>
@@ -6054,10 +6054,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.111</v>
+        <v>0.213</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.114</v>
+        <v>0.211</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0032</t>
+          <t>7066</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>REDTONE</t>
+          <t>YONGTAI</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E125" s="17" t="n">
-        <v>-0.0263</v>
+        <v>0.105</v>
+      </c>
+      <c r="E125" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>3852100</v>
+        <v>3868300</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>2.46</v>
+        <v>1.2</v>
       </c>
       <c r="H125" t="n">
-        <v>68.72</v>
-      </c>
-      <c r="I125" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.4</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.352</v>
+        <v>0.111</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.316</v>
+        <v>0.114</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6115,39 +6115,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0380</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AQUAWALK</t>
+          <t>REDTONE</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E126" s="15" t="n">
-        <v>0</v>
+        <v>0.37</v>
+      </c>
+      <c r="E126" s="17" t="n">
+        <v>-0.0263</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>3840300</v>
+        <v>3852100</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>1.15</v>
+        <v>2.46</v>
       </c>
       <c r="H126" t="n">
-        <v>38.65</v>
-      </c>
-      <c r="I126" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.72</v>
+      </c>
+      <c r="I126" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.148</v>
+        <v>0.352</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.153</v>
+        <v>0.316</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6175,10 +6175,10 @@
         <v>0</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>3774200</v>
+        <v>3782400</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="H127" t="n">
         <v>78.48</v>
@@ -6205,28 +6205,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>2.6</v>
+        <v>1.26</v>
       </c>
       <c r="E128" s="17" t="n">
-        <v>-0.0114</v>
+        <v>-0.0233</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>3711500</v>
+        <v>3719600</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>1.15</v>
+        <v>0.89</v>
       </c>
       <c r="H128" t="n">
-        <v>33.64</v>
+        <v>55.88</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6234,10 +6234,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>2.69</v>
+        <v>1.23</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>2.802</v>
+        <v>1.128</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6250,39 +6250,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="E129" s="17" t="n">
-        <v>-0.0192</v>
+        <v>-0.0114</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>3657900</v>
+        <v>3711500</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="H129" t="n">
-        <v>43.79</v>
-      </c>
-      <c r="I129" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.64</v>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>2.068</v>
+        <v>2.69</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>2.113</v>
+        <v>2.802</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6295,39 +6295,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>6.72</v>
+        <v>2.04</v>
       </c>
       <c r="E130" s="17" t="n">
-        <v>-0.0044</v>
+        <v>-0.0192</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>3598400</v>
+        <v>3657900</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.82</v>
+        <v>1.32</v>
       </c>
       <c r="H130" t="n">
-        <v>44.06</v>
-      </c>
-      <c r="I130" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.79</v>
+      </c>
+      <c r="I130" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>6.794</v>
+        <v>2.068</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>6.778</v>
+        <v>2.113</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6340,39 +6340,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.535</v>
+        <v>6.72</v>
       </c>
       <c r="E131" s="17" t="n">
-        <v>-0.0183</v>
+        <v>-0.0044</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>3591300</v>
+        <v>3598400</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="H131" t="n">
-        <v>60.64</v>
-      </c>
-      <c r="I131" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.06</v>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.51</v>
+        <v>6.794</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.458</v>
+        <v>6.778</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6385,39 +6385,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>1.26</v>
+        <v>0.535</v>
       </c>
       <c r="E132" s="17" t="n">
-        <v>-0.0233</v>
+        <v>-0.0183</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>3560700</v>
+        <v>3591300</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="H132" t="n">
-        <v>55.88</v>
-      </c>
-      <c r="I132" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.64</v>
+      </c>
+      <c r="I132" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>1.23</v>
+        <v>0.51</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>1.128</v>
+        <v>0.458</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6445,7 +6445,7 @@
         <v>-0.0105</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>3542200</v>
+        <v>3543600</v>
       </c>
       <c r="G133" s="12" t="n">
         <v>0.79</v>
@@ -6625,10 +6625,10 @@
         <v>0.013</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>3276900</v>
+        <v>3292600</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="H137" t="n">
         <v>64.52</v>
@@ -6700,39 +6700,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>CKI</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="E139" s="10" t="n">
-        <v>0.0549</v>
+        <v>0.355</v>
+      </c>
+      <c r="E139" s="17" t="n">
+        <v>-0.0658</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>3150100</v>
+        <v>3188900</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>1.46</v>
+        <v>1.93</v>
       </c>
       <c r="H139" t="n">
-        <v>87.31999999999999</v>
-      </c>
-      <c r="I139" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.82</v>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>2.034</v>
+        <v>0.392</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>1.709</v>
+        <v>0.391</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6745,39 +6745,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E140" s="17" t="n">
-        <v>-0.009899999999999999</v>
+        <v>2.69</v>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>0.0549</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>3133900</v>
+        <v>3151100</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.59</v>
+        <v>1.46</v>
       </c>
       <c r="H140" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="I140" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>87.31999999999999</v>
+      </c>
+      <c r="I140" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>1.058</v>
+        <v>2.034</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>1.072</v>
+        <v>1.709</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6790,28 +6790,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>0.61</v>
+        <v>1</v>
       </c>
       <c r="E141" s="17" t="n">
-        <v>-0.008100000000000001</v>
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>3104900</v>
+        <v>3133900</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>1.02</v>
+        <v>0.59</v>
       </c>
       <c r="H141" t="n">
-        <v>59.86</v>
+        <v>31.5</v>
       </c>
       <c r="I141" s="13" t="inlineStr">
         <is>
@@ -6819,10 +6819,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>0.607</v>
+        <v>1.058</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>0.586</v>
+        <v>1.072</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6835,28 +6835,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CKI</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>0.355</v>
+        <v>0.61</v>
       </c>
       <c r="E142" s="17" t="n">
-        <v>-0.0658</v>
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>3074000</v>
+        <v>3104900</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>1.86</v>
+        <v>1.02</v>
       </c>
       <c r="H142" t="n">
-        <v>30.82</v>
+        <v>59.86</v>
       </c>
       <c r="I142" s="13" t="inlineStr">
         <is>
@@ -6864,10 +6864,10 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>0.392</v>
+        <v>0.607</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>0.391</v>
+        <v>0.586</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -7068,7 +7068,7 @@
         <v>-0.0326</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>2915000</v>
+        <v>2920000</v>
       </c>
       <c r="G147" s="12" t="n">
         <v>0.89</v>
@@ -7246,7 +7246,7 @@
         <v>0.0469</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>2787000</v>
+        <v>2788000</v>
       </c>
       <c r="G151" s="12" t="n">
         <v>2.64</v>
@@ -7471,10 +7471,10 @@
         <v>-0.0425</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>2429400</v>
+        <v>2443600</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H156" t="n">
         <v>46.96</v>
@@ -7651,7 +7651,7 @@
         <v>-0.0522</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>2292900</v>
+        <v>2290700</v>
       </c>
       <c r="G160" s="12" t="n">
         <v>0.71</v>
@@ -7681,39 +7681,39 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E161" s="17" t="n">
-        <v>-0.0299</v>
+        <v>0.345</v>
+      </c>
+      <c r="E161" s="10" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>2232500</v>
+        <v>2265800</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.22</v>
+        <v>0.85</v>
       </c>
       <c r="H161" t="n">
-        <v>50.52</v>
-      </c>
-      <c r="I161" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.77</v>
+      </c>
+      <c r="I161" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>0.331</v>
+        <v>0.338</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>0.309</v>
+        <v>0.329</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
@@ -7726,39 +7726,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>LCTITAN</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E162" s="10" t="n">
-        <v>0.0455</v>
+        <v>0.325</v>
+      </c>
+      <c r="E162" s="17" t="n">
+        <v>-0.0299</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>2215800</v>
+        <v>2232500</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.83</v>
+        <v>0.22</v>
       </c>
       <c r="H162" t="n">
-        <v>53.77</v>
-      </c>
-      <c r="I162" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.52</v>
+      </c>
+      <c r="I162" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>0.338</v>
+        <v>0.331</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>0.329</v>
+        <v>0.309</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7786,7 +7786,7 @@
         <v>-0.019</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>2147600</v>
+        <v>2148100</v>
       </c>
       <c r="G163" s="12" t="n">
         <v>0.78</v>
@@ -8221,39 +8221,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>SENDAI</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>1.57</v>
+        <v>0.28</v>
       </c>
       <c r="E173" s="17" t="n">
-        <v>-0.0309</v>
+        <v>-0.0175</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>1905500</v>
+        <v>1929000</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="H173" t="n">
-        <v>38.42</v>
-      </c>
-      <c r="I173" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.61</v>
+      </c>
+      <c r="I173" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>1.633</v>
+        <v>0.254</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>1.697</v>
+        <v>0.271</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8266,39 +8266,39 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E174" s="15" t="n">
-        <v>0</v>
+        <v>1.43</v>
+      </c>
+      <c r="E174" s="10" t="n">
+        <v>0.0214</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>1901500</v>
+        <v>1905700</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="H174" t="n">
-        <v>78.34999999999999</v>
-      </c>
-      <c r="I174" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.39</v>
+      </c>
+      <c r="I174" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>1</v>
+        <v>1.42</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>0.864</v>
+        <v>1.312</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8311,28 +8311,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E175" s="10" t="n">
-        <v>0.0214</v>
+        <v>1.57</v>
+      </c>
+      <c r="E175" s="17" t="n">
+        <v>-0.0309</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>1898700</v>
+        <v>1905500</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.37</v>
       </c>
       <c r="H175" t="n">
-        <v>55.39</v>
+        <v>38.42</v>
       </c>
       <c r="I175" s="13" t="inlineStr">
         <is>
@@ -8340,10 +8340,10 @@
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>1.42</v>
+        <v>1.633</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>1.312</v>
+        <v>1.697</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
@@ -8356,39 +8356,39 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D176" s="9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E176" s="17" t="n">
-        <v>-0.009300000000000001</v>
+        <v>1.15</v>
+      </c>
+      <c r="E176" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>1894300</v>
+        <v>1904500</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="H176" t="n">
-        <v>33.09</v>
-      </c>
-      <c r="I176" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.34999999999999</v>
+      </c>
+      <c r="I176" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J176" s="9" t="n">
-        <v>1.126</v>
+        <v>1</v>
       </c>
       <c r="K176" s="9" t="n">
-        <v>1.155</v>
+        <v>0.864</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="14" t="inlineStr"/>
@@ -8401,28 +8401,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D177" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E177" s="10" t="n">
-        <v>0.0196</v>
+        <v>1.07</v>
+      </c>
+      <c r="E177" s="17" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>1888300</v>
+        <v>1894300</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>2.66</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H177" t="n">
-        <v>45.51</v>
+        <v>33.09</v>
       </c>
       <c r="I177" s="13" t="inlineStr">
         <is>
@@ -8430,10 +8430,10 @@
         </is>
       </c>
       <c r="J177" s="9" t="n">
-        <v>0.262</v>
+        <v>1.126</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>0.267</v>
+        <v>1.155</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="14" t="inlineStr"/>
@@ -8446,39 +8446,39 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>SENDAI</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D178" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E178" s="17" t="n">
-        <v>-0.0175</v>
+        <v>0.26</v>
+      </c>
+      <c r="E178" s="10" t="n">
+        <v>0.0196</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>1852700</v>
+        <v>1888300</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1.19</v>
+        <v>2.66</v>
       </c>
       <c r="H178" t="n">
-        <v>62.61</v>
-      </c>
-      <c r="I178" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.51</v>
+      </c>
+      <c r="I178" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J178" s="9" t="n">
-        <v>0.254</v>
+        <v>0.262</v>
       </c>
       <c r="K178" s="9" t="n">
-        <v>0.271</v>
+        <v>0.267</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr"/>
@@ -8506,10 +8506,10 @@
         <v>0</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>1851100</v>
+        <v>1876100</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="H179" t="n">
         <v>52.75</v>
@@ -8641,7 +8641,7 @@
         <v>-0.0076</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>1750700</v>
+        <v>1752700</v>
       </c>
       <c r="G182" s="12" t="n">
         <v>0.34</v>
@@ -8731,7 +8731,7 @@
         <v>0</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>1672000</v>
+        <v>1672200</v>
       </c>
       <c r="G184" s="12" t="n">
         <v>0.49</v>
@@ -8821,7 +8821,7 @@
         <v>-0.03700000000000001</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>1628100</v>
+        <v>1630100</v>
       </c>
       <c r="G186" s="12" t="n">
         <v>0.51</v>
@@ -8851,39 +8851,39 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>HIAPTEK</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D187" s="9" t="n">
-        <v>0.255</v>
+        <v>2.27</v>
       </c>
       <c r="E187" s="17" t="n">
-        <v>-0.0192</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>1605700</v>
+        <v>1629300</v>
       </c>
       <c r="G187" s="12" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="H187" t="n">
-        <v>47.35</v>
-      </c>
-      <c r="I187" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.47</v>
+      </c>
+      <c r="I187" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J187" s="9" t="n">
-        <v>0.256</v>
+        <v>2.175</v>
       </c>
       <c r="K187" s="9" t="n">
-        <v>0.259</v>
+        <v>2.001</v>
       </c>
       <c r="L187" t="inlineStr"/>
       <c r="M187" s="14" t="inlineStr"/>
@@ -8896,28 +8896,28 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>HIAPTEK</t>
         </is>
       </c>
       <c r="D188" s="9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E188" s="10" t="n">
-        <v>0.019</v>
+        <v>0.255</v>
+      </c>
+      <c r="E188" s="17" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>1591200</v>
+        <v>1605700</v>
       </c>
       <c r="G188" s="12" t="n">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="H188" t="n">
-        <v>57.87</v>
+        <v>47.35</v>
       </c>
       <c r="I188" s="13" t="inlineStr">
         <is>
@@ -8925,10 +8925,10 @@
         </is>
       </c>
       <c r="J188" s="9" t="n">
-        <v>1.03</v>
+        <v>0.256</v>
       </c>
       <c r="K188" s="9" t="n">
-        <v>0.991</v>
+        <v>0.259</v>
       </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" s="14" t="inlineStr"/>
@@ -8941,39 +8941,39 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D189" s="9" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E189" s="15" t="n">
-        <v>0</v>
+        <v>1.07</v>
+      </c>
+      <c r="E189" s="10" t="n">
+        <v>0.019</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1576000</v>
+        <v>1591200</v>
       </c>
       <c r="G189" s="12" t="n">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="H189" t="n">
-        <v>46.18</v>
-      </c>
-      <c r="I189" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.87</v>
+      </c>
+      <c r="I189" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J189" s="9" t="n">
-        <v>0.999</v>
+        <v>1.03</v>
       </c>
       <c r="K189" s="9" t="n">
-        <v>1.015</v>
+        <v>0.991</v>
       </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" s="14" t="inlineStr"/>
@@ -8986,28 +8986,28 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D190" s="9" t="n">
-        <v>0.245</v>
+        <v>0.99</v>
       </c>
       <c r="E190" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>1561700</v>
+        <v>1576000</v>
       </c>
       <c r="G190" s="12" t="n">
-        <v>0.75</v>
+        <v>0.68</v>
       </c>
       <c r="H190" t="n">
-        <v>53.86</v>
+        <v>46.18</v>
       </c>
       <c r="I190" s="16" t="inlineStr">
         <is>
@@ -9015,10 +9015,10 @@
         </is>
       </c>
       <c r="J190" s="9" t="n">
-        <v>0.241</v>
+        <v>0.999</v>
       </c>
       <c r="K190" s="9" t="n">
-        <v>0.243</v>
+        <v>1.015</v>
       </c>
       <c r="L190" t="inlineStr"/>
       <c r="M190" s="14" t="inlineStr"/>
@@ -9031,39 +9031,39 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>TUNEPRO</t>
         </is>
       </c>
       <c r="D191" s="9" t="n">
-        <v>0.63</v>
+        <v>0.26</v>
       </c>
       <c r="E191" s="10" t="n">
-        <v>0.0328</v>
+        <v>0.0612</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>1556200</v>
+        <v>1566900</v>
       </c>
       <c r="G191" s="12" t="n">
-        <v>0.59</v>
+        <v>3.08</v>
       </c>
       <c r="H191" t="n">
-        <v>46.07</v>
-      </c>
-      <c r="I191" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.34</v>
+      </c>
+      <c r="I191" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J191" s="9" t="n">
-        <v>0.64</v>
+        <v>0.253</v>
       </c>
       <c r="K191" s="9" t="n">
-        <v>0.631</v>
+        <v>0.264</v>
       </c>
       <c r="L191" t="inlineStr"/>
       <c r="M191" s="14" t="inlineStr"/>
@@ -9076,39 +9076,39 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D192" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E192" s="17" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.245</v>
+      </c>
+      <c r="E192" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>1536900</v>
+        <v>1561700</v>
       </c>
       <c r="G192" s="12" t="n">
-        <v>0.48</v>
+        <v>0.75</v>
       </c>
       <c r="H192" t="n">
-        <v>59.03</v>
-      </c>
-      <c r="I192" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.86</v>
+      </c>
+      <c r="I192" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J192" s="9" t="n">
-        <v>0.858</v>
+        <v>0.241</v>
       </c>
       <c r="K192" s="9" t="n">
-        <v>0.855</v>
+        <v>0.243</v>
       </c>
       <c r="L192" t="inlineStr"/>
       <c r="M192" s="14" t="inlineStr"/>
@@ -9121,28 +9121,28 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>EMETALL</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D193" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E193" s="15" t="n">
-        <v>0</v>
+        <v>0.63</v>
+      </c>
+      <c r="E193" s="10" t="n">
+        <v>0.0328</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>1534700</v>
+        <v>1556200</v>
       </c>
       <c r="G193" s="12" t="n">
-        <v>7.21</v>
+        <v>0.59</v>
       </c>
       <c r="H193" t="n">
-        <v>57.23</v>
+        <v>46.07</v>
       </c>
       <c r="I193" s="13" t="inlineStr">
         <is>
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="J193" s="9" t="n">
-        <v>0.439</v>
+        <v>0.64</v>
       </c>
       <c r="K193" s="9" t="n">
-        <v>0.431</v>
+        <v>0.631</v>
       </c>
       <c r="L193" t="inlineStr"/>
       <c r="M193" s="14" t="inlineStr"/>
@@ -9166,39 +9166,39 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D194" s="9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="E194" s="10" t="n">
-        <v>0.0237</v>
+        <v>0.865</v>
+      </c>
+      <c r="E194" s="17" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>1513900</v>
+        <v>1536900</v>
       </c>
       <c r="G194" s="12" t="n">
-        <v>2.01</v>
+        <v>0.48</v>
       </c>
       <c r="H194" t="n">
-        <v>58.75</v>
-      </c>
-      <c r="I194" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.03</v>
+      </c>
+      <c r="I194" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J194" s="9" t="n">
-        <v>1.646</v>
+        <v>0.858</v>
       </c>
       <c r="K194" s="9" t="n">
-        <v>1.729</v>
+        <v>0.855</v>
       </c>
       <c r="L194" t="inlineStr"/>
       <c r="M194" s="14" t="inlineStr"/>
@@ -9211,39 +9211,39 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D195" s="9" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="E195" s="17" t="n">
-        <v>-0.0225</v>
+        <v>0.44</v>
+      </c>
+      <c r="E195" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>1488400</v>
+        <v>1534700</v>
       </c>
       <c r="G195" s="12" t="n">
-        <v>0.42</v>
+        <v>7.21</v>
       </c>
       <c r="H195" t="n">
-        <v>49.75</v>
-      </c>
-      <c r="I195" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.23</v>
+      </c>
+      <c r="I195" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J195" s="9" t="n">
-        <v>6.524</v>
+        <v>0.439</v>
       </c>
       <c r="K195" s="9" t="n">
-        <v>6.468</v>
+        <v>0.431</v>
       </c>
       <c r="L195" t="inlineStr"/>
       <c r="M195" s="14" t="inlineStr"/>
@@ -9256,28 +9256,28 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>0168</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>BMGREEN</t>
         </is>
       </c>
       <c r="D196" s="9" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="E196" s="15" t="n">
-        <v>0</v>
+        <v>1.73</v>
+      </c>
+      <c r="E196" s="10" t="n">
+        <v>0.0237</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>1469700</v>
+        <v>1513900</v>
       </c>
       <c r="G196" s="12" t="n">
-        <v>0.35</v>
+        <v>2.01</v>
       </c>
       <c r="H196" t="n">
-        <v>47.33</v>
+        <v>58.75</v>
       </c>
       <c r="I196" s="16" t="inlineStr">
         <is>
@@ -9285,10 +9285,10 @@
         </is>
       </c>
       <c r="J196" s="9" t="n">
-        <v>7.643</v>
+        <v>1.646</v>
       </c>
       <c r="K196" s="9" t="n">
-        <v>7.796</v>
+        <v>1.729</v>
       </c>
       <c r="L196" t="inlineStr"/>
       <c r="M196" s="14" t="inlineStr"/>
@@ -9301,28 +9301,28 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>TUNEPRO</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D197" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E197" s="10" t="n">
-        <v>0.0612</v>
+        <v>6.51</v>
+      </c>
+      <c r="E197" s="17" t="n">
+        <v>-0.0225</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>1455100</v>
+        <v>1489900</v>
       </c>
       <c r="G197" s="12" t="n">
-        <v>2.86</v>
+        <v>0.42</v>
       </c>
       <c r="H197" t="n">
-        <v>55.34</v>
+        <v>49.75</v>
       </c>
       <c r="I197" s="16" t="inlineStr">
         <is>
@@ -9330,10 +9330,10 @@
         </is>
       </c>
       <c r="J197" s="9" t="n">
-        <v>0.253</v>
+        <v>6.524</v>
       </c>
       <c r="K197" s="9" t="n">
-        <v>0.264</v>
+        <v>6.468</v>
       </c>
       <c r="L197" t="inlineStr"/>
       <c r="M197" s="14" t="inlineStr"/>
@@ -9346,28 +9346,28 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>UMSINT</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D198" s="9" t="n">
-        <v>8.529999999999999</v>
-      </c>
-      <c r="E198" s="10" t="n">
-        <v>0.0155</v>
+        <v>7.57</v>
+      </c>
+      <c r="E198" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>1442000</v>
+        <v>1469700</v>
       </c>
       <c r="G198" s="12" t="n">
-        <v>6.39</v>
+        <v>0.35</v>
       </c>
       <c r="H198" t="n">
-        <v>57.86</v>
+        <v>47.33</v>
       </c>
       <c r="I198" s="16" t="inlineStr">
         <is>
@@ -9375,10 +9375,10 @@
         </is>
       </c>
       <c r="J198" s="9" t="n">
-        <v>8.305</v>
+        <v>7.643</v>
       </c>
       <c r="K198" s="9" t="n">
-        <v>8.119999999999999</v>
+        <v>7.796</v>
       </c>
       <c r="L198" t="inlineStr"/>
       <c r="M198" s="14" t="inlineStr"/>
@@ -9391,28 +9391,28 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>UMSINT</t>
         </is>
       </c>
       <c r="D199" s="9" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="E199" s="17" t="n">
-        <v>-0.008699999999999999</v>
+        <v>8.529999999999999</v>
+      </c>
+      <c r="E199" s="10" t="n">
+        <v>0.0155</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>1429300</v>
+        <v>1442000</v>
       </c>
       <c r="G199" s="12" t="n">
-        <v>1.02</v>
+        <v>6.39</v>
       </c>
       <c r="H199" t="n">
-        <v>61.47</v>
+        <v>57.86</v>
       </c>
       <c r="I199" s="16" t="inlineStr">
         <is>
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="J199" s="9" t="n">
-        <v>2.175</v>
+        <v>8.305</v>
       </c>
       <c r="K199" s="9" t="n">
-        <v>2.001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L199" t="inlineStr"/>
       <c r="M199" s="14" t="inlineStr"/>
@@ -9901,7 +9901,7 @@
         <v>0.0023</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>1305100</v>
+        <v>1307600</v>
       </c>
       <c r="G210" s="12" t="n">
         <v>0.37</v>
@@ -10201,28 +10201,28 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>0285</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>MERSEC</t>
+          <t>SENTRAL</t>
         </is>
       </c>
       <c r="D217" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E217" s="15" t="n">
-        <v>0</v>
+        <v>0.65</v>
+      </c>
+      <c r="E217" s="17" t="n">
+        <v>-0.0076</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>1171400</v>
+        <v>1180200</v>
       </c>
       <c r="G217" s="12" t="n">
-        <v>1.32</v>
+        <v>1.61</v>
       </c>
       <c r="H217" t="n">
-        <v>43.77</v>
+        <v>36.4</v>
       </c>
       <c r="I217" s="13" t="inlineStr">
         <is>
@@ -10230,10 +10230,10 @@
         </is>
       </c>
       <c r="J217" s="9" t="n">
-        <v>0.279</v>
+        <v>0.663</v>
       </c>
       <c r="K217" s="9" t="n">
-        <v>0.274</v>
+        <v>0.68</v>
       </c>
       <c r="L217" t="inlineStr"/>
       <c r="M217" s="14" t="inlineStr"/>
@@ -10246,28 +10246,28 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>0285</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>SENTRAL</t>
+          <t>MERSEC</t>
         </is>
       </c>
       <c r="D218" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E218" s="17" t="n">
-        <v>-0.0076</v>
+        <v>0.275</v>
+      </c>
+      <c r="E218" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>1170200</v>
+        <v>1171400</v>
       </c>
       <c r="G218" s="12" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="H218" t="n">
-        <v>36.4</v>
+        <v>43.77</v>
       </c>
       <c r="I218" s="13" t="inlineStr">
         <is>
@@ -10275,10 +10275,10 @@
         </is>
       </c>
       <c r="J218" s="9" t="n">
-        <v>0.663</v>
+        <v>0.279</v>
       </c>
       <c r="K218" s="9" t="n">
-        <v>0.68</v>
+        <v>0.274</v>
       </c>
       <c r="L218" t="inlineStr"/>
       <c r="M218" s="14" t="inlineStr"/>
@@ -10306,7 +10306,7 @@
         <v>0.0052</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>1150000</v>
+        <v>1151000</v>
       </c>
       <c r="G219" s="12" t="n">
         <v>0.62</v>
@@ -10696,28 +10696,28 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D228" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E228" s="10" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.925</v>
+      </c>
+      <c r="E228" s="17" t="n">
+        <v>-0.0464</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>1084000</v>
+        <v>1089600</v>
       </c>
       <c r="G228" s="12" t="n">
-        <v>0.27</v>
+        <v>0.62</v>
       </c>
       <c r="H228" t="n">
-        <v>30.26</v>
+        <v>57.84</v>
       </c>
       <c r="I228" s="16" t="inlineStr">
         <is>
@@ -10725,10 +10725,10 @@
         </is>
       </c>
       <c r="J228" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.903</v>
       </c>
       <c r="K228" s="9" t="n">
-        <v>0.598</v>
+        <v>0.769</v>
       </c>
       <c r="L228" t="inlineStr"/>
       <c r="M228" s="14" t="inlineStr"/>
@@ -10741,28 +10741,28 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D229" s="9" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="E229" s="17" t="n">
-        <v>-0.0464</v>
+        <v>0.545</v>
+      </c>
+      <c r="E229" s="10" t="n">
+        <v>0.009300000000000001</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>1083600</v>
+        <v>1084000</v>
       </c>
       <c r="G229" s="12" t="n">
-        <v>0.61</v>
+        <v>0.27</v>
       </c>
       <c r="H229" t="n">
-        <v>57.84</v>
+        <v>30.26</v>
       </c>
       <c r="I229" s="16" t="inlineStr">
         <is>
@@ -10770,10 +10770,10 @@
         </is>
       </c>
       <c r="J229" s="9" t="n">
-        <v>0.903</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K229" s="9" t="n">
-        <v>0.769</v>
+        <v>0.598</v>
       </c>
       <c r="L229" t="inlineStr"/>
       <c r="M229" s="14" t="inlineStr"/>
@@ -10921,39 +10921,39 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>0265</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>INFOM</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D233" s="9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E233" s="10" t="n">
-        <v>0.0127</v>
+        <v>0.43</v>
+      </c>
+      <c r="E233" s="17" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>1040200</v>
+        <v>1076600</v>
       </c>
       <c r="G233" s="12" t="n">
-        <v>3.99</v>
+        <v>0.31</v>
       </c>
       <c r="H233" t="n">
-        <v>59.87</v>
-      </c>
-      <c r="I233" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.26</v>
+      </c>
+      <c r="I233" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J233" s="9" t="n">
-        <v>1.576</v>
+        <v>0.433</v>
       </c>
       <c r="K233" s="9" t="n">
-        <v>1.525</v>
+        <v>0.453</v>
       </c>
       <c r="L233" t="inlineStr"/>
       <c r="M233" s="14" t="inlineStr"/>
@@ -10966,39 +10966,39 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>0265</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>INFOM</t>
         </is>
       </c>
       <c r="D234" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E234" s="17" t="n">
-        <v>-0.0115</v>
+        <v>1.6</v>
+      </c>
+      <c r="E234" s="10" t="n">
+        <v>0.0127</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>1031600</v>
+        <v>1040200</v>
       </c>
       <c r="G234" s="12" t="n">
-        <v>0.3</v>
+        <v>3.99</v>
       </c>
       <c r="H234" t="n">
-        <v>47.26</v>
-      </c>
-      <c r="I234" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.87</v>
+      </c>
+      <c r="I234" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J234" s="9" t="n">
-        <v>0.433</v>
+        <v>1.576</v>
       </c>
       <c r="K234" s="9" t="n">
-        <v>0.453</v>
+        <v>1.525</v>
       </c>
       <c r="L234" t="inlineStr"/>
       <c r="M234" s="14" t="inlineStr"/>
@@ -11566,7 +11566,7 @@
         <v>-0.0278</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>810900</v>
+        <v>813900</v>
       </c>
       <c r="G247" s="12" t="n">
         <v>0.47</v>
@@ -11656,7 +11656,7 @@
         <v>0.0107</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>803800</v>
+        <v>805100</v>
       </c>
       <c r="G249" s="12" t="n">
         <v>0.75</v>
@@ -11731,39 +11731,39 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>LWSABAH</t>
         </is>
       </c>
       <c r="D251" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E251" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>1.74</v>
+      </c>
+      <c r="E251" s="17" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>767800</v>
+        <v>780100</v>
       </c>
       <c r="G251" s="12" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H251" t="n">
-        <v>56.79</v>
-      </c>
-      <c r="I251" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.02</v>
+      </c>
+      <c r="I251" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J251" s="9" t="n">
-        <v>0.626</v>
+        <v>1.701</v>
       </c>
       <c r="K251" s="9" t="n">
-        <v>0.605</v>
+        <v>1.607</v>
       </c>
       <c r="L251" t="inlineStr"/>
       <c r="M251" s="14" t="inlineStr"/>
@@ -11776,28 +11776,28 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>TIMWELL</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D252" s="9" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="E252" s="15" t="n">
-        <v>0</v>
+        <v>0.64</v>
+      </c>
+      <c r="E252" s="10" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F252" s="11" t="n">
-        <v>753300</v>
+        <v>767800</v>
       </c>
       <c r="G252" s="12" t="n">
-        <v>1.13</v>
+        <v>0.59</v>
       </c>
       <c r="H252" t="n">
-        <v>78.97</v>
+        <v>56.79</v>
       </c>
       <c r="I252" s="16" t="inlineStr">
         <is>
@@ -11805,10 +11805,10 @@
         </is>
       </c>
       <c r="J252" s="9" t="n">
-        <v>2.128</v>
+        <v>0.626</v>
       </c>
       <c r="K252" s="9" t="n">
-        <v>1.973</v>
+        <v>0.605</v>
       </c>
       <c r="L252" t="inlineStr"/>
       <c r="M252" s="14" t="inlineStr"/>
@@ -11821,28 +11821,28 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>7854</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>KENANGA</t>
+          <t>TIMWELL</t>
         </is>
       </c>
       <c r="D253" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E253" s="10" t="n">
-        <v>0.0248</v>
+        <v>2.26</v>
+      </c>
+      <c r="E253" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F253" s="11" t="n">
-        <v>740700</v>
+        <v>753300</v>
       </c>
       <c r="G253" s="12" t="n">
-        <v>1.45</v>
+        <v>1.13</v>
       </c>
       <c r="H253" t="n">
-        <v>43.29</v>
+        <v>78.97</v>
       </c>
       <c r="I253" s="16" t="inlineStr">
         <is>
@@ -11850,10 +11850,10 @@
         </is>
       </c>
       <c r="J253" s="9" t="n">
-        <v>0.623</v>
+        <v>2.128</v>
       </c>
       <c r="K253" s="9" t="n">
-        <v>0.668</v>
+        <v>1.973</v>
       </c>
       <c r="L253" t="inlineStr"/>
       <c r="M253" s="14" t="inlineStr"/>
@@ -11881,7 +11881,7 @@
         <v>-0.008500000000000001</v>
       </c>
       <c r="F254" s="11" t="n">
-        <v>736500</v>
+        <v>741500</v>
       </c>
       <c r="G254" s="12" t="n">
         <v>0.41</v>
@@ -11911,39 +11911,39 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>LWSABAH</t>
+          <t>KENANGA</t>
         </is>
       </c>
       <c r="D255" s="9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="E255" s="17" t="n">
-        <v>-0.0169</v>
+        <v>0.62</v>
+      </c>
+      <c r="E255" s="10" t="n">
+        <v>0.0248</v>
       </c>
       <c r="F255" s="11" t="n">
-        <v>709800</v>
+        <v>740700</v>
       </c>
       <c r="G255" s="12" t="n">
-        <v>0.51</v>
+        <v>1.45</v>
       </c>
       <c r="H255" t="n">
-        <v>58.02</v>
-      </c>
-      <c r="I255" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.29</v>
+      </c>
+      <c r="I255" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J255" s="9" t="n">
-        <v>1.701</v>
+        <v>0.623</v>
       </c>
       <c r="K255" s="9" t="n">
-        <v>1.607</v>
+        <v>0.668</v>
       </c>
       <c r="L255" t="inlineStr"/>
       <c r="M255" s="14" t="inlineStr"/>
@@ -11956,28 +11956,28 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>SENFONG</t>
+          <t>AEON</t>
         </is>
       </c>
       <c r="D256" s="9" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="E256" s="17" t="n">
+        <v>-0.0104</v>
+      </c>
+      <c r="F256" s="11" t="n">
+        <v>733100</v>
+      </c>
+      <c r="G256" s="12" t="n">
         <v>0.7</v>
       </c>
-      <c r="E256" s="10" t="n">
-        <v>0.0219</v>
-      </c>
-      <c r="F256" s="11" t="n">
-        <v>704500</v>
-      </c>
-      <c r="G256" s="12" t="n">
-        <v>4.23</v>
-      </c>
       <c r="H256" t="n">
-        <v>55.57</v>
+        <v>28.62</v>
       </c>
       <c r="I256" s="13" t="inlineStr">
         <is>
@@ -11985,10 +11985,10 @@
         </is>
       </c>
       <c r="J256" s="9" t="n">
-        <v>0.694</v>
+        <v>0.983</v>
       </c>
       <c r="K256" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>1.016</v>
       </c>
       <c r="L256" t="inlineStr"/>
       <c r="M256" s="14" t="inlineStr"/>
@@ -12016,10 +12016,10 @@
         <v>-0.0282</v>
       </c>
       <c r="F257" s="11" t="n">
-        <v>697400</v>
+        <v>706400</v>
       </c>
       <c r="G257" s="12" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="H257" t="n">
         <v>55.04</v>
@@ -12046,39 +12046,39 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>1562</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>SPTOTO</t>
+          <t>SENFONG</t>
         </is>
       </c>
       <c r="D258" s="9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E258" s="17" t="n">
-        <v>-0.0156</v>
+        <v>0.7</v>
+      </c>
+      <c r="E258" s="10" t="n">
+        <v>0.0219</v>
       </c>
       <c r="F258" s="11" t="n">
-        <v>695200</v>
+        <v>704500</v>
       </c>
       <c r="G258" s="12" t="n">
-        <v>1.52</v>
+        <v>4.23</v>
       </c>
       <c r="H258" t="n">
-        <v>40.32</v>
-      </c>
-      <c r="I258" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.57</v>
+      </c>
+      <c r="I258" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J258" s="9" t="n">
-        <v>1.279</v>
+        <v>0.694</v>
       </c>
       <c r="K258" s="9" t="n">
-        <v>1.304</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="L258" t="inlineStr"/>
       <c r="M258" s="14" t="inlineStr"/>
@@ -12091,28 +12091,28 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>5028</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>HTPADU</t>
+          <t>SPTOTO</t>
         </is>
       </c>
       <c r="D259" s="9" t="n">
-        <v>0.905</v>
+        <v>1.26</v>
       </c>
       <c r="E259" s="17" t="n">
-        <v>-0.0622</v>
+        <v>-0.0156</v>
       </c>
       <c r="F259" s="11" t="n">
-        <v>688100</v>
+        <v>695200</v>
       </c>
       <c r="G259" s="12" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="H259" t="n">
-        <v>25.08</v>
+        <v>40.32</v>
       </c>
       <c r="I259" s="16" t="inlineStr">
         <is>
@@ -12120,10 +12120,10 @@
         </is>
       </c>
       <c r="J259" s="9" t="n">
-        <v>1.023</v>
+        <v>1.279</v>
       </c>
       <c r="K259" s="9" t="n">
-        <v>1.161</v>
+        <v>1.304</v>
       </c>
       <c r="L259" t="inlineStr"/>
       <c r="M259" s="14" t="inlineStr"/>
@@ -12136,28 +12136,28 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5028</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>AMEREIT</t>
+          <t>HTPADU</t>
         </is>
       </c>
       <c r="D260" s="9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E260" s="10" t="n">
-        <v>0.0323</v>
+        <v>0.905</v>
+      </c>
+      <c r="E260" s="17" t="n">
+        <v>-0.0622</v>
       </c>
       <c r="F260" s="11" t="n">
-        <v>677800</v>
+        <v>688100</v>
       </c>
       <c r="G260" s="12" t="n">
-        <v>13.25</v>
+        <v>1.45</v>
       </c>
       <c r="H260" t="n">
-        <v>63.43</v>
+        <v>25.08</v>
       </c>
       <c r="I260" s="16" t="inlineStr">
         <is>
@@ -12165,10 +12165,10 @@
         </is>
       </c>
       <c r="J260" s="9" t="n">
-        <v>1.528</v>
+        <v>1.023</v>
       </c>
       <c r="K260" s="9" t="n">
-        <v>1.522</v>
+        <v>1.161</v>
       </c>
       <c r="L260" t="inlineStr"/>
       <c r="M260" s="14" t="inlineStr"/>
@@ -12181,28 +12181,28 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>PIE</t>
+          <t>AMEREIT</t>
         </is>
       </c>
       <c r="D261" s="9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="E261" s="17" t="n">
-        <v>-0.0269</v>
+        <v>1.6</v>
+      </c>
+      <c r="E261" s="10" t="n">
+        <v>0.0323</v>
       </c>
       <c r="F261" s="11" t="n">
-        <v>671800</v>
+        <v>677800</v>
       </c>
       <c r="G261" s="12" t="n">
-        <v>0.53</v>
+        <v>13.25</v>
       </c>
       <c r="H261" t="n">
-        <v>60.91</v>
+        <v>63.43</v>
       </c>
       <c r="I261" s="16" t="inlineStr">
         <is>
@@ -12210,10 +12210,10 @@
         </is>
       </c>
       <c r="J261" s="9" t="n">
-        <v>1.714</v>
+        <v>1.528</v>
       </c>
       <c r="K261" s="9" t="n">
-        <v>1.606</v>
+        <v>1.522</v>
       </c>
       <c r="L261" t="inlineStr"/>
       <c r="M261" s="14" t="inlineStr"/>
@@ -12226,39 +12226,39 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>PIE</t>
         </is>
       </c>
       <c r="D262" s="9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="E262" s="17" t="n">
+        <v>-0.0269</v>
+      </c>
+      <c r="F262" s="11" t="n">
+        <v>671800</v>
+      </c>
+      <c r="G262" s="12" t="n">
         <v>0.53</v>
       </c>
-      <c r="E262" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F262" s="11" t="n">
-        <v>669100</v>
-      </c>
-      <c r="G262" s="12" t="n">
-        <v>1.02</v>
-      </c>
       <c r="H262" t="n">
-        <v>52.07</v>
-      </c>
-      <c r="I262" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.91</v>
+      </c>
+      <c r="I262" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J262" s="9" t="n">
-        <v>0.529</v>
+        <v>1.714</v>
       </c>
       <c r="K262" s="9" t="n">
-        <v>0.526</v>
+        <v>1.606</v>
       </c>
       <c r="L262" t="inlineStr"/>
       <c r="M262" s="14" t="inlineStr"/>
@@ -12271,28 +12271,28 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>AEON</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="D263" s="9" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="E263" s="17" t="n">
-        <v>-0.0104</v>
+        <v>0.53</v>
+      </c>
+      <c r="E263" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F263" s="11" t="n">
-        <v>663100</v>
+        <v>669100</v>
       </c>
       <c r="G263" s="12" t="n">
-        <v>0.63</v>
+        <v>1.02</v>
       </c>
       <c r="H263" t="n">
-        <v>28.62</v>
+        <v>52.07</v>
       </c>
       <c r="I263" s="13" t="inlineStr">
         <is>
@@ -12300,10 +12300,10 @@
         </is>
       </c>
       <c r="J263" s="9" t="n">
-        <v>0.983</v>
+        <v>0.529</v>
       </c>
       <c r="K263" s="9" t="n">
-        <v>1.016</v>
+        <v>0.526</v>
       </c>
       <c r="L263" t="inlineStr"/>
       <c r="M263" s="14" t="inlineStr"/>
@@ -12316,39 +12316,39 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>7084</t>
+          <t>7034</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>QL</t>
+          <t>TGUAN</t>
         </is>
       </c>
       <c r="D264" s="9" t="n">
-        <v>4</v>
+        <v>1.52</v>
       </c>
       <c r="E264" s="10" t="n">
-        <v>0.005</v>
+        <v>0.0066</v>
       </c>
       <c r="F264" s="11" t="n">
-        <v>655400</v>
+        <v>657600</v>
       </c>
       <c r="G264" s="12" t="n">
-        <v>0.38</v>
+        <v>0.99</v>
       </c>
       <c r="H264" t="n">
-        <v>55.89</v>
-      </c>
-      <c r="I264" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.72</v>
+      </c>
+      <c r="I264" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J264" s="9" t="n">
-        <v>3.916</v>
+        <v>1.596</v>
       </c>
       <c r="K264" s="9" t="n">
-        <v>3.924</v>
+        <v>1.554</v>
       </c>
       <c r="L264" t="inlineStr"/>
       <c r="M264" s="14" t="inlineStr"/>
@@ -12361,39 +12361,39 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>7034</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>TGUAN</t>
+          <t>QL</t>
         </is>
       </c>
       <c r="D265" s="9" t="n">
-        <v>1.52</v>
+        <v>4</v>
       </c>
       <c r="E265" s="10" t="n">
-        <v>0.0066</v>
+        <v>0.005</v>
       </c>
       <c r="F265" s="11" t="n">
-        <v>652600</v>
+        <v>655400</v>
       </c>
       <c r="G265" s="12" t="n">
-        <v>0.98</v>
+        <v>0.38</v>
       </c>
       <c r="H265" t="n">
-        <v>38.72</v>
-      </c>
-      <c r="I265" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.89</v>
+      </c>
+      <c r="I265" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J265" s="9" t="n">
-        <v>1.596</v>
+        <v>3.916</v>
       </c>
       <c r="K265" s="9" t="n">
-        <v>1.554</v>
+        <v>3.924</v>
       </c>
       <c r="L265" t="inlineStr"/>
       <c r="M265" s="14" t="inlineStr"/>
@@ -12541,39 +12541,39 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>SAM</t>
         </is>
       </c>
       <c r="D269" s="9" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E269" s="10" t="n">
-        <v>0.011</v>
+        <v>4.03</v>
+      </c>
+      <c r="E269" s="17" t="n">
+        <v>-0.0147</v>
       </c>
       <c r="F269" s="11" t="n">
-        <v>593700</v>
+        <v>597500</v>
       </c>
       <c r="G269" s="12" t="n">
-        <v>0.2</v>
+        <v>0.66</v>
       </c>
       <c r="H269" t="n">
-        <v>60</v>
-      </c>
-      <c r="I269" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.54</v>
+      </c>
+      <c r="I269" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J269" s="9" t="n">
-        <v>0.881</v>
+        <v>4.22</v>
       </c>
       <c r="K269" s="9" t="n">
-        <v>0.796</v>
+        <v>4.358</v>
       </c>
       <c r="L269" t="inlineStr"/>
       <c r="M269" s="14" t="inlineStr"/>
@@ -12586,39 +12586,39 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>9822</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>SAM</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D270" s="9" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="E270" s="17" t="n">
-        <v>-0.0147</v>
+        <v>0.915</v>
+      </c>
+      <c r="E270" s="10" t="n">
+        <v>0.011</v>
       </c>
       <c r="F270" s="11" t="n">
-        <v>587500</v>
+        <v>593700</v>
       </c>
       <c r="G270" s="12" t="n">
-        <v>0.65</v>
+        <v>0.2</v>
       </c>
       <c r="H270" t="n">
-        <v>40.54</v>
-      </c>
-      <c r="I270" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60</v>
+      </c>
+      <c r="I270" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J270" s="9" t="n">
-        <v>4.22</v>
+        <v>0.881</v>
       </c>
       <c r="K270" s="9" t="n">
-        <v>4.358</v>
+        <v>0.796</v>
       </c>
       <c r="L270" t="inlineStr"/>
       <c r="M270" s="14" t="inlineStr"/>
@@ -12826,7 +12826,7 @@
         <v>-0.021</v>
       </c>
       <c r="F275" s="11" t="n">
-        <v>548500</v>
+        <v>548600</v>
       </c>
       <c r="G275" s="12" t="n">
         <v>0.52</v>

--- a/docs/downloads/2026-09-24/bursa-report-2026-09-24.xlsx
+++ b/docs/downloads/2026-09-24/bursa-report-2026-09-24.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.67高于50日均线0.645，EMA20与SAR均呈多头，T3形态突破；RSI 58.41处中性偏强，未超买，信号技术面较可靠。</t>
+          <t>现价0.67高于50日均线0.645，EMA20与SAR均呈多头，T3形态突破；RSI 58.41处中性偏强区间，未超买，信号技术面一致性尚可。</t>
         </is>
       </c>
     </row>
@@ -3227,9 +3227,9 @@
       <c r="H61" t="n">
         <v>52.44</v>
       </c>
-      <c r="I61" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+      <c r="I61" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">

--- a/docs/downloads/2026-09-24/bursa-report-2026-09-24.xlsx
+++ b/docs/downloads/2026-09-24/bursa-report-2026-09-24.xlsx
@@ -3227,9 +3227,9 @@
       <c r="H61" t="n">
         <v>52.44</v>
       </c>
-      <c r="I61" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
